--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo por nicho'!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Varredura'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -818,14 +818,14 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
+          <t>stalkeia</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
           <t>Stalkeia</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>Stalkeia.ai</t>
-        </is>
-      </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
           <t>marca</t>
@@ -843,45 +843,41 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>quente</t>
+          <t>fria</t>
         </is>
       </c>
       <c r="G2" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>R$ 47-87</t>
+          <t>R$ 37,00</t>
         </is>
       </c>
       <c r="I2" s="12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="J2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="12" t="inlineStr">
-        <is>
-          <t>App de espionar WhatsApp/Instagram. Grafias: Stalkeia.com, Stalkeia App, IA STALKER. Cobra créditos extras para liberar resultado. Três menções em 25/08-26/08 com valores R$ 47 e R$ 87.</t>
-        </is>
-      </c>
+      <c r="K2" s="12" t="inlineStr"/>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/cobranca-de-taxa-adicional-nao-combinada-e-falta-de-acesso-ao-produto-comprado__chfFQTX8pupMWB5/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa-do-aplicativo-stalkeia-app-e-solicitacao-de-reembolso_zrIGWUSWcSp7p5Xp/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>hqflix</t>
+          <t>spygram</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>hqflix</t>
+          <t>Spygram</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -891,12 +887,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Streaming e entretenimento</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -907,40 +903,40 @@
       <c r="G3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="12" t="inlineStr"/>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>R$ 49,80</t>
+        </is>
+      </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="J3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="12" t="inlineStr">
-        <is>
-          <t>Serviço de streaming anunciado como acesso vitalício. Comprador de 21/11/2025 não consegue mais acessar. Solicita estorno.</t>
-        </is>
-      </c>
+      <c r="K3" s="12" t="inlineStr"/>
       <c r="L3" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/usuario-solicita-estorno-por-nao-conseguir-mais-acessar-o-servico-hqflix-que-foi-anunciado-como-acesso-vitalicio_7zfD-D4s6GauY3fc/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/usuario-pagou-por-app-de-monitoramento-falso-e-nao-recebeu-acesso-a-nada-solicita-reembolso_h9AXG_wRQFTAEB9J/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>freelancer imediato</t>
+          <t>comprado. gostaria do reembolso assim que</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>PLANO FREELANCER IMEDIATO</t>
+          <t>comprado. Gostaria do reembolso assim que</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -950,7 +946,7 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / trabalho remoto</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -961,39 +957,31 @@
       <c r="G4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>R$ 11 + R$ 30 upsell</t>
-        </is>
-      </c>
+      <c r="H4" s="12" t="inlineStr"/>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="J4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="12" t="inlineStr">
-        <is>
-          <t>Plano vendido pela equipe Cakto por R$ 11 para acessar sites de trabalho remoto. Após pagamento, exige R$ 30 adicional para liberar acesso. Mecânica de taxa para desbloquear.</t>
-        </is>
-      </c>
+      <c r="K4" s="12" t="inlineStr"/>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/plano-freelancer-imediato-pagamento-adicional-exigido-apos-compra-inicial-para-liberacao-de-acesso_Aa7b4b27tHVPApDH/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/pagamento-via-pix-nao-resultou-na-entrega-do-produto-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_cbUdm8Fq5-5oanwH/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>pagamento nao recebido cakto</t>
+          <t>curso online</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Pagamentos não recebidos (ângulo)</t>
+          <t>curso online</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -1008,7 +996,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Serviços financeiros / Pix</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -1019,198 +1007,24 @@
       <c r="G5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>R$ 13,89 + R$ 38,89</t>
-        </is>
-      </c>
+      <c r="H5" s="12" t="inlineStr"/>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="J5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>Cliente alega ter feito pagamentos via Cakto Pay (R$ 13,89 e R$ 38,89) e não ter recebido o serviço. Padrão de cobrança sem entrega.</t>
-        </is>
-      </c>
+      <c r="K5" s="12" t="inlineStr"/>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/cliente-alega-ter-sido-editado-pelo-reclame-aqui-pela-cakto-pay-apos-solicitacao-de-pagamento-nao-recebido_iGkp9DgcxElv0_2Y/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>reembolso cakto dificuldade</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Dificuldade de reembolso Cakto (ângulo)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Infoprodutos - suporte e reembolso</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="12" t="inlineStr"/>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>Comprador pediu reembolso em menos de 4 dias, não obteve resposta do produtor nem suporte da Cakto. Indica falha no fluxo de reembolso da plataforma.</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-falta-de-resposta-e-dificuldade-de-reembolso-na-cakto_jiJdywNvdI1eyqGx/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>conta digital cakto validacao falha</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Falha validação Conta Digital Cakto - produtor (ângulo)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Serviços financeiros / conta digital</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>R$ 1.100+ retidos</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>Produtor com vendas ativas não consegue transferir saldo (R$ 1.100+) por falha na validação da Conta Digital Cakto. Suporte lento, 15+ dias sem resolução. Travando operação de tráfego pago.</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/produtor-da-cakto-nao-consegue-transferir-saldo-de-vendas-devido-a-falha-na-validacao-da-conta-digital_4DnOrKwoT1hMSEch/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>reembolso perfectpay recusa</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Recusa reembolso PerfectPay (ângulo)</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>PerfectPay</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Infoprodutos - suporte e reembolso</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>Comprador solicita reembolso horas após compra, envia provas (PIX, email cancelamento, WhatsApp inativo). PerfectPay responde com mensagens robóticas genéricas pedindo mesmas infos já anexadas. Recusa intervir.</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-recusa-de-reembolso-e-atendimento-generico-pela-perfect-pay_BFp4AxOI5U-r8e8Q/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/curso-online-nao-entregue-apos-pagamento-com-falha-na-comunicacao-e-solicitacao-de-estorno_-bekag5hY78F-1mM/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L8"/>
+  <autoFilter ref="A1:L5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1221,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1273,17 +1087,17 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="B2" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C2" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14" t="n">
         <v>0</v>
-      </c>
-      <c r="D2" s="14" t="n">
-        <v>2</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>0</v>
@@ -1298,126 +1112,26 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="14" t="n">
         <v>0</v>
-      </c>
-      <c r="E3" s="14" t="n">
-        <v>1</v>
       </c>
       <c r="F3" s="14" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Streaming e entretenimento</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Ganhar dinheiro online / trabalho remoto</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Serviços financeiros / Pix</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Serviços financeiros / conta digital</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1431,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1488,7 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1797,12 +1511,12 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>conta digital cakto validacao falha</t>
+          <t>comprado. gostaria do reembolso assim que</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C22" s="14" t="n">
@@ -1812,7 +1526,7 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>freelancer imediato</t>
+          <t>conta digital cakto validacao falha</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -1821,18 +1535,18 @@
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>hqflix</t>
+          <t>curso online</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C24" s="14" t="n">
@@ -1842,7 +1556,7 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>pagamento nao recebido cakto</t>
+          <t>freelancer imediato</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
@@ -1851,13 +1565,13 @@
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>reembolso cakto dificuldade</t>
+          <t>hqflix</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
@@ -1866,21 +1580,81 @@
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
+          <t>pagamento nao recebido cakto</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>reembolso cakto dificuldade</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
           <t>reembolso perfectpay recusa</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C29" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>spygram</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>stalkeia</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -849,23 +849,19 @@
       <c r="G2" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>R$ 37,00</t>
-        </is>
-      </c>
+      <c r="H2" s="12" t="inlineStr"/>
       <c r="I2" s="12" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
       <c r="J2" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" s="12" t="inlineStr"/>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa-do-aplicativo-stalkeia-app-e-solicitacao-de-reembolso_zrIGWUSWcSp7p5Xp/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa__4nr816NYlTJmFOB/</t>
         </is>
       </c>
     </row>
@@ -914,7 +910,7 @@
         </is>
       </c>
       <c r="J3" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="12" t="inlineStr"/>
       <c r="L3" s="12" t="inlineStr">
@@ -964,7 +960,7 @@
         </is>
       </c>
       <c r="J4" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="12" t="inlineStr"/>
       <c r="L4" s="12" t="inlineStr">
@@ -1014,7 +1010,7 @@
         </is>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="12" t="inlineStr"/>
       <c r="L5" s="12" t="inlineStr">
@@ -1520,7 +1516,7 @@
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1550,7 +1546,7 @@
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1640,7 +1636,7 @@
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1655,7 +1651,7 @@
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="G2" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="12" t="inlineStr"/>
       <c r="I2" s="12" t="inlineStr">
@@ -856,12 +856,12 @@
         </is>
       </c>
       <c r="J2" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12" t="inlineStr"/>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa__4nr816NYlTJmFOB/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa-do-aplicativo-stalkeia-app-e-solicitacao-de-reembolso_zrIGWUSWcSp7p5Xp/</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="J3" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="12" t="inlineStr"/>
       <c r="L3" s="12" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="J4" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="12" t="inlineStr"/>
       <c r="L4" s="12" t="inlineStr">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="J5" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="12" t="inlineStr"/>
       <c r="L5" s="12" t="inlineStr">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo por nicho'!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Varredura'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -847,33 +847,37 @@
         </is>
       </c>
       <c r="G2" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="12" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>R$ 47,00, R$ 87,00</t>
+        </is>
+      </c>
       <c r="I2" s="12" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
       <c r="J2" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="12" t="inlineStr"/>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa-do-aplicativo-stalkeia-app-e-solicitacao-de-reembolso_zrIGWUSWcSp7p5Xp/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/cobranca-de-taxa-adicional-nao-combinada-e-falta-de-acesso-ao-produto-comprado__chfFQTX8pupMWB5/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>spygram</t>
+          <t>hqflix</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Spygram</t>
+          <t>hqflix</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -883,12 +887,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Streaming e entretenimento</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -899,40 +903,36 @@
       <c r="G3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>R$ 49,80</t>
-        </is>
-      </c>
+      <c r="H3" s="12" t="inlineStr"/>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="J3" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" s="12" t="inlineStr"/>
       <c r="L3" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/usuario-pagou-por-app-de-monitoramento-falso-e-nao-recebeu-acesso-a-nada-solicita-reembolso_h9AXG_wRQFTAEB9J/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/usuario-solicita-estorno-por-nao-conseguir-mais-acessar-o-servico-hqflix-que-foi-anunciado-como-acesso-vitalicio_7zfD-D4s6GauY3fc/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>comprado. gostaria do reembolso assim que</t>
+          <t>plano freelancer imediato</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>comprado. Gostaria do reembolso assim que</t>
+          <t>Plano Freelancer Imediato</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -953,74 +953,28 @@
       <c r="G4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="12" t="inlineStr"/>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>R$ 11,00</t>
+        </is>
+      </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J4" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" s="12" t="inlineStr"/>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/pagamento-via-pix-nao-resultou-na-entrega-do-produto-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_cbUdm8Fq5-5oanwH/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>curso online</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>curso online</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" s="12" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/curso-online-nao-entregue-apos-pagamento-com-falha-na-comunicacao-e-solicitacao-de-estorno_-bekag5hY78F-1mM/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/plano-freelancer-imediato-pagamento-adicional-exigido-apos-compra-inicial-para-liberacao-de-acesso_Aa7b4b27tHVPApDH/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1031,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1087,10 +1041,10 @@
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="14" t="n">
         <v>0</v>
@@ -1102,23 +1056,23 @@
         <v>0</v>
       </c>
       <c r="G2" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Streaming e entretenimento</t>
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="14" t="n">
         <v>0</v>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>2</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>0</v>
@@ -1127,7 +1081,32 @@
         <v>0</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1141,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1516,7 +1495,7 @@
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1546,7 +1525,7 @@
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1597,22 +1576,22 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>reembolso cakto dificuldade</t>
+          <t>plano freelancer imediato</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>reembolso perfectpay recusa</t>
+          <t>reembolso cakto dificuldade</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -1627,31 +1606,46 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>spygram</t>
+          <t>reembolso perfectpay recusa</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
+          <t>spygram</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
           <t>stalkeia</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="C31" s="14" t="n">
-        <v>2</v>
+      <c r="C32" s="14" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumo por nicho" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Varredura" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Achados" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Resumo_Nicho" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Historico" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo por nicho" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Varredura" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achados" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo_Nicho" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo por nicho'!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Varredura'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -847,11 +847,11 @@
         </is>
       </c>
       <c r="G2" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>R$ 47,00, R$ 87,00</t>
+          <t>R$ 47</t>
         </is>
       </c>
       <c r="I2" s="12" t="inlineStr">
@@ -860,24 +860,28 @@
         </is>
       </c>
       <c r="J2" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" s="12" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>realizei o pagamento direto no aplicativo, que prometia te entregar informações privadas de qualquer conta no instagram. porém, depois que você faz o primeiro pagamento, você não consegue o que é prometido enquanto não pagar outros valores, e ainda ameaçam enviar um alerta para a conta que supostamente eles estão espionando. acabei fazendo diversos pagamentos (deixei o pdf em anexo), e no final das contas não tive acesso a nada, pois fiz o teste com outras contas no instagram e ele simplesmente</t>
+        </is>
+      </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/cobranca-de-taxa-adicional-nao-combinada-e-falta-de-acesso-ao-produto-comprado__chfFQTX8pupMWB5/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa-do-e-solicitacao-de-reembolso-do-valor-pago_yID1cmkfVopy5OrZ/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>hqflix</t>
+          <t>lumi ai</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>hqflix</t>
+          <t>Lumi AI</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -892,7 +896,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Streaming e entretenimento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -903,46 +907,54 @@
       <c r="G3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="12" t="inlineStr"/>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>R$ 959,99.</t>
+        </is>
+      </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J3" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" s="12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>REEMBOLSO SOLICITADO DENTRO DO PRAZO, MAS Cakto IMPEDE A DEVOLUÇÃO POR FALTA DE SALDO DO PRODUTOR Realizei a compra do infoproduto Lumi AI através da plataforma Cakto no dia 27/08/2026, no valor de R$ 959,99. ID do pedido: ***** No dia seguinte à compra, em 28/08/2026, solicitei o reembolso pela própria plataforma, portanto dentro do prazo de 7 dias para solicitação de reembolso. O problema é que, ao tentar realizar o procedimento, a plataforma informa que o produtor está sem saldo suficiente pa</t>
+        </is>
+      </c>
       <c r="L3" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/usuario-solicita-estorno-por-nao-conseguir-mais-acessar-o-servico-hqflix-que-foi-anunciado-como-acesso-vitalicio_7zfD-D4s6GauY3fc/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-negado-por-falta-de-saldo-do-produtor-na-plataforma-cakto-apesar-de-solicitacao-dentro-do-prazo_387A3HmFDomhHErm/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>plano freelancer imediato</t>
+          <t>um curso e</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Plano Freelancer Imediato</t>
+          <t>um curso e</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -953,11 +965,7 @@
       <c r="G4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>R$ 11,00</t>
-        </is>
-      </c>
+      <c r="H4" s="12" t="inlineStr"/>
       <c r="I4" s="12" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -969,12 +977,178 @@
       <c r="K4" s="12" t="inlineStr"/>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/plano-freelancer-imediato-pagamento-adicional-exigido-apos-compra-inicial-para-liberacao-de-acesso_Aa7b4b27tHVPApDH/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/editado-pelo-reclame-aqui_UeZdzzFsRKKhakiR/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>eles mandam entrar em contato com od</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>eles mandam entrar em contato com o prod</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="12" t="inlineStr"/>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>Fiz uma compra pela empresa onde diz que tenho 7 dia para solicitar o cancelamento/reembolso de forma prática e ao solicitar o serviço eles mandam entrar em contato com o produtor e o mesmo não responde aos emails e mensagens enviadas pelos canais de comunicação e a plataforma CAKTO não está intervindo na situação e o prazo já vai esgotar e eles não resolvem a situação. Obs: o cancelamento/reembolso foi solicitado com menos de 24h após a adesão, já se passaram mais de 4 dias sem retorno. Empresa</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/empresa-nao-resolve-cancelamentoreembolso-e-nao-intervem-na-situacao_9tJ1cPoKxiMdK6tR/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>vavá academy</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Vavá Academy</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="12" t="inlineStr"/>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>Realizei a compra de um produto da Vavá Academy por meio da plataforma Cakto, porém **não recebi o acesso à plataforma nem o produto adquirido**. Após a compra, tentei entrar em contato com o criador responsável por e-mail para solicitar o acesso e resolver a situação, mas **não obtive nenhuma resposta** até o momento. Ou seja, o pagamento foi realizado, mas o produto não foi disponibilizado e não estou conseguindo contato com o responsável. Diante disso, solicito o **reembolso integral do valor</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/produto-nao-entregue-e-criador-nao-responde-solicito-reembolso_605Q8ntQ-aQlegi3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>grupo no telegram</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Grupo no Telegram</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>R$ 143,68.</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>No final de julho, realizei a compra de um produto digital chamado "GRUPO NO TELEGRAM" através de um link gerado na plataforma Cakto. O vendedor se identifica como Kaique Santtos, cujo e-mail cadastrado e de contato é *****. A compra foi aprovada no meu cartão de crédito sob o código de pedido *****, no valor de R$ 143,68. Na minha fatura, a cobrança aparece exatamente como "CAKTO*GRUPO NO TELEGRAM". Durante a negociação no WhatsApp, o vendedor me informou que a entrega (a transferência de posse</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/editado-pelo-reclame-aqui-em-compra-de-produto-digital-processada-pela-cakto-com-editado-pelo-reclame-aqui-e-nao-entrega_HJtQooCkVBEfTtMB/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1041,13 +1215,13 @@
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>0</v>
@@ -1056,23 +1230,23 @@
         <v>0</v>
       </c>
       <c r="G2" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Streaming e entretenimento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>0</v>
@@ -1081,23 +1255,23 @@
         <v>0</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>0</v>
@@ -1106,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1120,7 +1294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1531,22 +1705,22 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>freelancer imediato</t>
+          <t>eles mandam entrar em contato com od</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>hqflix</t>
+          <t>freelancer imediato</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
@@ -1561,52 +1735,52 @@
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>pagamento nao recebido cakto</t>
+          <t>grupo no telegram</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>plano freelancer imediato</t>
+          <t>hqflix</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>reembolso cakto dificuldade</t>
+          <t>lumi ai</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>reembolso perfectpay recusa</t>
+          <t>pagamento nao recebido cakto</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -1621,31 +1795,106 @@
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>spygram</t>
+          <t>plano freelancer imediato</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
+          <t>reembolso cakto dificuldade</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>reembolso perfectpay recusa</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>spygram</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
           <t>stalkeia</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="C32" s="14" t="n">
-        <v>3</v>
+      <c r="C35" s="14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>um curso e</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>vavá academy</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo por nicho'!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Varredura'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="J2" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2" s="12" t="inlineStr">
         <is>
@@ -876,27 +876,27 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>lumi ai</t>
+          <t>um curso e</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Lumi AI</t>
+          <t>um curso e</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -907,39 +907,31 @@
       <c r="G3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>R$ 959,99.</t>
-        </is>
-      </c>
+      <c r="H3" s="12" t="inlineStr"/>
       <c r="I3" s="12" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
       <c r="J3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="12" t="inlineStr">
-        <is>
-          <t>REEMBOLSO SOLICITADO DENTRO DO PRAZO, MAS Cakto IMPEDE A DEVOLUÇÃO POR FALTA DE SALDO DO PRODUTOR Realizei a compra do infoproduto Lumi AI através da plataforma Cakto no dia 27/08/2026, no valor de R$ 959,99. ID do pedido: ***** No dia seguinte à compra, em 28/08/2026, solicitei o reembolso pela própria plataforma, portanto dentro do prazo de 7 dias para solicitação de reembolso. O problema é que, ao tentar realizar o procedimento, a plataforma informa que o produtor está sem saldo suficiente pa</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K3" s="12" t="inlineStr"/>
       <c r="L3" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-negado-por-falta-de-saldo-do-produtor-na-plataforma-cakto-apesar-de-solicitacao-dentro-do-prazo_387A3HmFDomhHErm/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/editado-pelo-reclame-aqui_UeZdzzFsRKKhakiR/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>mas eu n</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>mas eu n</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -949,12 +941,12 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -977,19 +969,19 @@
       <c r="K4" s="12" t="inlineStr"/>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/editado-pelo-reclame-aqui_UeZdzzFsRKKhakiR/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/vendedor-nao-recebe-dinheiro-das-vendas-devido-a-analise-de-documentacao-demorada-e-suporte-lento_oW_Ar32UzJWou7Co/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>eles mandam entrar em contato com od</t>
+          <t>um livro de macrame em paguei com pix. en</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>eles mandam entrar em contato com o prod</t>
+          <t>um livro de macrame em paguei com Pix. En</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -1026,29 +1018,29 @@
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Fiz uma compra pela empresa onde diz que tenho 7 dia para solicitar o cancelamento/reembolso de forma prática e ao solicitar o serviço eles mandam entrar em contato com o produtor e o mesmo não responde aos emails e mensagens enviadas pelos canais de comunicação e a plataforma CAKTO não está intervindo na situação e o prazo já vai esgotar e eles não resolvem a situação. Obs: o cancelamento/reembolso foi solicitado com menos de 24h após a adesão, já se passaram mais de 4 dias sem retorno. Empresa</t>
+          <t>Fiz uma compra de um livro de macrame em paguei com Pix. Enviaram um código para entrar, mas não consigo. Vem uma mensagem de token invalido. Quero uma resposta pf Erro ao acessar livro digital de macramê comprado via Pix, com mensagem de token inválido.</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/empresa-nao-resolve-cancelamentoreembolso-e-nao-intervem-na-situacao_9tJ1cPoKxiMdK6tR/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/erro-ao-acessar-livro-digital-de-macrame-comprado-via-pix-com-mensagem-de-token-invalido_MVEYCodphEJ69zx8/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>vavá academy</t>
+          <t>eles mandam entrar em contato com od</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Vavá Academy</t>
+          <t>eles mandam entrar em contato com o prod</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1058,7 +1050,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -1076,79 +1068,21 @@
         </is>
       </c>
       <c r="J6" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Realizei a compra de um produto da Vavá Academy por meio da plataforma Cakto, porém **não recebi o acesso à plataforma nem o produto adquirido**. Após a compra, tentei entrar em contato com o criador responsável por e-mail para solicitar o acesso e resolver a situação, mas **não obtive nenhuma resposta** até o momento. Ou seja, o pagamento foi realizado, mas o produto não foi disponibilizado e não estou conseguindo contato com o responsável. Diante disso, solicito o **reembolso integral do valor</t>
+          <t>Fiz uma compra pela empresa onde diz que tenho 7 dia para solicitar o cancelamento/reembolso de forma prática e ao solicitar o serviço eles mandam entrar em contato com o produtor e o mesmo não responde aos emails e mensagens enviadas pelos canais de comunicação e a plataforma CAKTO não está intervindo na situação e o prazo já vai esgotar e eles não resolvem a situação. Obs: o cancelamento/reembolso foi solicitado com menos de 24h após a adesão, já se passaram mais de 4 dias sem retorno. Empresa</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/produto-nao-entregue-e-criador-nao-responde-solicito-reembolso_605Q8ntQ-aQlegi3/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>grupo no telegram</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Grupo no Telegram</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Espionagem e rastreamento</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>R$ 143,68.</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>No final de julho, realizei a compra de um produto digital chamado "GRUPO NO TELEGRAM" através de um link gerado na plataforma Cakto. O vendedor se identifica como Kaique Santtos, cujo e-mail cadastrado e de contato é *****. A compra foi aprovada no meu cartão de crédito sob o código de pedido *****, no valor de R$ 143,68. Na minha fatura, a cobrança aparece exatamente como "CAKTO*GRUPO NO TELEGRAM". Durante a negociação no WhatsApp, o vendedor me informou que a entrega (a transferência de posse</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/editado-pelo-reclame-aqui-em-compra-de-produto-digital-processada-pela-cakto-com-editado-pelo-reclame-aqui-e-nao-entrega_HJtQooCkVBEfTtMB/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/empresa-nao-resolve-cancelamentoreembolso-e-nao-intervem-na-situacao_9tJ1cPoKxiMdK6tR/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:L6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1211,17 +1145,17 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>0</v>
@@ -1230,23 +1164,23 @@
         <v>0</v>
       </c>
       <c r="G2" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>0</v>
@@ -1255,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1265,10 +1199,10 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>1</v>
@@ -1280,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1294,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1714,7 +1648,7 @@
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1744,7 +1678,7 @@
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1774,33 +1708,33 @@
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>pagamento nao recebido cakto</t>
+          <t>mas eu n</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>plano freelancer imediato</t>
+          <t>pagamento nao recebido cakto</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C31" s="14" t="n">
@@ -1810,12 +1744,12 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>reembolso cakto dificuldade</t>
+          <t>plano freelancer imediato</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
@@ -1825,7 +1759,7 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>reembolso perfectpay recusa</t>
+          <t>reembolso cakto dificuldade</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -1840,22 +1774,22 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>spygram</t>
+          <t>reembolso perfectpay recusa</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>spygram</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -1864,37 +1798,67 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>stalkeia</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
+          <t>um curso e</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>um livro de macrame em paguei com pix. en</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
           <t>vavá academy</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C37" s="14" t="n">
-        <v>0</v>
+      <c r="C39" s="14" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -860,13 +860,9 @@
         </is>
       </c>
       <c r="J2" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" s="12" t="inlineStr">
-        <is>
-          <t>realizei o pagamento direto no aplicativo, que prometia te entregar informações privadas de qualquer conta no instagram. porém, depois que você faz o primeiro pagamento, você não consegue o que é prometido enquanto não pagar outros valores, e ainda ameaçam enviar um alerta para a conta que supostamente eles estão espionando. acabei fazendo diversos pagamentos (deixei o pdf em anexo), e no final das contas não tive acesso a nada, pois fiz o teste com outras contas no instagram e ele simplesmente</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="K2" s="12" t="inlineStr"/>
       <c r="L2" s="12" t="inlineStr">
         <is>
           <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa-do-e-solicitacao-de-reembolso-do-valor-pago_yID1cmkfVopy5OrZ/</t>
@@ -876,27 +872,27 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>converza.io</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>Converza.io</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Chatbots / Automação de mensagens</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -914,29 +910,29 @@
         </is>
       </c>
       <c r="J3" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="12" t="inlineStr"/>
       <c r="L3" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/editado-pelo-reclame-aqui_UeZdzzFsRKKhakiR/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/exijo-reembolso-servico-nao-funciona-e-suporte-nao-responde_OPi-rimJXtkjo2yB/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>mas eu n</t>
+          <t>comunidade vsa</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>mas eu n</t>
+          <t>COMUNIDADE VSA</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -946,7 +942,7 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Marketing / Comunidades de negócios</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -957,7 +953,11 @@
       <c r="G4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="12" t="inlineStr"/>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>R$ 248,89.</t>
+        </is>
+      </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -969,24 +969,24 @@
       <c r="K4" s="12" t="inlineStr"/>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/vendedor-nao-recebe-dinheiro-das-vendas-devido-a-analise-de-documentacao-demorada-e-suporte-lento_oW_Ar32UzJWou7Co/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-de-compra-com-erro-de-saldo-na-conta-do-vendedor_e5d-tH3gUGahNktM/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>um livro de macrame em paguei com pix. en</t>
+          <t>retrato da sua alma gêmea</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>um livro de macrame em paguei com Pix. En</t>
+          <t>Retrato da Sua Alma Gêmea</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Arte personalizada / IA generativa</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -1007,7 +1007,11 @@
       <c r="G5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="12" t="inlineStr"/>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>R$ 48,89</t>
+        </is>
+      </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -1016,31 +1020,27 @@
       <c r="J5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>Fiz uma compra de um livro de macrame em paguei com Pix. Enviaram um código para entrar, mas não consigo. Vem uma mensagem de token invalido. Quero uma resposta pf Erro ao acessar livro digital de macramê comprado via Pix, com mensagem de token inválido.</t>
-        </is>
-      </c>
+      <c r="K5" s="12" t="inlineStr"/>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/erro-ao-acessar-livro-digital-de-macrame-comprado-via-pix-com-mensagem-de-token-invalido_MVEYCodphEJ69zx8/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/editado-pelo-reclame-aqui-e-solicitacao-de-estorno-para-produto-retrato-da-sua-alma-gemea_H8ihRLGIEQMZ9WSb/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>eles mandam entrar em contato com od</t>
+          <t>pack canva happy hour</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>eles mandam entrar em contato com o prod</t>
+          <t>Pack Canva Happy Hour</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>PLR / Produtos digitais para revenda</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -1061,23 +1061,23 @@
       <c r="G6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="12" t="inlineStr"/>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>R$ 15,15</t>
+        </is>
+      </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
       <c r="J6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>Fiz uma compra pela empresa onde diz que tenho 7 dia para solicitar o cancelamento/reembolso de forma prática e ao solicitar o serviço eles mandam entrar em contato com o produtor e o mesmo não responde aos emails e mensagens enviadas pelos canais de comunicação e a plataforma CAKTO não está intervindo na situação e o prazo já vai esgotar e eles não resolvem a situação. Obs: o cancelamento/reembolso foi solicitado com menos de 24h após a adesão, já se passaram mais de 4 dias sem retorno. Empresa</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K6" s="12" t="inlineStr"/>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/empresa-nao-resolve-cancelamentoreembolso-e-nao-intervem-na-situacao_9tJ1cPoKxiMdK6tR/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-de-cursos-online-apos-arrependimento-de-compra_-CZPnDHntp_r19_O/</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1145,17 +1145,17 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="14" t="n">
         <v>0</v>
-      </c>
-      <c r="D2" s="14" t="n">
-        <v>3</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>0</v>
@@ -1164,13 +1164,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Chatbots / Automação de mensagens</t>
         </is>
       </c>
       <c r="B3" s="14" t="n">
@@ -1195,17 +1195,17 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Marketing / Comunidades de negócios</t>
         </is>
       </c>
       <c r="B4" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="14" t="n">
         <v>0</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>1</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>0</v>
@@ -1214,6 +1214,56 @@
         <v>0</v>
       </c>
       <c r="G4" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Arte personalizada / IA generativa</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>PLR / Produtos digitais para revenda</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1228,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1609,37 +1659,37 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>conta digital cakto validacao falha</t>
+          <t>comunidade vsa</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>curso online</t>
+          <t>conta digital cakto validacao falha</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>eles mandam entrar em contato com od</t>
+          <t>converza.io</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
@@ -1648,28 +1698,28 @@
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>freelancer imediato</t>
+          <t>curso online</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>grupo no telegram</t>
+          <t>eles mandam entrar em contato com od</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
@@ -1678,13 +1728,13 @@
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>hqflix</t>
+          <t>freelancer imediato</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
@@ -1693,13 +1743,13 @@
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>lumi ai</t>
+          <t>grupo no telegram</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -1714,27 +1764,27 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>mas eu n</t>
+          <t>hqflix</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>pagamento nao recebido cakto</t>
+          <t>lumi ai</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C31" s="14" t="n">
@@ -1744,7 +1794,7 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>plano freelancer imediato</t>
+          <t>mas eu n</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -1759,22 +1809,22 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>reembolso cakto dificuldade</t>
+          <t>pack canva happy hour</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>reembolso perfectpay recusa</t>
+          <t>pagamento nao recebido cakto</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
@@ -1789,42 +1839,42 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>spygram</t>
+          <t>plano freelancer imediato</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>reembolso cakto dificuldade</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>reembolso perfectpay recusa</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C37" s="14" t="n">
@@ -1834,7 +1884,7 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>um livro de macrame em paguei com pix. en</t>
+          <t>retrato da sua alma gêmea</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
@@ -1849,15 +1899,75 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
+          <t>spygram</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>stalkeia</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>um curso e</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>um livro de macrame em paguei com pix. en</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
           <t>vavá academy</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C39" s="14" t="n">
+      <c r="C43" s="14" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo por nicho'!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Varredura'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="J2" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2" s="12" t="inlineStr"/>
       <c r="L2" s="12" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="J3" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="12" t="inlineStr"/>
       <c r="L3" s="12" t="inlineStr">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="J4" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="12" t="inlineStr"/>
       <c r="L4" s="12" t="inlineStr">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="12" t="inlineStr"/>
       <c r="L5" s="12" t="inlineStr">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="J6" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="12" t="inlineStr"/>
       <c r="L6" s="12" t="inlineStr">
@@ -1081,8 +1081,274 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>fica saindo e entrando sozinho</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>fica saindo e entrando sozinho</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="12" t="inlineStr"/>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="12" t="inlineStr"/>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>método atlas</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Método Atlas</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="12" t="inlineStr"/>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desativaram as contas ,já procurei uma advogada e delegacia pra denunciar. Não caiam é [Editado pelo Reclame Aqui] RA Ads</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/compra-do-metodo-atlas-nao-cumpre-o-prometido-e-suporte-desativado_wzci0DCEtGCFBRc6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>interactive live</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Interactive Live</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="12" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>Comprei o produto "Interactive Live" através da plataforma Perfect Pay, que atuou como processadora de pagamento da venda. O produto recebido não correspondeu ao que foi anunciado/esperado, e eu solicitei o cancelamento/reembolso ainda dentro do prazo de garantia de 7 dias previsto no site/checkout, que também é assegurado pelo direito de arrependimento do art. 49 do Código de Defesa do Consumidor para compras feitas fora do estabelecimento comercial (como é o caso de compras online). Esse prazo</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-e-prazo-expirado-devido-a-burocracia-da-perfect-pay_wFj48yi7DgllZO-Z/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>low ticket do zero 2.0 no dia 30</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Low Ticket do Zero 2.0 no dia 30</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="12" t="inlineStr"/>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor. Não respondida CAKTO PAY Rio de Janeiro - RJ 31/08/2026 às 17:20</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>um aplicativo</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>um aplicativo</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="12" t="inlineStr"/>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo suporte da plataforma e não me respondem, foi uma compra de +- 840 reais Quero o reembolso da minha compra: Dados da compra: Poxa, vou te ajudar a resolver isso! Me informe: Qual e-mail você usou na compra?</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L6"/>
+  <autoFilter ref="A1:L11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1093,7 +1359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1149,13 +1415,13 @@
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>0</v>
@@ -1164,23 +1430,23 @@
         <v>0</v>
       </c>
       <c r="G2" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Chatbots / Automação de mensagens</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>0</v>
@@ -1189,13 +1455,13 @@
         <v>0</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>Marketing / Comunidades de negócios</t>
+          <t>Chatbots / Automação de mensagens</t>
         </is>
       </c>
       <c r="B4" s="14" t="n">
@@ -1220,7 +1486,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Arte personalizada / IA generativa</t>
+          <t>Marketing / Comunidades de negócios</t>
         </is>
       </c>
       <c r="B5" s="14" t="n">
@@ -1245,25 +1511,100 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
+          <t>Arte personalizada / IA generativa</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
           <t>PLR / Produtos digitais para revenda</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1278,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1668,7 +2009,7 @@
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1698,7 +2039,7 @@
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1734,27 +2075,27 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>freelancer imediato</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>grupo no telegram</t>
+          <t>freelancer imediato</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
@@ -1764,37 +2105,37 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>hqflix</t>
+          <t>grupo no telegram</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>lumi ai</t>
+          <t>hqflix</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>mas eu n</t>
+          <t>interactive live</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -1803,13 +2144,13 @@
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>pack canva happy hour</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -1824,12 +2165,12 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>pagamento nao recebido cakto</t>
+          <t>lumi ai</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
@@ -1839,7 +2180,7 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>plano freelancer imediato</t>
+          <t>mas eu n</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -1854,27 +2195,27 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>reembolso cakto dificuldade</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>reembolso perfectpay recusa</t>
+          <t>pack canva happy hour</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C37" s="14" t="n">
@@ -1884,67 +2225,67 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>retrato da sua alma gêmea</t>
+          <t>pagamento nao recebido cakto</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C38" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>spygram</t>
+          <t>plano freelancer imediato</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>reembolso cakto dificuldade</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>reembolso perfectpay recusa</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>um livro de macrame em paguei com pix. en</t>
+          <t>retrato da sua alma gêmea</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
@@ -1959,15 +2300,90 @@
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
+          <t>spygram</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>stalkeia</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>um aplicativo</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>um curso e</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>um livro de macrame em paguei com pix. en</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
           <t>vavá academy</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo por nicho'!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Varredura'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Achados'!$A$1:$L$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -818,17 +818,17 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>Stalkeia</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
@@ -847,37 +847,33 @@
         </is>
       </c>
       <c r="G2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="12" t="inlineStr"/>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>R$ 47</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="J2" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="K2" s="12" t="inlineStr"/>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa-do-e-solicitacao-de-reembolso-do-valor-pago_yID1cmkfVopy5OrZ/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>converza.io</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Converza.io</t>
+          <t>Método Atlas</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -887,12 +883,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Chatbots / Automação de mensagens</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -912,37 +908,41 @@
       <c r="J3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="12" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desativaram as contas ,já procurei uma advogada e delegacia pra denunciar. Não caiam é [Editado pelo Reclame Aqui] RA Ads</t>
+        </is>
+      </c>
       <c r="L3" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/exijo-reembolso-servico-nao-funciona-e-suporte-nao-responde_OPi-rimJXtkjo2yB/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/compra-do-metodo-atlas-nao-cumpre-o-prometido-e-suporte-desativado_wzci0DCEtGCFBRc6/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>comunidade vsa</t>
+          <t>interactive live</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>COMUNIDADE VSA</t>
+          <t>Interactive Live</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Marketing / Comunidades de negócios</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -953,11 +953,7 @@
       <c r="G4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>R$ 248,89.</t>
-        </is>
-      </c>
+      <c r="H4" s="12" t="inlineStr"/>
       <c r="I4" s="12" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -966,27 +962,31 @@
       <c r="J4" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="12" t="inlineStr"/>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>Comprei o produto "Interactive Live" através da plataforma Perfect Pay, que atuou como processadora de pagamento da venda. O produto recebido não correspondeu ao que foi anunciado/esperado, e eu solicitei o cancelamento/reembolso ainda dentro do prazo de garantia de 7 dias previsto no site/checkout, que também é assegurado pelo direito de arrependimento do art. 49 do Código de Defesa do Consumidor para compras feitas fora do estabelecimento comercial (como é o caso de compras online). Esse prazo</t>
+        </is>
+      </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-de-compra-com-erro-de-saldo-na-conta-do-vendedor_e5d-tH3gUGahNktM/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-e-prazo-expirado-devido-a-burocracia-da-perfect-pay_wFj48yi7DgllZO-Z/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>retrato da sua alma gêmea</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Retrato da Sua Alma Gêmea</t>
+          <t>Low Ticket do Zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Arte personalizada / IA generativa</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -1007,11 +1007,7 @@
       <c r="G5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>R$ 48,89</t>
-        </is>
-      </c>
+      <c r="H5" s="12" t="inlineStr"/>
       <c r="I5" s="12" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -1020,27 +1016,31 @@
       <c r="J5" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="12" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor. Resolvido CAKTO PAY Rio de Janeiro - RJ 31/08/2026 às 17:20</t>
+        </is>
+      </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/editado-pelo-reclame-aqui-e-solicitacao-de-estorno-para-produto-retrato-da-sua-alma-gemea_H8ihRLGIEQMZ9WSb/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>pack canva happy hour</t>
+          <t>um aplicativo</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Pack Canva Happy Hour</t>
+          <t>um aplicativo</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>PLR / Produtos digitais para revenda</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -1061,11 +1061,7 @@
       <c r="G6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>R$ 15,15</t>
-        </is>
-      </c>
+      <c r="H6" s="12" t="inlineStr"/>
       <c r="I6" s="12" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -1074,281 +1070,19 @@
       <c r="J6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="12" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo suporte da plataforma e não me respondem, foi uma compra de +- 840 reais Quero o reembolso da minha compra: Dados da compra: Poxa, vou te ajudar a resolver isso! Me informe: Qual e-mail você usou na compra?</t>
+        </is>
+      </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-de-cursos-online-apos-arrependimento-de-compra_-CZPnDHntp_r19_O/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>fica saindo e entrando sozinho</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>fica saindo e entrando sozinho</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>PerfectPay</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="12" t="inlineStr"/>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>método atlas</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Método Atlas</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>marca</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>PerfectPay</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Educação e consultoria</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desativaram as contas ,já procurei uma advogada e delegacia pra denunciar. Não caiam é [Editado pelo Reclame Aqui] RA Ads</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/compra-do-metodo-atlas-nao-cumpre-o-prometido-e-suporte-desativado_wzci0DCEtGCFBRc6/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>interactive live</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Interactive Live</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>PerfectPay</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Espionagem e rastreamento</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>Comprei o produto "Interactive Live" através da plataforma Perfect Pay, que atuou como processadora de pagamento da venda. O produto recebido não correspondeu ao que foi anunciado/esperado, e eu solicitei o cancelamento/reembolso ainda dentro do prazo de garantia de 7 dias previsto no site/checkout, que também é assegurado pelo direito de arrependimento do art. 49 do Código de Defesa do Consumidor para compras feitas fora do estabelecimento comercial (como é o caso de compras online). Esse prazo</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-e-prazo-expirado-devido-a-burocracia-da-perfect-pay_wFj48yi7DgllZO-Z/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Low Ticket do Zero 2.0 no dia 30</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor. Não respondida CAKTO PAY Rio de Janeiro - RJ 31/08/2026 às 17:20</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>um aplicativo</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>um aplicativo</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Infoprodutos - suporte e reembolso</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo suporte da plataforma e não me respondem, foi uma compra de +- 840 reais Quero o reembolso da minha compra: Dados da compra: Poxa, vou te ajudar a resolver isso! Me informe: Qual e-mail você usou na compra?</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
           <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:L6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1359,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1411,17 +1145,17 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="B2" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C2" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>0</v>
@@ -1436,17 +1170,17 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="14" t="n">
         <v>0</v>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>2</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>0</v>
@@ -1455,23 +1189,23 @@
         <v>0</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>Chatbots / Automação de mensagens</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="B4" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>0</v>
@@ -1486,17 +1220,17 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Marketing / Comunidades de negócios</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="B5" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="14" t="n">
         <v>0</v>
@@ -1505,106 +1239,6 @@
         <v>0</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Arte personalizada / IA generativa</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>PLR / Produtos digitais para revenda</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Educação e consultoria</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Infoprodutos - suporte e reembolso</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2009,7 +1643,7 @@
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2039,7 +1673,7 @@
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2084,7 +1718,7 @@
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2144,7 +1778,7 @@
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2159,7 +1793,7 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2204,7 +1838,7 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2219,7 +1853,7 @@
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2294,7 +1928,7 @@
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2324,7 +1958,7 @@
         </is>
       </c>
       <c r="C44" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -2339,7 +1973,7 @@
         </is>
       </c>
       <c r="C45" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -533,7 +533,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / trabalho remoto</t>
+          <t>Educação / Marketing digital e low ticket</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -565,11 +565,11 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Reembolso solicitado por propaganda enganosa sobre suporte individual no curso Fábrica de Low Ticket  Resolvido  CAKTO PAY  Cansanção - BA  01/09/2026 às 08:18  ID: 257896487  Olá,  Solicito o reembolso da compra da Fábrica de</t>
+          <t>Adquiri o curso com base na promessa apresentada pelo produtor de que haveria suporte individual. Porém, após entrar no grupo de WhatsApp, me deparei com uma discussão entre outros alunos que estavam reclamando justamente sobre essa questão. Na conversa, um dos administradores informou que a estratégia havia sido alterada e que o suporte agora seria realizado de forma coletiva pelo grupo. Eu não fui comunicado previamente sobre essa mudança e essa não foi a condição pela qual adquiri o curso. Co</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -581,17 +581,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Método Atlas</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -621,26 +621,22 @@
       <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Compra do Método Atlas não cumpre o prometido e suporte desativado  Respondida  PerfectPay  Belém - PA  31/08/2026 às 15:21  ID: 257839151  Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com supor</t>
-        </is>
-      </c>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/compra-do-metodo-atlas-nao-cumpre-o-prometido-e-suporte-desativado_wzci0DCEtGCFBRc6/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Interactive Live</t>
+          <t>Método Atlas</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -655,7 +651,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -673,43 +669,43 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Reembolso negado e prazo expirado devido à burocracia da Perfect Pay  Respondida  PerfectPay  Mesquita - RJ  31/08/2026 às 12:25  ID: 257816301  Comprei o produto "Interactive Live" através da plataforma Perfect Pay, que atuou</t>
+          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desativaram as contas ,já procurei uma advogada e delegacia pra denunciar. Não caiam é [Editado pelo Reclame Aqui] RA Ads</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-e-prazo-expirado-devido-a-burocracia-da-perfect-pay_wFj48yi7DgllZO-Z/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/compra-do-metodo-atlas-nao-cumpre-o-prometido-e-suporte-desativado_wzci0DCEtGCFBRc6/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>low ticket do zero</t>
+          <t>interactive live</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Low Ticket do Zero 2.0</t>
+          <t>Interactive Live</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / trabalho remoto</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -727,33 +723,33 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor.  Resolvido  CAKTO PAY  Rio de Janeiro - RJ  31/08/2026 às 17:20  ID: 257854207  Realizei a compra do produto Low Ticket do Zero 2.0 no dia</t>
+          <t>Comprei o produto "Interactive Live" através da plataforma Perfect Pay, que atuou como processadora de pagamento da venda. O produto recebido não correspondeu ao que foi anunciado/esperado, e eu solicitei o cancelamento/reembolso ainda dentro do prazo de garantia de 7 dias previsto no site/checkout, que também é assegurado pelo direito de arrependimento do art. 49 do Código de Defesa do Consumidor para compras feitas fora do estabelecimento comercial (como é o caso de compras online). Esse prazo</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-e-prazo-expirado-devido-a-burocracia-da-perfect-pay_wFj48yi7DgllZO-Z/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>cloakeuai</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cloakeuai</t>
+          <t>Low Ticket do Zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -763,7 +759,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de marketing / Cloaker</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -785,39 +781,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Reclamação sobre aplicativo não funcional e falta de resposta do suporte para reembolso.  Não respondida  CAKTO PAY  São Sebastião do Paraíso - MG  31/08/2026 às 15:39  ID: 257841583  Fiz uma compra de um aplicativo, porém o me</t>
+          <t>Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor. Resolvido CAKTO PAY Rio de Janeiro - RJ 31/08/2026 às 17:20</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>zap radar</t>
+          <t>cloakeuai</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ZAP Radar</t>
+          <t>Cloakeuai</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de IA / Cloaking</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -835,43 +831,43 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Solicitação de estorno de compra no site ZAP Radar por não recebimento de relatório.  Respondida  PerfectPay  Niterói - RJ  31/08/2026 às 22:22  ID: 257882275  Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pel</t>
+          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo suporte da plataforma e não me respondem, foi uma compra de +- 840 reais Quero o reembolso da minha compra: Dados da compra: Poxa, vou te ajudar a resolver isso! Me informe: Qual e-mail você usou na compra?</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>apostila de psicologia025</t>
+          <t>códigos lucrativos</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Apostila de Psicologia 2025</t>
+          <t>Códigos Lucrativos</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -893,17 +889,839 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Apostila de Psicologia 2025 não abre e cliente não obtém retorno sobre compra online.  Respondida  CAKTO PAY  Sorocaba - SP  01/09/2026 às 10:19  ID: 257909223  Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um com</t>
+          <t>Comprei dois aplicativos codigos lucrativos e opinipix pela perfect pay,mas eles são [Editado pelo Reclame Aqui] . [Editado pelo Reclame Aqui]. Quero meu dinheiro de volta. Resposta da Empresa 31/01/2025 às 17:31</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>aristocracy negócios digitais</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Aristocracy Negócios Digitais</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Produtos digitais variados / Assinatura vitalícia</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/acesso-negado-a-produtos-com-assinatura-vitalicia-e-namorada-customizada-nao-funciona_VUCzPEy-WEHTKJWB/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>zap radar</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ZAP Radar</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de espionagem / WhatsApp</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o estorno do valor pago. RA Ads</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>apostila de psicologia 2025</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Apostila de Psicologia 2025</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Educação / Concursos e certificações</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico. Já entrei em contato por e-mail, por chat mais não consigo retorno. Já enviei os comprovantes de pagamentos de cada compra, mais não obtenho resposta. Esse material é para concurso, porém a Apostila não abre. Quando clico dá que já foi concluída sem ao menos eu ler. Comprei o material porque preciso, e hoje já entrei e não abre. Gostaria que resolvessem isso. Edna Carvalho</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>https://www.reclameaqui.com.br/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>comunidade knights club</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>COMUNIDADE KNIGHTS CLUB</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Comunidades / Mentoria de negócios</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,99,</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>No dia 21/08/2026, realizei a compra da COMUNIDADE KNIGHTS CLUB, no valor de R$ 67,99, através da plataforma de pagamentos Cakto, com pagamento realizado via Pix. Após a compra, descobri que a ferramenta de inteligência artificial adquirida é destinada ao uso em computador. Essa informação não estava suficientemente clara para mim no momento da compra. Como não possuo computador, entrei em contato com o suporte para saber se seria possível utilizar a ferramenta pelo celular e fui informado de qu</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-de-compra-via-pix-nao-realizado-apos-solicitacao-dentro-do-prazo-legal_w1bmesmQpVhI5h0M/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>validação cadastral: em análise</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Validação cadastral: Em análise</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>R$ 38,09</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Olá, equipe da Cakto.Estou com um problema sério em relação à validação dos meus documentos na plataforma. Realizei o envio do meu documento digital no dia 18 de agosto, e desde então o status permanece travado como "Validação cadastral: Em análise".Já se passaram semanas e o processo não avança. Por conta dessa demora na análise, não consigo realizar movimentações na minha conta. Atualmente, possuo um saldo de R$ 38,09 categorizado como "Disponível para transferir", mas a opção de "Efetuar Saqu</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/demora-na-validacao-de-documentos-impede-movimentacao-e-saque-de-valores-na-plataforma-cakto_AxgK77MKxCN0UISD/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>continua ativo</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>continua ativo</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>O produto continua ativo,sendo que não estou usando o serviço. RA Ads</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/cancelamento-de-assinatura-nao-realizado-e-cobranca-indevida-persistente_4mA_vDyxabA5d2h8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>manuscrito dos milagres</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Manuscrito dos Milagres</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>R$ 99,00</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra do produto "Manuscrito dos Milagres" no valor de 99 reais através da plataforma de vocês. Trata-se de um [Editado pelo Reclame Aqui] que usa inteligência artificial com a imagem do ator Jonathan Roumie. O conteúdo não foi entregue e não abre. Como estou dentro do prazo legal de 7 dias previsto pelo Artigo 49 do Código de Defesa do Consumidor, exijo o cancelamento imediato e o estorno integral do valor Comprei um produto através da perfectpay Curso(s): Manuscrito dos Milagres Ap</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-manuscrito-dos-milagres-nao-entregue-e-solicitacao-de-estorno_YM7HDxei_9htWhyn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,89</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o produto Youclone no dia 28/08, no pix. Quando fui entrar no curso, não abre a área de membros e não consigo assistir o curso. Na minha área de membros só tem um curso que eu comprei faz tempo. Detalhes do Pedido Pedido: ***** Data: 28/08/2026</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>na ultima quarta feira</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>na ultima quarta feira</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Boa noite. Fiz a compra de um produto na ultima quarta feira (26/08/20226) e até essa data eu não recebi o produto. Recebi o e-mail de confirmação do pagamento e um acesso pra fazer o download do material, mas não dá certo. Pra todo lugar que eles me enviam não dá certo. Falo com o pessoal do suporte e eles me deixam sem respostas. Só começam o atendimento. Pedi reembolso, também não dá certo. me mandaram 10 códigos de confirmação e com um segundo diz que expirou. tanto por E-mail quanto por cel</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/produto-nao-recebido-e-dificuldade-de-acesso-ao-material-digital-com-falha-no-reembolso-e-suporte-ineficaz_iOzRmbylQ4neQezT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>de seguran</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>de seguran</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-reembolso-de-pedido-com-codigo-de-transacao_poCcMMKbZVAkXZx9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>e a plataforma deveria no m</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>e a plataforma deveria no m</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra nessa plataforma e não consigo pedir o reembolso pois a plataforma alega não vender produto. Quero o reembolso pois não gostei do produto e a plataforma deveria no mínimo disponibilizar essa função no site. Segundo a plataforma eu tenho que entrar em contato com o responsável do produto, como irei pedir o reembolso pois o dono do produto não responde. ***** Numero do pedido da minha compra  Reembolso negado por plataforma que alega não vender o produto.</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-por-plataforma-que-alega-nao-vender-o-produto_S-syATG5Z4eLNeZI/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>stalkeia</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Stalkeia</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>R$ 401,40.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>O produto prometia acesso a contas e mensagens do Instagram, mas na verdade entrega apenas um aplicativo que simula a interface do Instagram e cria conversas artificiais. Ou seja, trata-se de um serviço [Editado pelo Reclame Aqui], que não entrega o que anuncia. Eu testei com dois perfis diferentes e as mensagens são as mesmas, ou seja, [Editado pelo Reclame Aqui] e [Editado pelo Reclame Aqui]. Além disso, após um primeiro pagamento a plataforma vai nos induzindo a efetuar outras compras para co</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/servico-editado-pelo-reclame-aqui-da-via-perfect-pay-com-promessa-editado-pelo-reclame-aqui_XI7_jZmAIuhQa5In/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>de postagem autom</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>de postagem autom</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, Instagram e tiktok. Porém dentro da plataforma , fui informada que teria que pagar mais um valor para integração com as plataformas, informaram que esse valor é pagamento único, para as plataformas liberarem a integração ( não fica nada com eles). Como meu intuito é as postagens automáticas, comprei. Enviei o comprovante, como solicitado e aguardei o prazo para eles , entrar</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por bastante tempo e disse ter efetuado o reembolso, coisa que eu não sei se aconteceu ou não, por que isso foi antes de ontem e lá na cakto ainda está como "pago" e não algo como "reembolso em andamento" ou coisa assim! Me disseram na última resposta que iam me mandar mensagem no contato cadastrado no reclame aqui, coisa que ainda não fizeram e o prazo pra reembolso é até am</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>adquirido teria condi</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>adquirido teria condi</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Venho solicitar a contestação de uma compra realizada referente à contratação de uma estrutura montada para geração de retorno financeiro. A contratação foi realizada acreditando que o serviço/produto adquirido teria condições de funcionar conforme apresentado pelos responsáveis pela estrutura. O problema é que, após a contratação e a montagem das estruturas, o resultado esperado não aconteceu. Além do valor já pago pela aquisição do produto/estrutura, posteriormente fui informado de que seria n</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L8"/>
+  <autoFilter ref="A1:L23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -914,7 +1732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -966,17 +1784,17 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / trabalho remoto</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -985,24 +1803,24 @@
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
@@ -1010,23 +1828,23 @@
         <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
@@ -1041,17 +1859,17 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ferramentas de marketing / Cloaker</t>
+          <t>Educação / Marketing digital e low ticket</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
@@ -1060,6 +1878,206 @@
         <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Cloaking</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Produtos digitais variados / Assinatura vitalícia</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Ferramentas de espionagem / WhatsApp</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Educação / Concursos e certificações</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Comunidades / Mentoria de negócios</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1074,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1102,7 +2120,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>apostila de psicologia025</t>
+          <t>adquirido teria condi</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -1117,7 +2135,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>cloakeuai</t>
+          <t>apostila de psicologia 2025</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1132,7 +2150,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>apostila de psicologia025</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1141,13 +2159,13 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>aristocracy negócios digitais</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1162,7 +2180,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero</t>
+          <t>cloakeuai</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1171,13 +2189,13 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>comunidade knights club</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1192,16 +2210,271 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>continua ativo</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>códigos lucrativos</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>de postagem autom</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>de seguran</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>e a plataforma deveria no m</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>fica saindo e entrando sozinho</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>fábrica de low ticket</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>interactive live</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>low ticket do zero</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>low ticket do zero 2.0 no dia 30</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>manuscrito dos milagres</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>método atlas</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>na ultima quarta feira</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>stalkeia</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>validação cadastral: em análise</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>zap radar</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -581,12 +581,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>on line rj comercio varejista de acessorios ltda</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>On Line Rj Comercio Varejista De Acessorios Ltda</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -612,36 +612,40 @@
       <c r="G3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-de-assinatura-tokfy-via-pix-devido-a-plano-incorreto-e-falha-no-login-para-cancelamento_lwKWxoGQVq5QbJLn/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Método Atlas</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -651,7 +655,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -671,31 +675,27 @@
       <c r="J4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desativaram as contas ,já procurei uma advogada e delegacia pra denunciar. Não caiam é [Editado pelo Reclame Aqui] RA Ads</t>
-        </is>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/compra-do-metodo-atlas-nao-cumpre-o-prometido-e-suporte-desativado_wzci0DCEtGCFBRc6/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Interactive Live</t>
+          <t>Método Atlas</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -723,28 +723,28 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Comprei o produto "Interactive Live" através da plataforma Perfect Pay, que atuou como processadora de pagamento da venda. O produto recebido não correspondeu ao que foi anunciado/esperado, e eu solicitei o cancelamento/reembolso ainda dentro do prazo de garantia de 7 dias previsto no site/checkout, que também é assegurado pelo direito de arrependimento do art. 49 do Código de Defesa do Consumidor para compras feitas fora do estabelecimento comercial (como é o caso de compras online). Esse prazo</t>
+          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desativaram as contas ,já procurei uma advogada e delegacia pra denunciar. Não caiam é [Editado pelo Reclame Aqui] RA Ads</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-e-prazo-expirado-devido-a-burocracia-da-perfect-pay_wFj48yi7DgllZO-Z/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/compra-do-metodo-atlas-nao-cumpre-o-prometido-e-suporte-desativado_wzci0DCEtGCFBRc6/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
+          <t>interactive live</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Low Ticket do Zero 2.0 no dia 30</t>
+          <t>Interactive Live</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -777,28 +777,28 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor. Resolvido CAKTO PAY Rio de Janeiro - RJ 31/08/2026 às 17:20</t>
+          <t>Comprei o produto "Interactive Live" através da plataforma Perfect Pay, que atuou como processadora de pagamento da venda. O produto recebido não correspondeu ao que foi anunciado/esperado, e eu solicitei o cancelamento/reembolso ainda dentro do prazo de garantia de 7 dias previsto no site/checkout, que também é assegurado pelo direito de arrependimento do art. 49 do Código de Defesa do Consumidor para compras feitas fora do estabelecimento comercial (como é o caso de compras online). Esse prazo</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-e-prazo-expirado-devido-a-burocracia-da-perfect-pay_wFj48yi7DgllZO-Z/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>cloakeuai</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Cloakeuai</t>
+          <t>Low Ticket do Zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Cloaking</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -835,24 +835,24 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo suporte da plataforma e não me respondem, foi uma compra de +- 840 reais Quero o reembolso da minha compra: Dados da compra: Poxa, vou te ajudar a resolver isso! Me informe: Qual e-mail você usou na compra?</t>
+          <t>Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor. Resolvido CAKTO PAY Rio de Janeiro - RJ 31/08/2026 às 17:20</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>códigos lucrativos</t>
+          <t>cloakeuai</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Códigos Lucrativos</t>
+          <t>Cloakeuai</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+          <t>Ferramentas de IA / Cloaking</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -885,28 +885,28 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Comprei dois aplicativos codigos lucrativos e opinipix pela perfect pay,mas eles são [Editado pelo Reclame Aqui] . [Editado pelo Reclame Aqui]. Quero meu dinheiro de volta. Resposta da Empresa 31/01/2025 às 17:31</t>
+          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo suporte da plataforma e não me respondem, foi uma compra de +- 840 reais Quero o reembolso da minha compra: Dados da compra: Poxa, vou te ajudar a resolver isso! Me informe: Qual e-mail você usou na compra?</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>aristocracy negócios digitais</t>
+          <t>códigos lucrativos</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Aristocracy Negócios Digitais</t>
+          <t>Códigos Lucrativos</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Produtos digitais variados / Assinatura vitalícia</t>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -939,24 +939,28 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Comprei dois aplicativos codigos lucrativos e opinipix pela perfect pay,mas eles são [Editado pelo Reclame Aqui] . [Editado pelo Reclame Aqui]. Quero meu dinheiro de volta. Resposta da Empresa 31/01/2025 às 17:31</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/acesso-negado-a-produtos-com-assinatura-vitalicia-e-namorada-customizada-nao-funciona_VUCzPEy-WEHTKJWB/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>zap radar</t>
+          <t>aristocracy negócios digitais</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ZAP Radar</t>
+          <t>Aristocracy Negócios Digitais</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -971,7 +975,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de espionagem / WhatsApp</t>
+          <t>Produtos digitais variados / Assinatura vitalícia</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -991,26 +995,22 @@
       <c r="J10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o estorno do valor pago. RA Ads</t>
-        </is>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/acesso-negado-a-produtos-com-assinatura-vitalicia-e-namorada-customizada-nao-funciona_VUCzPEy-WEHTKJWB/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>apostila de psicologia 2025</t>
+          <t>zap radar</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Apostila de Psicologia 2025</t>
+          <t>ZAP Radar</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Educação / Concursos e certificações</t>
+          <t>Ferramentas de espionagem / WhatsApp</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico. Já entrei em contato por e-mail, por chat mais não consigo retorno. Já enviei os comprovantes de pagamentos de cada compra, mais não obtenho resposta. Esse material é para concurso, porém a Apostila não abre. Quando clico dá que já foi concluída sem ao menos eu ler. Comprei o material porque preciso, e hoje já entrei e não abre. Gostaria que resolvessem isso. Edna Carvalho</t>
+          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o estorno do valor pago. RA Ads</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>comunidade knights club</t>
+          <t>apostila de psicologia 2025</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>COMUNIDADE KNIGHTS CLUB</t>
+          <t>Apostila de Psicologia 2025</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Comunidades / Mentoria de negócios</t>
+          <t>Educação / Concursos e certificações</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,39 +1090,35 @@
       <c r="G12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>R$ 67,99,</t>
-        </is>
-      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>No dia 21/08/2026, realizei a compra da COMUNIDADE KNIGHTS CLUB, no valor de R$ 67,99, através da plataforma de pagamentos Cakto, com pagamento realizado via Pix. Após a compra, descobri que a ferramenta de inteligência artificial adquirida é destinada ao uso em computador. Essa informação não estava suficientemente clara para mim no momento da compra. Como não possuo computador, entrei em contato com o suporte para saber se seria possível utilizar a ferramenta pelo celular e fui informado de qu</t>
+          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico. Já entrei em contato por e-mail, por chat mais não consigo retorno. Já enviei os comprovantes de pagamentos de cada compra, mais não obtenho resposta. Esse material é para concurso, porém a Apostila não abre. Quando clico dá que já foi concluída sem ao menos eu ler. Comprei o material porque preciso, e hoje já entrei e não abre. Gostaria que resolvessem isso. Edna Carvalho</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-de-compra-via-pix-nao-realizado-apos-solicitacao-dentro-do-prazo-legal_w1bmesmQpVhI5h0M/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>validação cadastral: em análise</t>
+          <t>comunidade knights club</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Validação cadastral: Em análise</t>
+          <t>COMUNIDADE KNIGHTS CLUB</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1137,7 +1133,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Comunidades / Mentoria de negócios</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1150,7 +1146,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>R$ 38,09</t>
+          <t>R$ 67,99,</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1159,28 +1155,28 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Olá, equipe da Cakto.Estou com um problema sério em relação à validação dos meus documentos na plataforma. Realizei o envio do meu documento digital no dia 18 de agosto, e desde então o status permanece travado como "Validação cadastral: Em análise".Já se passaram semanas e o processo não avança. Por conta dessa demora na análise, não consigo realizar movimentações na minha conta. Atualmente, possuo um saldo de R$ 38,09 categorizado como "Disponível para transferir", mas a opção de "Efetuar Saqu</t>
+          <t>No dia 21/08/2026, realizei a compra da COMUNIDADE KNIGHTS CLUB, no valor de R$ 67,99, através da plataforma de pagamentos Cakto, com pagamento realizado via Pix. Após a compra, descobri que a ferramenta de inteligência artificial adquirida é destinada ao uso em computador. Essa informação não estava suficientemente clara para mim no momento da compra. Como não possuo computador, entrei em contato com o suporte para saber se seria possível utilizar a ferramenta pelo celular e fui informado de qu</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/demora-na-validacao-de-documentos-impede-movimentacao-e-saque-de-valores-na-plataforma-cakto_AxgK77MKxCN0UISD/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-de-compra-via-pix-nao-realizado-apos-solicitacao-dentro-do-prazo-legal_w1bmesmQpVhI5h0M/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>continua ativo</t>
+          <t>validação cadastral: em análise</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>continua ativo</t>
+          <t>Validação cadastral: Em análise</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1195,7 +1191,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1206,35 +1202,39 @@
       <c r="G14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>R$ 38,09</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>O produto continua ativo,sendo que não estou usando o serviço. RA Ads</t>
+          <t>Olá, equipe da Cakto.Estou com um problema sério em relação à validação dos meus documentos na plataforma. Realizei o envio do meu documento digital no dia 18 de agosto, e desde então o status permanece travado como "Validação cadastral: Em análise".Já se passaram semanas e o processo não avança. Por conta dessa demora na análise, não consigo realizar movimentações na minha conta. Atualmente, possuo um saldo de R$ 38,09 categorizado como "Disponível para transferir", mas a opção de "Efetuar Saqu</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/cancelamento-de-assinatura-nao-realizado-e-cobranca-indevida-persistente_4mA_vDyxabA5d2h8/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/demora-na-validacao-de-documentos-impede-movimentacao-e-saque-de-valores-na-plataforma-cakto_AxgK77MKxCN0UISD/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>manuscrito dos milagres</t>
+          <t>continua ativo</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Manuscrito dos Milagres</t>
+          <t>continua ativo</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1260,39 +1260,35 @@
       <c r="G15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>R$ 99,00</t>
-        </is>
-      </c>
+      <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Realizei a compra do produto "Manuscrito dos Milagres" no valor de 99 reais através da plataforma de vocês. Trata-se de um [Editado pelo Reclame Aqui] que usa inteligência artificial com a imagem do ator Jonathan Roumie. O conteúdo não foi entregue e não abre. Como estou dentro do prazo legal de 7 dias previsto pelo Artigo 49 do Código de Defesa do Consumidor, exijo o cancelamento imediato e o estorno integral do valor Comprei um produto através da perfectpay Curso(s): Manuscrito dos Milagres Ap</t>
+          <t>O produto continua ativo,sendo que não estou usando o serviço. RA Ads</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-manuscrito-dos-milagres-nao-entregue-e-solicitacao-de-estorno_YM7HDxei_9htWhyn/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/cancelamento-de-assinatura-nao-realizado-e-cobranca-indevida-persistente_4mA_vDyxabA5d2h8/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>youclone no dia 28</t>
+          <t>manuscrito dos milagres</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Youclone no dia 28</t>
+          <t>Manuscrito dos Milagres</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1302,7 +1298,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1320,7 +1316,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,89</t>
+          <t>R$ 99,00</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1329,28 +1325,28 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Comprei o produto Youclone no dia 28/08, no pix. Quando fui entrar no curso, não abre a área de membros e não consigo assistir o curso. Na minha área de membros só tem um curso que eu comprei faz tempo. Detalhes do Pedido Pedido: ***** Data: 28/08/2026</t>
+          <t>Realizei a compra do produto "Manuscrito dos Milagres" no valor de 99 reais através da plataforma de vocês. Trata-se de um [Editado pelo Reclame Aqui] que usa inteligência artificial com a imagem do ator Jonathan Roumie. O conteúdo não foi entregue e não abre. Como estou dentro do prazo legal de 7 dias previsto pelo Artigo 49 do Código de Defesa do Consumidor, exijo o cancelamento imediato e o estorno integral do valor Comprei um produto através da perfectpay Curso(s): Manuscrito dos Milagres Ap</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-manuscrito-dos-milagres-nao-entregue-e-solicitacao-de-estorno_YM7HDxei_9htWhyn/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>youclone no dia 28</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>Youclone no dia 28</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1365,7 +1361,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1376,35 +1372,39 @@
       <c r="G17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,89</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Boa noite. Fiz a compra de um produto na ultima quarta feira (26/08/20226) e até essa data eu não recebi o produto. Recebi o e-mail de confirmação do pagamento e um acesso pra fazer o download do material, mas não dá certo. Pra todo lugar que eles me enviam não dá certo. Falo com o pessoal do suporte e eles me deixam sem respostas. Só começam o atendimento. Pedi reembolso, também não dá certo. me mandaram 10 códigos de confirmação e com um segundo diz que expirou. tanto por E-mail quanto por cel</t>
+          <t>Comprei o produto Youclone no dia 28/08, no pix. Quando fui entrar no curso, não abre a área de membros e não consigo assistir o curso. Na minha área de membros só tem um curso que eu comprei faz tempo. Detalhes do Pedido Pedido: ***** Data: 28/08/2026</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/produto-nao-recebido-e-dificuldade-de-acesso-ao-material-digital-com-falha-no-reembolso-e-suporte-ineficaz_iOzRmbylQ4neQezT/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>de seguran</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>de seguran</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1437,24 +1437,28 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Boa noite. Fiz a compra de um produto na ultima quarta feira (26/08/20226) e até essa data eu não recebi o produto. Recebi o e-mail de confirmação do pagamento e um acesso pra fazer o download do material, mas não dá certo. Pra todo lugar que eles me enviam não dá certo. Falo com o pessoal do suporte e eles me deixam sem respostas. Só começam o atendimento. Pedi reembolso, também não dá certo. me mandaram 10 códigos de confirmação e com um segundo diz que expirou. tanto por E-mail quanto por cel</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-reembolso-de-pedido-com-codigo-de-transacao_poCcMMKbZVAkXZx9/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/produto-nao-recebido-e-dificuldade-de-acesso-ao-material-digital-com-falha-no-reembolso-e-suporte-ineficaz_iOzRmbylQ4neQezT/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>e a plataforma deveria no m</t>
+          <t>pelo qual paguei n</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>e a plataforma deveria no m</t>
+          <t>pelo qual paguei n</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1464,7 +1468,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1487,43 +1491,39 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra nessa plataforma e não consigo pedir o reembolso pois a plataforma alega não vender produto. Quero o reembolso pois não gostei do produto e a plataforma deveria no mínimo disponibilizar essa função no site. Segundo a plataforma eu tenho que entrar em contato com o responsável do produto, como irei pedir o reembolso pois o dono do produto não responde. ***** Numero do pedido da minha compra  Reembolso negado por plataforma que alega não vender o produto.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-por-plataforma-que-alega-nao-vender-o-produto_S-syATG5Z4eLNeZI/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-por-indisponibilidade-do-curso-corselet-classico_kKh1cXRxKbVwJRHp/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>e conseguiu acess</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Stalkeia</t>
+          <t>e conseguiu acess</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>R$ 401,40.</t>
+          <t>R$ 20,89</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,28 +1545,24 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>O produto prometia acesso a contas e mensagens do Instagram, mas na verdade entrega apenas um aplicativo que simula a interface do Instagram e cria conversas artificiais. Ou seja, trata-se de um serviço [Editado pelo Reclame Aqui], que não entrega o que anuncia. Eu testei com dois perfis diferentes e as mensagens são as mesmas, ou seja, [Editado pelo Reclame Aqui] e [Editado pelo Reclame Aqui]. Além disso, após um primeiro pagamento a plataforma vai nos induzindo a efetuar outras compras para co</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/servico-editado-pelo-reclame-aqui-da-via-perfect-pay-com-promessa-editado-pelo-reclame-aqui_XI7_jZmAIuhQa5In/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/inconsistencias-na-contabilizacao-de-vendas-e-pagamentos-na-conta-cakto_KtH_3-H9eW4zj_bs/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>um site hoje e quero solicitar o cancelam</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>um site hoje e quero solicitar o cancelam</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1576,12 +1572,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1599,28 +1595,24 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, Instagram e tiktok. Porém dentro da plataforma , fui informada que teria que pagar mais um valor para integração com as plataformas, informaram que esse valor é pagamento único, para as plataformas liberarem a integração ( não fica nada com eles). Como meu intuito é as postagens automáticas, comprei. Enviei o comprovante, como solicitado e aguardei o prazo para eles , entrar</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-3-pedidos-devido-a-arrependimento-e-insatisfacao-com-o-produtosite_KUDEd8s3eGajQ3-L/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>de seguran</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>de seguran</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1630,12 +1622,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1653,28 +1645,24 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por bastante tempo e disse ter efetuado o reembolso, coisa que eu não sei se aconteceu ou não, por que isso foi antes de ontem e lá na cakto ainda está como "pago" e não algo como "reembolso em andamento" ou coisa assim! Me disseram na última resposta que iam me mandar mensagem no contato cadastrado no reclame aqui, coisa que ainda não fizeram e o prazo pra reembolso é até am</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-reembolso-de-pedido-com-codigo-de-transacao_poCcMMKbZVAkXZx9/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>adquirido teria condi</t>
+          <t>e a plataforma deveria no m</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>adquirido teria condi</t>
+          <t>e a plataforma deveria no m</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1684,7 +1672,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1707,21 +1695,241 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
+          <t>Fiz uma compra nessa plataforma e não consigo pedir o reembolso pois a plataforma alega não vender produto. Quero o reembolso pois não gostei do produto e a plataforma deveria no mínimo disponibilizar essa função no site. Segundo a plataforma eu tenho que entrar em contato com o responsável do produto, como irei pedir o reembolso pois o dono do produto não responde. ***** Numero do pedido da minha compra  Reembolso negado por plataforma que alega não vender o produto.</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-por-plataforma-que-alega-nao-vender-o-produto_S-syATG5Z4eLNeZI/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>stalkeia</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Stalkeia</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>R$ 401,40.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>O produto prometia acesso a contas e mensagens do Instagram, mas na verdade entrega apenas um aplicativo que simula a interface do Instagram e cria conversas artificiais. Ou seja, trata-se de um serviço [Editado pelo Reclame Aqui], que não entrega o que anuncia. Eu testei com dois perfis diferentes e as mensagens são as mesmas, ou seja, [Editado pelo Reclame Aqui] e [Editado pelo Reclame Aqui]. Além disso, após um primeiro pagamento a plataforma vai nos induzindo a efetuar outras compras para co</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/servico-editado-pelo-reclame-aqui-da-via-perfect-pay-com-promessa-editado-pelo-reclame-aqui_XI7_jZmAIuhQa5In/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>de postagem autom</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>de postagem autom</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, Instagram e tiktok. Porém dentro da plataforma , fui informada que teria que pagar mais um valor para integração com as plataformas, informaram que esse valor é pagamento único, para as plataformas liberarem a integração ( não fica nada com eles). Como meu intuito é as postagens automáticas, comprei. Enviei o comprovante, como solicitado e aguardei o prazo para eles , entrar</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por bastante tempo e disse ter efetuado o reembolso, coisa que eu não sei se aconteceu ou não, por que isso foi antes de ontem e lá na cakto ainda está como "pago" e não algo como "reembolso em andamento" ou coisa assim! Me disseram na última resposta que iam me mandar mensagem no contato cadastrado no reclame aqui, coisa que ainda não fizeram e o prazo pra reembolso é até am</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>adquirido teria condi</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>adquirido teria condi</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
           <t>Venho solicitar a contestação de uma compra realizada referente à contratação de uma estrutura montada para geração de retorno financeiro. A contratação foi realizada acreditando que o serviço/produto adquirido teria condições de funcionar conforme apresentado pelos responsáveis pela estrutura. O problema é que, após a contratação e a montagem das estruturas, o resultado esperado não aconteceu. Além do valor já pago pela aquisição do produto/estrutura, posteriormente fui informado de que seria n</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>https://www.reclameaqui.com.br/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L23"/>
+  <autoFilter ref="A1:L27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1788,13 +1996,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -1803,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -1813,14 +2021,14 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
@@ -1828,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2092,7 +2300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2129,7 +2337,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2144,7 +2352,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2174,7 +2382,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2189,7 +2397,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2204,7 +2412,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2219,7 +2427,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2234,7 +2442,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -2249,7 +2457,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2264,7 +2472,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2279,13 +2487,13 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>e conseguiu acess</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2294,13 +2502,13 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2315,7 +2523,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>fábrica de low ticket</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2324,13 +2532,13 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero</t>
+          <t>interactive live</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2339,13 +2547,13 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
+          <t>low ticket do zero</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2360,7 +2568,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>manuscrito dos milagres</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2369,13 +2577,13 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>manuscrito dos milagres</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2390,7 +2598,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2399,13 +2607,13 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2414,13 +2622,13 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>on line rj comercio varejista de acessorios ltda</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2429,13 +2637,13 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>validação cadastral: em análise</t>
+          <t>pelo qual paguei n</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2444,13 +2652,13 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>youclone no dia 28</t>
+          <t>stalkeia</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2459,22 +2667,82 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>um site hoje e quero solicitar o cancelam</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>validação cadastral: em análise</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
           <t>zap radar</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>2</v>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -1928,8 +1928,62 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>dois cursos de idiomas</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>dois cursos de idiomas</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de dois cursos de idiomas, no caso Espanhol. Paguei pelos dois cursos via pi, porém só tive acesso a um curso, o outro aparece como acesso negado e não consigo acessar. Já entrei em contato com o suporte, porém o email retorna como email inválido. Entro em contato com o suporte para solicitar reembolso e ninguém me dá um retorno. Solicito devolução do valor, porém não tenho contato com ninguém da empresa. Acesso negado a curso de espanhol pago e dificuldade de contato com o suport</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/acesso-negado-a-curso-de-espanhol-pago-e-dificuldade-de-contato-com-o-suporte-para-reembolso_9d9eJH4OMC_ApZLR/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L27"/>
+  <autoFilter ref="A1:L28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1996,13 +2050,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -2011,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2300,7 +2354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2337,7 +2391,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2352,7 +2406,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2382,7 +2436,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2397,7 +2451,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -2412,7 +2466,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2427,7 +2481,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2442,7 +2496,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -2457,7 +2511,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -2472,13 +2526,13 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>e a plataforma deveria no m</t>
+          <t>dois cursos de idiomas</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2487,13 +2541,13 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>e conseguiu acess</t>
+          <t>e a plataforma deveria no m</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2502,13 +2556,13 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>e conseguiu acess</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2523,7 +2577,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2532,13 +2586,13 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>fábrica de low ticket</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2547,13 +2601,13 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero</t>
+          <t>interactive live</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2562,13 +2616,13 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
+          <t>low ticket do zero</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2577,13 +2631,13 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>manuscrito dos milagres</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2592,13 +2646,13 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>manuscrito dos milagres</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2607,13 +2661,13 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2622,13 +2676,13 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>on line rj comercio varejista de acessorios ltda</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2637,13 +2691,13 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>pelo qual paguei n</t>
+          <t>on line rj comercio varejista de acessorios ltda</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2652,13 +2706,13 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>pelo qual paguei n</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2673,7 +2727,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
+          <t>stalkeia</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2682,13 +2736,13 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>um site hoje e quero solicitar o cancelam</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2703,7 +2757,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>validação cadastral: em análise</t>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2712,13 +2766,13 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>youclone no dia 28</t>
+          <t>validação cadastral: em análise</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2727,22 +2781,37 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t>zap radar</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>3</v>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -523,27 +523,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>stalkeia</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fábrica de Low Ticket</t>
+          <t>Stalkeia</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Educação / Marketing digital e low ticket</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>R$ 254,98</t>
+          <t>R$ 47</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -569,29 +569,29 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Adquiri o curso com base na promessa apresentada pelo produtor de que haveria suporte individual. Porém, após entrar no grupo de WhatsApp, me deparei com uma discussão entre outros alunos que estavam reclamando justamente sobre essa questão. Na conversa, um dos administradores informou que a estratégia havia sido alterada e que o suporte agora seria realizado de forma coletiva pelo grupo. Eu não fui comunicado previamente sobre essa mudança e essa não foi a condição pela qual adquiri o curso. Co</t>
+          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas propaganda enganosa do Stalkeia.app e solicitação de reembolso do valor pago.  Resolvido  PerfectPay  Goiânia - GO  31/08/2026 às 04:47  ID: 257782105  realizei o pagamento direto no aplicativo, que prometia te entregar</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa-do-e-solicitacao-de-reembolso-do-valor-pago_yID1cmkfVopy5OrZ/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>on line rj comercio varejista de acessorios ltda</t>
+          <t>fábrica de low ticket</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>On Line Rj Comercio Varejista De Acessorios Ltda</t>
+          <t>Fábrica de Low Ticket</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ganhar dinheiro online / trabalho remoto</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
+          <t>R$ 254,98</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -623,24 +623,28 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Reembolso solicitado por propaganda enganosa sobre suporte individual no curso Fábrica de Low Ticket  Resolvido  CAKTO PAY  Cansanção - BA  01/09/2026 às 08:18  ID: 257896487  Olá,  Solicito o reembolso da compra da Fábrica de</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-de-assinatura-tokfy-via-pix-devido-a-plano-incorreto-e-falha-no-login-para-cancelamento_lwKWxoGQVq5QbJLn/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>um curso e</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>um curso e</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -655,7 +659,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -669,33 +673,37 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas [Editado pelo Reclame Aqui]  Resolvido  PerfectPay  Osasco - SP  31/08/2026 às 00:24  ID: 257779321  Fiz compra de um curso e é [Editado pelo Reclame Aqui]. Quero [Editado pelo Reclame Aqui] código *****  Aguardo.  RA Ad</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/editado-pelo-reclame-aqui_UeZdzzFsRKKhakiR/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>ra ads previous slide next slide compartilhe resp</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Método Atlas</t>
+          <t>RA Ads Previous slide Next slide Compartilhe Resp</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -705,7 +713,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -719,32 +727,32 @@
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desativaram as contas ,já procurei uma advogada e delegacia pra denunciar. Não caiam é [Editado pelo Reclame Aqui] RA Ads</t>
+          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas [Editado pelo Reclame Aqui]  Resolvido  PerfectPay  Mogi das Cruzes - SP  30/08/2026 às 23:05  ID: 257777077  Sofia um [Editado pelo Reclame Aqui], paguei e não recebi o produto  RA Ads Previous slide Next slide  Compart</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/compra-do-metodo-atlas-nao-cumpre-o-prometido-e-suporte-desativado_wzci0DCEtGCFBRc6/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/editado-pelo-reclame-aqui_SUXSgNqlxlTtM8rF/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>e ele nao chegou quero meu dinheiro de volta ra ad</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Interactive Live</t>
+          <t>e ele nao chegou quero meu dinheiro de volta RA Ad</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -759,7 +767,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -773,37 +781,37 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Comprei o produto "Interactive Live" através da plataforma Perfect Pay, que atuou como processadora de pagamento da venda. O produto recebido não correspondeu ao que foi anunciado/esperado, e eu solicitei o cancelamento/reembolso ainda dentro do prazo de garantia de 7 dias previsto no site/checkout, que também é assegurado pelo direito de arrependimento do art. 49 do Código de Defesa do Consumidor para compras feitas fora do estabelecimento comercial (como é o caso de compras online). Esse prazo</t>
+          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Propaganda inganosa  Respondida  PerfectPay  Caxias do Sul - RS  30/08/2026 às 15:07  ID: 257755023     Fiz a compra de um produto e ele nao chegou quero meu dinheiro de volta  RA Ads Previous slide Next slide  Compartil</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-e-prazo-expirado-devido-a-burocracia-da-perfect-pay_wFj48yi7DgllZO-Z/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-inganosa_WXGZ3QLZ1OhfoBjb/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
+          <t>converza.io</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Low Ticket do Zero 2.0 no dia 30</t>
+          <t>Converza.io</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -827,37 +835,37 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor. Resolvido CAKTO PAY Rio de Janeiro - RJ 31/08/2026 às 17:20</t>
+          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Exijo reembolso serviço não funciona e suporte não responde  Respondida  CAKTO PAY  São Paulo - SP  31/08/2026 às 03:25  ID: 257781633  Assinei um plano da Converza.io, porém não consigo sequer criar um dispositivo para</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/exijo-reembolso-servico-nao-funciona-e-suporte-nao-responde_OPi-rimJXtkjo2yB/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>cloakeuai</t>
+          <t>comunidade vsa</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Cloakeuai</t>
+          <t>COMUNIDADE VSA</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -867,7 +875,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Cloaking</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -878,50 +886,54 @@
       <c r="G8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>R$ 248,89.</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo suporte da plataforma e não me respondem, foi uma compra de +- 840 reais Quero o reembolso da minha compra: Dados da compra: Poxa, vou te ajudar a resolver isso! Me informe: Qual e-mail você usou na compra?</t>
+          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Solicitação de reembolso de compra com erro de saldo na conta do vendedor  Respondida  CAKTO PAY  Junqueiro - AL  31/08/2026 às 02:34  ID: 257781211  Olá,  Solicito o reembolso da compra da COMUNIDADE VSA, realizada em 2</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-de-compra-com-erro-de-saldo-na-conta-do-vendedor_e5d-tH3gUGahNktM/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>códigos lucrativos</t>
+          <t>retrato da sua alma gêmea</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Códigos Lucrativos</t>
+          <t>Retrato da Sua Alma Gêmea</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -932,50 +944,54 @@
       <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>R$ 48,89</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Comprei dois aplicativos codigos lucrativos e opinipix pela perfect pay,mas eles são [Editado pelo Reclame Aqui] . [Editado pelo Reclame Aqui]. Quero meu dinheiro de volta. Resposta da Empresa 31/01/2025 às 17:31</t>
+          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas [Editado pelo Reclame Aqui] e solicitação de estorno para produto "Retrato da Sua Alma Gêmea"  Respondida  CAKTO PAY  Campinas - SP  31/08/2026 às 02:06  ID: 257780917  Olá, equipe da Cakto Pay,No dia 28/08/2026, realize</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/editado-pelo-reclame-aqui-e-solicitacao-de-estorno-para-produto-retrato-da-sua-alma-gemea_H8ihRLGIEQMZ9WSb/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>aristocracy negócios digitais</t>
+          <t>pack canva</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Aristocracy Negócios Digitais</t>
+          <t>Pack Canva</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Produtos digitais variados / Assinatura vitalícia</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,19 +1002,27 @@
       <c r="G10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>R$ 15,15</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Solicitação de cancelamento e reembolso de cursos online após arrependimento de compra.  Respondida  CAKTO PAY  Suzano - SP  30/08/2026 às 19:54  ID: 257768163  Me chamo *****, solicito o cancelamento e reembolso do valo</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/acesso-negado-a-produtos-com-assinatura-vitalicia-e-namorada-customizada-nao-funciona_VUCzPEy-WEHTKJWB/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-de-cursos-online-apos-arrependimento-de-compra_-CZPnDHntp_r19_O/</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1039,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1025,7 +1049,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de espionagem / WhatsApp</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1043,11 +1067,11 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o estorno do valor pago. RA Ads</t>
+          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Solicitação de estorno de compra no site ZAP Radar por não recebimento de relatório.  Respondida  PerfectPay  Niterói - RJ  31/08/2026 às 22:22  ID: 257882275  Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pel</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1059,7 +1083,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>apostila de psicologia 2025</t>
+          <t>apostila de psicologia025</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1069,7 +1093,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1079,7 +1103,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Educação / Concursos e certificações</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1097,11 +1121,11 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico. Já entrei em contato por e-mail, por chat mais não consigo retorno. Já enviei os comprovantes de pagamentos de cada compra, mais não obtenho resposta. Esse material é para concurso, porém a Apostila não abre. Quando clico dá que já foi concluída sem ao menos eu ler. Comprei o material porque preciso, e hoje já entrei e não abre. Gostaria que resolvessem isso. Edna Carvalho</t>
+          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Apostila de Psicologia 2025 não abre e cliente não obtém retorno sobre compra online.  Respondida  CAKTO PAY  Sorocaba - SP  01/09/2026 às 10:19  ID: 257909223  Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um com</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1110,880 +1134,8 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>comunidade knights club</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>COMUNIDADE KNIGHTS CLUB</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Comunidades / Mentoria de negócios</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>R$ 67,99,</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>No dia 21/08/2026, realizei a compra da COMUNIDADE KNIGHTS CLUB, no valor de R$ 67,99, através da plataforma de pagamentos Cakto, com pagamento realizado via Pix. Após a compra, descobri que a ferramenta de inteligência artificial adquirida é destinada ao uso em computador. Essa informação não estava suficientemente clara para mim no momento da compra. Como não possuo computador, entrei em contato com o suporte para saber se seria possível utilizar a ferramenta pelo celular e fui informado de qu</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-de-compra-via-pix-nao-realizado-apos-solicitacao-dentro-do-prazo-legal_w1bmesmQpVhI5h0M/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>validação cadastral: em análise</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Validação cadastral: Em análise</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>R$ 38,09</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Olá, equipe da Cakto.Estou com um problema sério em relação à validação dos meus documentos na plataforma. Realizei o envio do meu documento digital no dia 18 de agosto, e desde então o status permanece travado como "Validação cadastral: Em análise".Já se passaram semanas e o processo não avança. Por conta dessa demora na análise, não consigo realizar movimentações na minha conta. Atualmente, possuo um saldo de R$ 38,09 categorizado como "Disponível para transferir", mas a opção de "Efetuar Saqu</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/demora-na-validacao-de-documentos-impede-movimentacao-e-saque-de-valores-na-plataforma-cakto_AxgK77MKxCN0UISD/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>continua ativo</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>continua ativo</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Infoprodutos - suporte e reembolso</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>O produto continua ativo,sendo que não estou usando o serviço. RA Ads</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/cancelamento-de-assinatura-nao-realizado-e-cobranca-indevida-persistente_4mA_vDyxabA5d2h8/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>manuscrito dos milagres</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Manuscrito dos Milagres</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>PerfectPay</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>R$ 99,00</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Realizei a compra do produto "Manuscrito dos Milagres" no valor de 99 reais através da plataforma de vocês. Trata-se de um [Editado pelo Reclame Aqui] que usa inteligência artificial com a imagem do ator Jonathan Roumie. O conteúdo não foi entregue e não abre. Como estou dentro do prazo legal de 7 dias previsto pelo Artigo 49 do Código de Defesa do Consumidor, exijo o cancelamento imediato e o estorno integral do valor Comprei um produto através da perfectpay Curso(s): Manuscrito dos Milagres Ap</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-manuscrito-dos-milagres-nao-entregue-e-solicitacao-de-estorno_YM7HDxei_9htWhyn/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>youclone no dia 28</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Youclone no dia 28</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,89</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Comprei o produto Youclone no dia 28/08, no pix. Quando fui entrar no curso, não abre a área de membros e não consigo assistir o curso. Na minha área de membros só tem um curso que eu comprei faz tempo. Detalhes do Pedido Pedido: ***** Data: 28/08/2026</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>na ultima quarta feira</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>na ultima quarta feira</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Infoprodutos - suporte e reembolso</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Boa noite. Fiz a compra de um produto na ultima quarta feira (26/08/20226) e até essa data eu não recebi o produto. Recebi o e-mail de confirmação do pagamento e um acesso pra fazer o download do material, mas não dá certo. Pra todo lugar que eles me enviam não dá certo. Falo com o pessoal do suporte e eles me deixam sem respostas. Só começam o atendimento. Pedi reembolso, também não dá certo. me mandaram 10 códigos de confirmação e com um segundo diz que expirou. tanto por E-mail quanto por cel</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/produto-nao-recebido-e-dificuldade-de-acesso-ao-material-digital-com-falha-no-reembolso-e-suporte-ineficaz_iOzRmbylQ4neQezT/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>pelo qual paguei n</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>pelo qual paguei n</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-por-indisponibilidade-do-curso-corselet-classico_kKh1cXRxKbVwJRHp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>e conseguiu acess</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>e conseguiu acess</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>R$ 20,89</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/inconsistencias-na-contabilizacao-de-vendas-e-pagamentos-na-conta-cakto_KtH_3-H9eW4zj_bs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-3-pedidos-devido-a-arrependimento-e-insatisfacao-com-o-produtosite_KUDEd8s3eGajQ3-L/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>de seguran</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>de seguran</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>PerfectPay</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Outros</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-reembolso-de-pedido-com-codigo-de-transacao_poCcMMKbZVAkXZx9/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>e a plataforma deveria no m</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>e a plataforma deveria no m</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>PerfectPay</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra nessa plataforma e não consigo pedir o reembolso pois a plataforma alega não vender produto. Quero o reembolso pois não gostei do produto e a plataforma deveria no mínimo disponibilizar essa função no site. Segundo a plataforma eu tenho que entrar em contato com o responsável do produto, como irei pedir o reembolso pois o dono do produto não responde. ***** Numero do pedido da minha compra  Reembolso negado por plataforma que alega não vender o produto.</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-por-plataforma-que-alega-nao-vender-o-produto_S-syATG5Z4eLNeZI/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>stalkeia</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Stalkeia</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>marca</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>PerfectPay</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Espionagem e rastreamento</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>R$ 401,40.</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>O produto prometia acesso a contas e mensagens do Instagram, mas na verdade entrega apenas um aplicativo que simula a interface do Instagram e cria conversas artificiais. Ou seja, trata-se de um serviço [Editado pelo Reclame Aqui], que não entrega o que anuncia. Eu testei com dois perfis diferentes e as mensagens são as mesmas, ou seja, [Editado pelo Reclame Aqui] e [Editado pelo Reclame Aqui]. Além disso, após um primeiro pagamento a plataforma vai nos induzindo a efetuar outras compras para co</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/servico-editado-pelo-reclame-aqui-da-via-perfect-pay-com-promessa-editado-pelo-reclame-aqui_XI7_jZmAIuhQa5In/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>de postagem autom</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>de postagem autom</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>PerfectPay</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Espionagem e rastreamento</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, Instagram e tiktok. Porém dentro da plataforma , fui informada que teria que pagar mais um valor para integração com as plataformas, informaram que esse valor é pagamento único, para as plataformas liberarem a integração ( não fica nada com eles). Como meu intuito é as postagens automáticas, comprei. Enviei o comprovante, como solicitado e aguardei o prazo para eles , entrar</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por bastante tempo e disse ter efetuado o reembolso, coisa que eu não sei se aconteceu ou não, por que isso foi antes de ontem e lá na cakto ainda está como "pago" e não algo como "reembolso em andamento" ou coisa assim! Me disseram na última resposta que iam me mandar mensagem no contato cadastrado no reclame aqui, coisa que ainda não fizeram e o prazo pra reembolso é até am</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>adquirido teria condi</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>adquirido teria condi</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Venho solicitar a contestação de uma compra realizada referente à contratação de uma estrutura montada para geração de retorno financeiro. A contratação foi realizada acreditando que o serviço/produto adquirido teria condições de funcionar conforme apresentado pelos responsáveis pela estrutura. O problema é que, após a contratação e a montagem das estruturas, o resultado esperado não aconteceu. Além do valor já pago pela aquisição do produto/estrutura, posteriormente fui informado de que seria n</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>dois cursos de idiomas</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>dois cursos de idiomas</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>angulo</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Cakto</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Produtividade</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>fria</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra de dois cursos de idiomas, no caso Espanhol. Paguei pelos dois cursos via pi, porém só tive acesso a um curso, o outro aparece como acesso negado e não consigo acessar. Já entrei em contato com o suporte, porém o email retorna como email inválido. Entro em contato com o suporte para solicitar reembolso e ninguém me dá um retorno. Solicito devolução do valor, porém não tenho contato com ninguém da empresa. Acesso negado a curso de espanhol pago e dificuldade de contato com o suport</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/acesso-negado-a-curso-de-espanhol-pago-e-dificuldade-de-contato-com-o-suporte-para-reembolso_9d9eJH4OMC_ApZLR/</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L28"/>
+  <autoFilter ref="A1:L12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1994,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2050,13 +1202,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -2065,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2075,13 +1227,13 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
@@ -2090,23 +1242,23 @@
         <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
@@ -2115,23 +1267,23 @@
         <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Educação / Marketing digital e low ticket</t>
+          <t>Ganhar dinheiro online / trabalho remoto</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
@@ -2140,206 +1292,6 @@
         <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Educação e consultoria</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Ferramentas de IA / Cloaking</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Produtos digitais variados / Assinatura vitalícia</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Ferramentas de espionagem / WhatsApp</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Educação / Concursos e certificações</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Comunidades / Mentoria de negócios</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Outros</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2354,7 +1306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2391,7 +1343,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2406,7 +1358,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2436,7 +1388,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2451,7 +1403,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -2466,28 +1418,28 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>continua ativo</t>
+          <t>comunidade vsa</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>códigos lucrativos</t>
+          <t>continua ativo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -2496,28 +1448,28 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>converza.io</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>de seguran</t>
+          <t>códigos lucrativos</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2526,13 +1478,13 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>dois cursos de idiomas</t>
+          <t>de postagem autom</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2541,13 +1493,13 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>e a plataforma deveria no m</t>
+          <t>de seguran</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2556,13 +1508,13 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>e conseguiu acess</t>
+          <t>dois cursos de idiomas</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2571,13 +1523,13 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>e a plataforma deveria no m</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2586,13 +1538,13 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>e conseguiu acess</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2601,28 +1553,28 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>e ele nao chegou quero meu dinheiro de volta ra ad</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2631,13 +1583,13 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
+          <t>fábrica de low ticket</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2646,13 +1598,13 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>manuscrito dos milagres</t>
+          <t>interactive live</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2661,13 +1613,13 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>low ticket do zero</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2676,13 +1628,13 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2691,13 +1643,13 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>on line rj comercio varejista de acessorios ltda</t>
+          <t>manuscrito dos milagres</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2706,13 +1658,13 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>pelo qual paguei n</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2721,13 +1673,13 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2736,13 +1688,13 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
+          <t>on line rj comercio varejista de acessorios ltda</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2751,28 +1703,28 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>pack canva</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>validação cadastral: em análise</t>
+          <t>pelo qual paguei n</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2781,37 +1733,142 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>youclone no dia 28</t>
+          <t>ra ads previous slide next slide compartilhe resp</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>retrato da sua alma gêmea</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>stalkeia</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>um curso e</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>um site hoje e quero solicitar o cancelam</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>validação cadastral: em análise</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
           <t>zap radar</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>5</v>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -523,27 +523,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>fábrica de low ticket</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Stalkeia</t>
+          <t>Fábrica de Low Ticket</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Educação / Marketing digital e low ticket</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>R$ 47</t>
+          <t>R$ 254,98</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -565,33 +565,33 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas propaganda enganosa do Stalkeia.app e solicitação de reembolso do valor pago.  Resolvido  PerfectPay  Goiânia - GO  31/08/2026 às 04:47  ID: 257782105  realizei o pagamento direto no aplicativo, que prometia te entregar</t>
+          <t>Adquiri o curso com base na promessa apresentada pelo produtor de que haveria suporte individual. Porém, após entrar no grupo de WhatsApp, me deparei com uma discussão entre outros alunos que estavam reclamando justamente sobre essa questão. Na conversa, um dos administradores informou que a estratégia havia sido alterada e que o suporte agora seria realizado de forma coletiva pelo grupo. Eu não fui comunicado previamente sobre essa mudança e essa não foi a condição pela qual adquiri o curso. Co</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa-do-e-solicitacao-de-reembolso-do-valor-pago_yID1cmkfVopy5OrZ/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>on line rj comercio varejista de acessorios ltda</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Fábrica de Low Ticket</t>
+          <t>On Line Rj Comercio Varejista De Acessorios Ltda</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / trabalho remoto</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>R$ 254,98</t>
+          <t>R$ 297,00</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -623,28 +623,24 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Reembolso solicitado por propaganda enganosa sobre suporte individual no curso Fábrica de Low Ticket  Resolvido  CAKTO PAY  Cansanção - BA  01/09/2026 às 08:18  ID: 257896487  Olá,  Solicito o reembolso da compra da Fábrica de</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-de-assinatura-tokfy-via-pix-devido-a-plano-incorreto-e-falha-no-login-para-cancelamento_lwKWxoGQVq5QbJLn/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -659,7 +655,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -673,37 +669,33 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas [Editado pelo Reclame Aqui]  Resolvido  PerfectPay  Osasco - SP  31/08/2026 às 00:24  ID: 257779321  Fiz compra de um curso e é [Editado pelo Reclame Aqui]. Quero [Editado pelo Reclame Aqui] código *****  Aguardo.  RA Ad</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/editado-pelo-reclame-aqui_UeZdzzFsRKKhakiR/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ra ads previous slide next slide compartilhe resp</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Previous slide Next slide Compartilhe Resp</t>
+          <t>Método Atlas</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -713,7 +705,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -727,32 +719,32 @@
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas [Editado pelo Reclame Aqui]  Resolvido  PerfectPay  Mogi das Cruzes - SP  30/08/2026 às 23:05  ID: 257777077  Sofia um [Editado pelo Reclame Aqui], paguei e não recebi o produto  RA Ads Previous slide Next slide  Compart</t>
+          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desativaram as contas ,já procurei uma advogada e delegacia pra denunciar. Não caiam é [Editado pelo Reclame Aqui] RA Ads</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/editado-pelo-reclame-aqui_SUXSgNqlxlTtM8rF/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/compra-do-metodo-atlas-nao-cumpre-o-prometido-e-suporte-desativado_wzci0DCEtGCFBRc6/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>e ele nao chegou quero meu dinheiro de volta ra ad</t>
+          <t>interactive live</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>e ele nao chegou quero meu dinheiro de volta RA Ad</t>
+          <t>Interactive Live</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -767,7 +759,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -781,37 +773,37 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Propaganda inganosa  Respondida  PerfectPay  Caxias do Sul - RS  30/08/2026 às 15:07  ID: 257755023     Fiz a compra de um produto e ele nao chegou quero meu dinheiro de volta  RA Ads Previous slide Next slide  Compartil</t>
+          <t>Comprei o produto "Interactive Live" através da plataforma Perfect Pay, que atuou como processadora de pagamento da venda. O produto recebido não correspondeu ao que foi anunciado/esperado, e eu solicitei o cancelamento/reembolso ainda dentro do prazo de garantia de 7 dias previsto no site/checkout, que também é assegurado pelo direito de arrependimento do art. 49 do Código de Defesa do Consumidor para compras feitas fora do estabelecimento comercial (como é o caso de compras online). Esse prazo</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-inganosa_WXGZ3QLZ1OhfoBjb/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-e-prazo-expirado-devido-a-burocracia-da-perfect-pay_wFj48yi7DgllZO-Z/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>converza.io</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Converza.io</t>
+          <t>Low Ticket do Zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -835,37 +827,37 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Exijo reembolso serviço não funciona e suporte não responde  Respondida  CAKTO PAY  São Paulo - SP  31/08/2026 às 03:25  ID: 257781633  Assinei um plano da Converza.io, porém não consigo sequer criar um dispositivo para</t>
+          <t>Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor. Resolvido CAKTO PAY Rio de Janeiro - RJ 31/08/2026 às 17:20</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/exijo-reembolso-servico-nao-funciona-e-suporte-nao-responde_OPi-rimJXtkjo2yB/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>comunidade vsa</t>
+          <t>cloakeuai</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COMUNIDADE VSA</t>
+          <t>Cloakeuai</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -875,7 +867,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de IA / Cloaking</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -886,54 +878,50 @@
       <c r="G8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>R$ 248,89.</t>
-        </is>
-      </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Solicitação de reembolso de compra com erro de saldo na conta do vendedor  Respondida  CAKTO PAY  Junqueiro - AL  31/08/2026 às 02:34  ID: 257781211  Olá,  Solicito o reembolso da compra da COMUNIDADE VSA, realizada em 2</t>
+          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo suporte da plataforma e não me respondem, foi uma compra de +- 840 reais Quero o reembolso da minha compra: Dados da compra: Poxa, vou te ajudar a resolver isso! Me informe: Qual e-mail você usou na compra?</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-de-compra-com-erro-de-saldo-na-conta-do-vendedor_e5d-tH3gUGahNktM/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>retrato da sua alma gêmea</t>
+          <t>códigos lucrativos</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Retrato da Sua Alma Gêmea</t>
+          <t>Códigos Lucrativos</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -944,54 +932,50 @@
       <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>R$ 48,89</t>
-        </is>
-      </c>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas [Editado pelo Reclame Aqui] e solicitação de estorno para produto "Retrato da Sua Alma Gêmea"  Respondida  CAKTO PAY  Campinas - SP  31/08/2026 às 02:06  ID: 257780917  Olá, equipe da Cakto Pay,No dia 28/08/2026, realize</t>
+          <t>Comprei dois aplicativos codigos lucrativos e opinipix pela perfect pay,mas eles são [Editado pelo Reclame Aqui] . [Editado pelo Reclame Aqui]. Quero meu dinheiro de volta. Resposta da Empresa 31/01/2025 às 17:31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/editado-pelo-reclame-aqui-e-solicitacao-de-estorno-para-produto-retrato-da-sua-alma-gemea_H8ihRLGIEQMZ9WSb/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>pack canva</t>
+          <t>aristocracy negócios digitais</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Pack Canva</t>
+          <t>Aristocracy Negócios Digitais</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Produtos digitais variados / Assinatura vitalícia</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1002,27 +986,19 @@
       <c r="G10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>R$ 15,15</t>
-        </is>
-      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Solicitação de cancelamento e reembolso de cursos online após arrependimento de compra.  Respondida  CAKTO PAY  Suzano - SP  30/08/2026 às 19:54  ID: 257768163  Me chamo *****, solicito o cancelamento e reembolso do valo</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-de-cursos-online-apos-arrependimento-de-compra_-CZPnDHntp_r19_O/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/acesso-negado-a-produtos-com-assinatura-vitalicia-e-namorada-customizada-nao-funciona_VUCzPEy-WEHTKJWB/</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1015,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1049,7 +1025,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de espionagem / WhatsApp</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1067,11 +1043,11 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Solicitação de estorno de compra no site ZAP Radar por não recebimento de relatório.  Respondida  PerfectPay  Niterói - RJ  31/08/2026 às 22:22  ID: 257882275  Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pel</t>
+          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o estorno do valor pago. RA Ads</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1083,7 +1059,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>apostila de psicologia025</t>
+          <t>apostila de psicologia 2025</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1093,7 +1069,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1103,7 +1079,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Educação / Concursos e certificações</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1121,21 +1097,893 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico. Já entrei em contato por e-mail, por chat mais não consigo retorno. Já enviei os comprovantes de pagamentos de cada compra, mais não obtenho resposta. Esse material é para concurso, porém a Apostila não abre. Quando clico dá que já foi concluída sem ao menos eu ler. Comprei o material porque preciso, e hoje já entrei e não abre. Gostaria que resolvessem isso. Edna Carvalho</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>comunidade knights club</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>COMUNIDADE KNIGHTS CLUB</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Comunidades / Mentoria de negócios</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,99,</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>No dia 21/08/2026, realizei a compra da COMUNIDADE KNIGHTS CLUB, no valor de R$ 67,99, através da plataforma de pagamentos Cakto, com pagamento realizado via Pix. Após a compra, descobri que a ferramenta de inteligência artificial adquirida é destinada ao uso em computador. Essa informação não estava suficientemente clara para mim no momento da compra. Como não possuo computador, entrei em contato com o suporte para saber se seria possível utilizar a ferramenta pelo celular e fui informado de qu</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-de-compra-via-pix-nao-realizado-apos-solicitacao-dentro-do-prazo-legal_w1bmesmQpVhI5h0M/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>validação cadastral: em análise</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Validação cadastral: Em análise</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>R$ 38,09</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Olá, equipe da Cakto.Estou com um problema sério em relação à validação dos meus documentos na plataforma. Realizei o envio do meu documento digital no dia 18 de agosto, e desde então o status permanece travado como "Validação cadastral: Em análise".Já se passaram semanas e o processo não avança. Por conta dessa demora na análise, não consigo realizar movimentações na minha conta. Atualmente, possuo um saldo de R$ 38,09 categorizado como "Disponível para transferir", mas a opção de "Efetuar Saqu</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/demora-na-validacao-de-documentos-impede-movimentacao-e-saque-de-valores-na-plataforma-cakto_AxgK77MKxCN0UISD/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>continua ativo</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>continua ativo</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>O produto continua ativo,sendo que não estou usando o serviço. RA Ads</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/cancelamento-de-assinatura-nao-realizado-e-cobranca-indevida-persistente_4mA_vDyxabA5d2h8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>manuscrito dos milagres</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Manuscrito dos Milagres</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>R$ 99,00</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra do produto "Manuscrito dos Milagres" no valor de 99 reais através da plataforma de vocês. Trata-se de um [Editado pelo Reclame Aqui] que usa inteligência artificial com a imagem do ator Jonathan Roumie. O conteúdo não foi entregue e não abre. Como estou dentro do prazo legal de 7 dias previsto pelo Artigo 49 do Código de Defesa do Consumidor, exijo o cancelamento imediato e o estorno integral do valor Comprei um produto através da perfectpay Curso(s): Manuscrito dos Milagres Ap</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-manuscrito-dos-milagres-nao-entregue-e-solicitacao-de-estorno_YM7HDxei_9htWhyn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,89</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o produto Youclone no dia 28/08, no pix. Quando fui entrar no curso, não abre a área de membros e não consigo assistir o curso. Na minha área de membros só tem um curso que eu comprei faz tempo. Detalhes do Pedido Pedido: ***** Data: 28/08/2026</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>na ultima quarta feira</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>na ultima quarta feira</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Boa noite. Fiz a compra de um produto na ultima quarta feira (26/08/20226) e até essa data eu não recebi o produto. Recebi o e-mail de confirmação do pagamento e um acesso pra fazer o download do material, mas não dá certo. Pra todo lugar que eles me enviam não dá certo. Falo com o pessoal do suporte e eles me deixam sem respostas. Só começam o atendimento. Pedi reembolso, também não dá certo. me mandaram 10 códigos de confirmação e com um segundo diz que expirou. tanto por E-mail quanto por cel</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/produto-nao-recebido-e-dificuldade-de-acesso-ao-material-digital-com-falha-no-reembolso-e-suporte-ineficaz_iOzRmbylQ4neQezT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>pelo qual paguei n</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>pelo qual paguei n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-por-indisponibilidade-do-curso-corselet-classico_kKh1cXRxKbVwJRHp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>e conseguiu acess</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>e conseguiu acess</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>R$ 20,89</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/inconsistencias-na-contabilizacao-de-vendas-e-pagamentos-na-conta-cakto_KtH_3-H9eW4zj_bs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>um site hoje e quero solicitar o cancelam</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>um site hoje e quero solicitar o cancelam</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-3-pedidos-devido-a-arrependimento-e-insatisfacao-com-o-produtosite_KUDEd8s3eGajQ3-L/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>de seguran</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>de seguran</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-reembolso-de-pedido-com-codigo-de-transacao_poCcMMKbZVAkXZx9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>e a plataforma deveria no m</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>e a plataforma deveria no m</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra nessa plataforma e não consigo pedir o reembolso pois a plataforma alega não vender produto. Quero o reembolso pois não gostei do produto e a plataforma deveria no mínimo disponibilizar essa função no site. Segundo a plataforma eu tenho que entrar em contato com o responsável do produto, como irei pedir o reembolso pois o dono do produto não responde. ***** Numero do pedido da minha compra  Reembolso negado por plataforma que alega não vender o produto.</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-por-plataforma-que-alega-nao-vender-o-produto_S-syATG5Z4eLNeZI/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>stalkeia</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Stalkeia</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>R$ 401,40.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>O produto prometia acesso a contas e mensagens do Instagram, mas na verdade entrega apenas um aplicativo que simula a interface do Instagram e cria conversas artificiais. Ou seja, trata-se de um serviço [Editado pelo Reclame Aqui], que não entrega o que anuncia. Eu testei com dois perfis diferentes e as mensagens são as mesmas, ou seja, [Editado pelo Reclame Aqui] e [Editado pelo Reclame Aqui]. Além disso, após um primeiro pagamento a plataforma vai nos induzindo a efetuar outras compras para co</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/servico-editado-pelo-reclame-aqui-da-via-perfect-pay-com-promessa-editado-pelo-reclame-aqui_XI7_jZmAIuhQa5In/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>de postagem autom</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>de postagem autom</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, Instagram e tiktok. Porém dentro da plataforma , fui informada que teria que pagar mais um valor para integração com as plataformas, informaram que esse valor é pagamento único, para as plataformas liberarem a integração ( não fica nada com eles). Como meu intuito é as postagens automáticas, comprei. Enviei o comprovante, como solicitado e aguardei o prazo para eles , entrar</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por bastante tempo e disse ter efetuado o reembolso, coisa que eu não sei se aconteceu ou não, por que isso foi antes de ontem e lá na cakto ainda está como "pago" e não algo como "reembolso em andamento" ou coisa assim! Me disseram na última resposta que iam me mandar mensagem no contato cadastrado no reclame aqui, coisa que ainda não fizeram e o prazo pra reembolso é até am</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>adquirido teria condi</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>adquirido teria condi</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Venho solicitar a contestação de uma compra realizada referente à contratação de uma estrutura montada para geração de retorno financeiro. A contratação foi realizada acreditando que o serviço/produto adquirido teria condições de funcionar conforme apresentado pelos responsáveis pela estrutura. O problema é que, após a contratação e a montagem das estruturas, o resultado esperado não aconteceu. Além do valor já pago pela aquisição do produto/estrutura, posteriormente fui informado de que seria n</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>dois cursos de idiomas</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>dois cursos de idiomas</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Apostila de Psicologia 2025 não abre e cliente não obtém retorno sobre compra online.  Respondida  CAKTO PAY  Sorocaba - SP  01/09/2026 às 10:19  ID: 257909223  Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um com</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de dois cursos de idiomas, no caso Espanhol. Paguei pelos dois cursos via pi, porém só tive acesso a um curso, o outro aparece como acesso negado e não consigo acessar. Já entrei em contato com o suporte, porém o email retorna como email inválido. Entro em contato com o suporte para solicitar reembolso e ninguém me dá um retorno. Solicito devolução do valor, porém não tenho contato com ninguém da empresa. Acesso negado a curso de espanhol pago e dificuldade de contato com o suport</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/acesso-negado-a-curso-de-espanhol-pago-e-dificuldade-de-contato-com-o-suporte-para-reembolso_9d9eJH4OMC_ApZLR/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L12"/>
+  <autoFilter ref="A1:L28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1146,7 +1994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1202,13 +2050,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -1217,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -1227,14 +2075,14 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
@@ -1242,24 +2090,24 @@
         <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
@@ -1267,23 +2115,23 @@
         <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / trabalho remoto</t>
+          <t>Educação / Marketing digital e low ticket</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
@@ -1292,6 +2140,206 @@
         <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Cloaking</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Produtos digitais variados / Assinatura vitalícia</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Ferramentas de espionagem / WhatsApp</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Educação / Concursos e certificações</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Comunidades / Mentoria de negócios</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1373,7 +2421,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1433,7 +2481,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1463,7 +2511,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1568,7 +2616,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1598,7 +2646,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1718,7 +2766,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1748,7 +2796,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1763,7 +2811,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1778,7 +2826,7 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -1793,7 +2841,7 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1868,7 +2916,7 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -523,27 +523,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>stalkeia</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fábrica de Low Ticket</t>
+          <t>Stalkeia</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Educação / Marketing digital e low ticket</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>R$ 254,98</t>
+          <t>R$ 401,40., R$ 47,00</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -569,24 +569,24 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Adquiri o curso com base na promessa apresentada pelo produtor de que haveria suporte individual. Porém, após entrar no grupo de WhatsApp, me deparei com uma discussão entre outros alunos que estavam reclamando justamente sobre essa questão. Na conversa, um dos administradores informou que a estratégia havia sido alterada e que o suporte agora seria realizado de forma coletiva pelo grupo. Eu não fui comunicado previamente sobre essa mudança e essa não foi a condição pela qual adquiri o curso. Co</t>
+          <t>O produto prometia acesso a contas e mensagens do Instagram, mas na verdade entrega apenas um aplicativo que simula a interface do Instagram e cria conversas artificiais. Ou seja, trata-se de um serviço [Editado pelo Reclame Aqui], que não entrega o que anuncia. Eu testei com dois perfis diferentes e as mensagens são as mesmas, ou seja, [Editado pelo Reclame Aqui] e [Editado pelo Reclame Aqui]. Além disso, após um primeiro pagamento a plataforma vai nos induzindo a efetuar outras compras para co</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/servico-editado-pelo-reclame-aqui-da-via-perfect-pay-com-promessa-editado-pelo-reclame-aqui_XI7_jZmAIuhQa5In/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>on line rj comercio varejista de acessorios ltda</t>
+          <t>fábrica de low ticket</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>On Line Rj Comercio Varejista De Acessorios Ltda</t>
+          <t>Fábrica de Low Ticket</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Educação / Marketing digital e low ticket</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00</t>
+          <t>R$ 254,98</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -623,24 +623,28 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Adquiri o curso com base na promessa apresentada pelo produtor de que haveria suporte individual. Porém, após entrar no grupo de WhatsApp, me deparei com uma discussão entre outros alunos que estavam reclamando justamente sobre essa questão. Na conversa, um dos administradores informou que a estratégia havia sido alterada e que o suporte agora seria realizado de forma coletiva pelo grupo. Eu não fui comunicado previamente sobre essa mudança e essa não foi a condição pela qual adquiri o curso. Co</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-de-assinatura-tokfy-via-pix-devido-a-plano-incorreto-e-falha-no-login-para-cancelamento_lwKWxoGQVq5QbJLn/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>on line rj comercio varejista de acessorios ltda</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>On Line Rj Comercio Varejista De Acessorios Ltda</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -650,12 +654,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -666,36 +670,40 @@
       <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>R$ 297,00</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-de-assinatura-tokfy-via-pix-devido-a-plano-incorreto-e-falha-no-login-para-cancelamento_lwKWxoGQVq5QbJLn/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Método Atlas</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -705,7 +713,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -725,31 +733,27 @@
       <c r="J5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desativaram as contas ,já procurei uma advogada e delegacia pra denunciar. Não caiam é [Editado pelo Reclame Aqui] RA Ads</t>
-        </is>
-      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/compra-do-metodo-atlas-nao-cumpre-o-prometido-e-suporte-desativado_wzci0DCEtGCFBRc6/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Interactive Live</t>
+          <t>Método Atlas</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -759,7 +763,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -777,28 +781,28 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Comprei o produto "Interactive Live" através da plataforma Perfect Pay, que atuou como processadora de pagamento da venda. O produto recebido não correspondeu ao que foi anunciado/esperado, e eu solicitei o cancelamento/reembolso ainda dentro do prazo de garantia de 7 dias previsto no site/checkout, que também é assegurado pelo direito de arrependimento do art. 49 do Código de Defesa do Consumidor para compras feitas fora do estabelecimento comercial (como é o caso de compras online). Esse prazo</t>
+          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desativaram as contas ,já procurei uma advogada e delegacia pra denunciar. Não caiam é [Editado pelo Reclame Aqui] RA Ads</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-e-prazo-expirado-devido-a-burocracia-da-perfect-pay_wFj48yi7DgllZO-Z/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/compra-do-metodo-atlas-nao-cumpre-o-prometido-e-suporte-desativado_wzci0DCEtGCFBRc6/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
+          <t>interactive live</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Low Ticket do Zero 2.0 no dia 30</t>
+          <t>Interactive Live</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -808,12 +812,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -831,28 +835,28 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor. Resolvido CAKTO PAY Rio de Janeiro - RJ 31/08/2026 às 17:20</t>
+          <t>Comprei o produto "Interactive Live" através da plataforma Perfect Pay, que atuou como processadora de pagamento da venda. O produto recebido não correspondeu ao que foi anunciado/esperado, e eu solicitei o cancelamento/reembolso ainda dentro do prazo de garantia de 7 dias previsto no site/checkout, que também é assegurado pelo direito de arrependimento do art. 49 do Código de Defesa do Consumidor para compras feitas fora do estabelecimento comercial (como é o caso de compras online). Esse prazo</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-e-prazo-expirado-devido-a-burocracia-da-perfect-pay_wFj48yi7DgllZO-Z/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>cloakeuai</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Cloakeuai</t>
+          <t>Low Ticket do Zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -867,7 +871,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Cloaking</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -889,24 +893,24 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo suporte da plataforma e não me respondem, foi uma compra de +- 840 reais Quero o reembolso da minha compra: Dados da compra: Poxa, vou te ajudar a resolver isso! Me informe: Qual e-mail você usou na compra?</t>
+          <t>Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor. Resolvido CAKTO PAY Rio de Janeiro - RJ 31/08/2026 às 17:20</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>códigos lucrativos</t>
+          <t>cloakeuai</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Códigos Lucrativos</t>
+          <t>Cloakeuai</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -916,12 +920,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+          <t>Ferramentas de IA / Cloaking</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -939,28 +943,28 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Comprei dois aplicativos codigos lucrativos e opinipix pela perfect pay,mas eles são [Editado pelo Reclame Aqui] . [Editado pelo Reclame Aqui]. Quero meu dinheiro de volta. Resposta da Empresa 31/01/2025 às 17:31</t>
+          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo suporte da plataforma e não me respondem, foi uma compra de +- 840 reais Quero o reembolso da minha compra: Dados da compra: Poxa, vou te ajudar a resolver isso! Me informe: Qual e-mail você usou na compra?</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>aristocracy negócios digitais</t>
+          <t>códigos lucrativos</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Aristocracy Negócios Digitais</t>
+          <t>Códigos Lucrativos</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -975,7 +979,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Produtos digitais variados / Assinatura vitalícia</t>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -993,24 +997,28 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Comprei dois aplicativos codigos lucrativos e opinipix pela perfect pay,mas eles são [Editado pelo Reclame Aqui] . [Editado pelo Reclame Aqui]. Quero meu dinheiro de volta. Resposta da Empresa 31/01/2025 às 17:31</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/acesso-negado-a-produtos-com-assinatura-vitalicia-e-namorada-customizada-nao-funciona_VUCzPEy-WEHTKJWB/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>zap radar</t>
+          <t>aristocracy negócios digitais</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ZAP Radar</t>
+          <t>Aristocracy Negócios Digitais</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1025,7 +1033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de espionagem / WhatsApp</t>
+          <t>Produtos digitais variados / Assinatura vitalícia</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1043,28 +1051,24 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o estorno do valor pago. RA Ads</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/acesso-negado-a-produtos-com-assinatura-vitalicia-e-namorada-customizada-nao-funciona_VUCzPEy-WEHTKJWB/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>apostila de psicologia 2025</t>
+          <t>zap radar</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Apostila de Psicologia 2025</t>
+          <t>ZAP Radar</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1074,12 +1078,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Educação / Concursos e certificações</t>
+          <t>Ferramentas de espionagem / WhatsApp</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1097,28 +1101,28 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico. Já entrei em contato por e-mail, por chat mais não consigo retorno. Já enviei os comprovantes de pagamentos de cada compra, mais não obtenho resposta. Esse material é para concurso, porém a Apostila não abre. Quando clico dá que já foi concluída sem ao menos eu ler. Comprei o material porque preciso, e hoje já entrei e não abre. Gostaria que resolvessem isso. Edna Carvalho</t>
+          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o estorno do valor pago. RA Ads</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>comunidade knights club</t>
+          <t>apostila de psicologia 2025</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>COMUNIDADE KNIGHTS CLUB</t>
+          <t>Apostila de Psicologia 2025</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1133,7 +1137,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Comunidades / Mentoria de negócios</t>
+          <t>Educação / Concursos e certificações</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1144,39 +1148,35 @@
       <c r="G13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>R$ 67,99,</t>
-        </is>
-      </c>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>No dia 21/08/2026, realizei a compra da COMUNIDADE KNIGHTS CLUB, no valor de R$ 67,99, através da plataforma de pagamentos Cakto, com pagamento realizado via Pix. Após a compra, descobri que a ferramenta de inteligência artificial adquirida é destinada ao uso em computador. Essa informação não estava suficientemente clara para mim no momento da compra. Como não possuo computador, entrei em contato com o suporte para saber se seria possível utilizar a ferramenta pelo celular e fui informado de qu</t>
+          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico. Já entrei em contato por e-mail, por chat mais não consigo retorno. Já enviei os comprovantes de pagamentos de cada compra, mais não obtenho resposta. Esse material é para concurso, porém a Apostila não abre. Quando clico dá que já foi concluída sem ao menos eu ler. Comprei o material porque preciso, e hoje já entrei e não abre. Gostaria que resolvessem isso. Edna Carvalho</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-de-compra-via-pix-nao-realizado-apos-solicitacao-dentro-do-prazo-legal_w1bmesmQpVhI5h0M/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>validação cadastral: em análise</t>
+          <t>comunidade knights club</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Validação cadastral: Em análise</t>
+          <t>COMUNIDADE KNIGHTS CLUB</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Comunidades / Mentoria de negócios</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>R$ 38,09</t>
+          <t>R$ 67,99,</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1213,28 +1213,28 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Olá, equipe da Cakto.Estou com um problema sério em relação à validação dos meus documentos na plataforma. Realizei o envio do meu documento digital no dia 18 de agosto, e desde então o status permanece travado como "Validação cadastral: Em análise".Já se passaram semanas e o processo não avança. Por conta dessa demora na análise, não consigo realizar movimentações na minha conta. Atualmente, possuo um saldo de R$ 38,09 categorizado como "Disponível para transferir", mas a opção de "Efetuar Saqu</t>
+          <t>No dia 21/08/2026, realizei a compra da COMUNIDADE KNIGHTS CLUB, no valor de R$ 67,99, através da plataforma de pagamentos Cakto, com pagamento realizado via Pix. Após a compra, descobri que a ferramenta de inteligência artificial adquirida é destinada ao uso em computador. Essa informação não estava suficientemente clara para mim no momento da compra. Como não possuo computador, entrei em contato com o suporte para saber se seria possível utilizar a ferramenta pelo celular e fui informado de qu</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/demora-na-validacao-de-documentos-impede-movimentacao-e-saque-de-valores-na-plataforma-cakto_AxgK77MKxCN0UISD/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-de-compra-via-pix-nao-realizado-apos-solicitacao-dentro-do-prazo-legal_w1bmesmQpVhI5h0M/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>continua ativo</t>
+          <t>validação cadastral: em análise</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>continua ativo</t>
+          <t>Validação cadastral: Em análise</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1260,35 +1260,39 @@
       <c r="G15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>R$ 38,09</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>O produto continua ativo,sendo que não estou usando o serviço. RA Ads</t>
+          <t>Olá, equipe da Cakto.Estou com um problema sério em relação à validação dos meus documentos na plataforma. Realizei o envio do meu documento digital no dia 18 de agosto, e desde então o status permanece travado como "Validação cadastral: Em análise".Já se passaram semanas e o processo não avança. Por conta dessa demora na análise, não consigo realizar movimentações na minha conta. Atualmente, possuo um saldo de R$ 38,09 categorizado como "Disponível para transferir", mas a opção de "Efetuar Saqu</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/cancelamento-de-assinatura-nao-realizado-e-cobranca-indevida-persistente_4mA_vDyxabA5d2h8/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/demora-na-validacao-de-documentos-impede-movimentacao-e-saque-de-valores-na-plataforma-cakto_AxgK77MKxCN0UISD/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>manuscrito dos milagres</t>
+          <t>continua ativo</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Manuscrito dos Milagres</t>
+          <t>continua ativo</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1298,12 +1302,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1314,39 +1318,35 @@
       <c r="G16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>R$ 99,00</t>
-        </is>
-      </c>
+      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Realizei a compra do produto "Manuscrito dos Milagres" no valor de 99 reais através da plataforma de vocês. Trata-se de um [Editado pelo Reclame Aqui] que usa inteligência artificial com a imagem do ator Jonathan Roumie. O conteúdo não foi entregue e não abre. Como estou dentro do prazo legal de 7 dias previsto pelo Artigo 49 do Código de Defesa do Consumidor, exijo o cancelamento imediato e o estorno integral do valor Comprei um produto através da perfectpay Curso(s): Manuscrito dos Milagres Ap</t>
+          <t>O produto continua ativo,sendo que não estou usando o serviço. RA Ads</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-manuscrito-dos-milagres-nao-entregue-e-solicitacao-de-estorno_YM7HDxei_9htWhyn/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/cancelamento-de-assinatura-nao-realizado-e-cobranca-indevida-persistente_4mA_vDyxabA5d2h8/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>youclone no dia 28</t>
+          <t>manuscrito dos milagres</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Youclone no dia 28</t>
+          <t>Manuscrito dos Milagres</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,89</t>
+          <t>R$ 99,00</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1383,28 +1383,28 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Comprei o produto Youclone no dia 28/08, no pix. Quando fui entrar no curso, não abre a área de membros e não consigo assistir o curso. Na minha área de membros só tem um curso que eu comprei faz tempo. Detalhes do Pedido Pedido: ***** Data: 28/08/2026</t>
+          <t>Realizei a compra do produto "Manuscrito dos Milagres" no valor de 99 reais através da plataforma de vocês. Trata-se de um [Editado pelo Reclame Aqui] que usa inteligência artificial com a imagem do ator Jonathan Roumie. O conteúdo não foi entregue e não abre. Como estou dentro do prazo legal de 7 dias previsto pelo Artigo 49 do Código de Defesa do Consumidor, exijo o cancelamento imediato e o estorno integral do valor Comprei um produto através da perfectpay Curso(s): Manuscrito dos Milagres Ap</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-manuscrito-dos-milagres-nao-entregue-e-solicitacao-de-estorno_YM7HDxei_9htWhyn/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>youclone no dia 28</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>Youclone no dia 28</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1430,35 +1430,39 @@
       <c r="G18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,89</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Boa noite. Fiz a compra de um produto na ultima quarta feira (26/08/20226) e até essa data eu não recebi o produto. Recebi o e-mail de confirmação do pagamento e um acesso pra fazer o download do material, mas não dá certo. Pra todo lugar que eles me enviam não dá certo. Falo com o pessoal do suporte e eles me deixam sem respostas. Só começam o atendimento. Pedi reembolso, também não dá certo. me mandaram 10 códigos de confirmação e com um segundo diz que expirou. tanto por E-mail quanto por cel</t>
+          <t>Comprei o produto Youclone no dia 28/08, no pix. Quando fui entrar no curso, não abre a área de membros e não consigo assistir o curso. Na minha área de membros só tem um curso que eu comprei faz tempo. Detalhes do Pedido Pedido: ***** Data: 28/08/2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/produto-nao-recebido-e-dificuldade-de-acesso-ao-material-digital-com-falha-no-reembolso-e-suporte-ineficaz_iOzRmbylQ4neQezT/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>pelo qual paguei n</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>pelo qual paguei n</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1473,7 +1477,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1491,24 +1495,28 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Boa noite. Fiz a compra de um produto na ultima quarta feira (26/08/20226) e até essa data eu não recebi o produto. Recebi o e-mail de confirmação do pagamento e um acesso pra fazer o download do material, mas não dá certo. Pra todo lugar que eles me enviam não dá certo. Falo com o pessoal do suporte e eles me deixam sem respostas. Só começam o atendimento. Pedi reembolso, também não dá certo. me mandaram 10 códigos de confirmação e com um segundo diz que expirou. tanto por E-mail quanto por cel</t>
+        </is>
+      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-por-indisponibilidade-do-curso-corselet-classico_kKh1cXRxKbVwJRHp/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/produto-nao-recebido-e-dificuldade-de-acesso-ao-material-digital-com-falha-no-reembolso-e-suporte-ineficaz_iOzRmbylQ4neQezT/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>e conseguiu acess</t>
+          <t>pelo qual paguei n</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>e conseguiu acess</t>
+          <t>pelo qual paguei n</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1534,35 +1542,31 @@
       <c r="G20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>R$ 20,89</t>
-        </is>
-      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/inconsistencias-na-contabilizacao-de-vendas-e-pagamentos-na-conta-cakto_KtH_3-H9eW4zj_bs/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-por-indisponibilidade-do-curso-corselet-classico_kKh1cXRxKbVwJRHp/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
+          <t>e conseguiu acess</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
+          <t>e conseguiu acess</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1588,31 +1592,35 @@
       <c r="G21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>R$ 20,89</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-3-pedidos-devido-a-arrependimento-e-insatisfacao-com-o-produtosite_KUDEd8s3eGajQ3-L/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/inconsistencias-na-contabilizacao-de-vendas-e-pagamentos-na-conta-cakto_KtH_3-H9eW4zj_bs/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>de seguran</t>
+          <t>um site hoje e quero solicitar o cancelam</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>de seguran</t>
+          <t>um site hoje e quero solicitar o cancelam</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1622,12 +1630,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1645,24 +1653,24 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-reembolso-de-pedido-com-codigo-de-transacao_poCcMMKbZVAkXZx9/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-3-pedidos-devido-a-arrependimento-e-insatisfacao-com-o-produtosite_KUDEd8s3eGajQ3-L/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>e a plataforma deveria no m</t>
+          <t>não conseguiu confirmar a distribuidora</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>e a plataforma deveria no m</t>
+          <t>não conseguiu confirmar a distribuidora</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1691,37 +1699,37 @@
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra nessa plataforma e não consigo pedir o reembolso pois a plataforma alega não vender produto. Quero o reembolso pois não gostei do produto e a plataforma deveria no mínimo disponibilizar essa função no site. Segundo a plataforma eu tenho que entrar em contato com o responsável do produto, como irei pedir o reembolso pois o dono do produto não responde. ***** Numero do pedido da minha compra  Reembolso negado por plataforma que alega não vender o produto.</t>
+          <t>À equipe de Relações Institucionais e Ouvidoria da Amazon Brasil. Venho por meio desta registrar uma reclamação formal e de urgência a respeito da minha conta de vendedor (Seller Central), suspensa desde o dia 07/02. O motivo alegado inicialmente para a suspensão foi a necessidade de validação da documentação de [Editado pelo Reclame Aqui] de suprimentos (fornecedores/distribuidores). A plataforma já me enviou uma notificação oficial por e-mail confirmando textualmente que toda a documentação so</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-por-plataforma-que-alega-nao-vender-o-produto_S-syATG5Z4eLNeZI/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/retencao-indevida-de-saldo-e-recusa-de-validacao-de-distribuidor-em-conta-de-vendedor-suspensa_P16RGZ09cZwpr2hu/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>de seguran</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Stalkeia</t>
+          <t>de seguran</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1731,7 +1739,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1742,11 +1750,7 @@
       <c r="G24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>R$ 401,40.</t>
-        </is>
-      </c>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -1755,26 +1759,22 @@
       <c r="J24" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>O produto prometia acesso a contas e mensagens do Instagram, mas na verdade entrega apenas um aplicativo que simula a interface do Instagram e cria conversas artificiais. Ou seja, trata-se de um serviço [Editado pelo Reclame Aqui], que não entrega o que anuncia. Eu testei com dois perfis diferentes e as mensagens são as mesmas, ou seja, [Editado pelo Reclame Aqui] e [Editado pelo Reclame Aqui]. Além disso, após um primeiro pagamento a plataforma vai nos induzindo a efetuar outras compras para co</t>
-        </is>
-      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/servico-editado-pelo-reclame-aqui-da-via-perfect-pay-com-promessa-editado-pelo-reclame-aqui_XI7_jZmAIuhQa5In/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/solicitacao-de-reembolso-de-pedido-com-codigo-de-transacao_poCcMMKbZVAkXZx9/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>e a plataforma deveria no m</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>e a plataforma deveria no m</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1807,28 +1807,28 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, Instagram e tiktok. Porém dentro da plataforma , fui informada que teria que pagar mais um valor para integração com as plataformas, informaram que esse valor é pagamento único, para as plataformas liberarem a integração ( não fica nada com eles). Como meu intuito é as postagens automáticas, comprei. Enviei o comprovante, como solicitado e aguardei o prazo para eles , entrar</t>
+          <t>Fiz uma compra nessa plataforma e não consigo pedir o reembolso pois a plataforma alega não vender produto. Quero o reembolso pois não gostei do produto e a plataforma deveria no mínimo disponibilizar essa função no site. Segundo a plataforma eu tenho que entrar em contato com o responsável do produto, como irei pedir o reembolso pois o dono do produto não responde. ***** Numero do pedido da minha compra  Reembolso negado por plataforma que alega não vender o produto.</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/reembolso-negado-por-plataforma-que-alega-nao-vender-o-produto_S-syATG5Z4eLNeZI/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>de postagem autom</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>de postagem autom</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1861,28 +1861,28 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por bastante tempo e disse ter efetuado o reembolso, coisa que eu não sei se aconteceu ou não, por que isso foi antes de ontem e lá na cakto ainda está como "pago" e não algo como "reembolso em andamento" ou coisa assim! Me disseram na última resposta que iam me mandar mensagem no contato cadastrado no reclame aqui, coisa que ainda não fizeram e o prazo pra reembolso é até am</t>
+          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, Instagram e tiktok. Porém dentro da plataforma , fui informada que teria que pagar mais um valor para integração com as plataformas, informaram que esse valor é pagamento único, para as plataformas liberarem a integração ( não fica nada com eles). Como meu intuito é as postagens automáticas, comprei. Enviei o comprovante, como solicitado e aguardei o prazo para eles , entrar</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>adquirido teria condi</t>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>adquirido teria condi</t>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1915,28 +1915,28 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Venho solicitar a contestação de uma compra realizada referente à contratação de uma estrutura montada para geração de retorno financeiro. A contratação foi realizada acreditando que o serviço/produto adquirido teria condições de funcionar conforme apresentado pelos responsáveis pela estrutura. O problema é que, após a contratação e a montagem das estruturas, o resultado esperado não aconteceu. Além do valor já pago pela aquisição do produto/estrutura, posteriormente fui informado de que seria n</t>
+          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por bastante tempo e disse ter efetuado o reembolso, coisa que eu não sei se aconteceu ou não, por que isso foi antes de ontem e lá na cakto ainda está como "pago" e não algo como "reembolso em andamento" ou coisa assim! Me disseram na última resposta que iam me mandar mensagem no contato cadastrado no reclame aqui, coisa que ainda não fizeram e o prazo pra reembolso é até am</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>dois cursos de idiomas</t>
+          <t>adquirido teria condi</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>dois cursos de idiomas</t>
+          <t>adquirido teria condi</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1969,21 +1969,337 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
+          <t>Venho solicitar a contestação de uma compra realizada referente à contratação de uma estrutura montada para geração de retorno financeiro. A contratação foi realizada acreditando que o serviço/produto adquirido teria condições de funcionar conforme apresentado pelos responsáveis pela estrutura. O problema é que, após a contratação e a montagem das estruturas, o resultado esperado não aconteceu. Além do valor já pago pela aquisição do produto/estrutura, posteriormente fui informado de que seria n</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>dois cursos de idiomas</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>dois cursos de idiomas</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
           <t>Fiz uma compra de dois cursos de idiomas, no caso Espanhol. Paguei pelos dois cursos via pi, porém só tive acesso a um curso, o outro aparece como acesso negado e não consigo acessar. Já entrei em contato com o suporte, porém o email retorna como email inválido. Entro em contato com o suporte para solicitar reembolso e ninguém me dá um retorno. Solicito devolução do valor, porém não tenho contato com ninguém da empresa. Acesso negado a curso de espanhol pago e dificuldade de contato com o suport</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>https://www.reclameaqui.com.br/cakto-pay/acesso-negado-a-curso-de-espanhol-pago-e-dificuldade-de-contato-com-o-suporte-para-reembolso_9d9eJH4OMC_ApZLR/</t>
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>aparece na perfect pay mas o mesmo n</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>APARECE NA PERFECT PAY MAS O MESMO N</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Fiz A COMPRA DE UM SERVIÇO NO QUAL É [Editado pelo Reclame Aqui] E O PRODUTO APARECE NA PERFECT PAY MAS O MESMO NÃO SE RESPONSABILIZA PELO CANCELAMENTO, ISSO É [Editado pelo Reclame Aqui]. IREI ACIONAR O PROCON. ID DA COMPRA: ***** VALOR: 37,90 Compra de serviço com promessa de [Editado pelo Reclame Aqui] e Perfect Pay se isenta de responsabilidade</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/compra-de-servico-com-promessa-de-editado-pelo-reclame-aqui-e-perfect-pay-se-isenta-de-responsabilidade_0DOgqsLTHMXBEQUg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>umgrama de karaoke e est</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>um programa de karaoke e est</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de um programa de karaoke e está dando conteúdo não encontrado paguei via pix. Conteúdo não encontrado</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/conteudo-nao-encontrado_eh2tS2q3T2WGSky_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>uma m</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>uma m</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de uma máscara coreana , fiz o pagamento no PIX e a empresa relatou que eu nao havia pago, eu ,logo a seguir enviei o comprovante pago e a partir daí,eles nao retornaram mais. Pagamento via PIX não reconhecido e falta de retorno da empresa após envio de comprovante.</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/pagamento-via-pix-nao-reconhecido-e-falta-de-retorno-da-empresa-apos-envio-de-comprovante_C6tRKpYDqejq7Cvf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>curso online capsulas gourmet e c</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>curso online capsulas gourmet e c</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/materiais-de-curso-online-de-capsulas-gourmet-e-capuccinos-nao-disponiveis_jlp3yz2MCVJGF1UT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>um curso no dia 01</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>um curso no dia 01</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/produto-nao-entregue_RxHp4cyuljYU2Wtj/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L28"/>
+  <autoFilter ref="A1:L34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2050,13 +2366,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -2065,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2100,13 +2416,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
@@ -2115,20 +2431,20 @@
         <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Educação / Marketing digital e low ticket</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>1</v>
@@ -2140,23 +2456,23 @@
         <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Educação / Marketing digital e low ticket</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
@@ -2354,7 +2670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2391,28 +2707,28 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>apostila de psicologia 2025</t>
+          <t>aparece na perfect pay mas o mesmo n</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>apostila de psicologia025</t>
+          <t>apostila de psicologia 2025</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -2421,13 +2737,13 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>aristocracy negócios digitais</t>
+          <t>apostila de psicologia025</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2436,13 +2752,13 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>cloakeuai</t>
+          <t>aristocracy negócios digitais</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -2457,7 +2773,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>comunidade knights club</t>
+          <t>cloakeuai</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2466,88 +2782,88 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>comunidade vsa</t>
+          <t>comunidade knights club</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>continua ativo</t>
+          <t>comunidade vsa</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>converza.io</t>
+          <t>continua ativo</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>códigos lucrativos</t>
+          <t>converza.io</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>curso online capsulas gourmet e c</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>de seguran</t>
+          <t>códigos lucrativos</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2556,13 +2872,13 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>dois cursos de idiomas</t>
+          <t>de postagem autom</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2571,13 +2887,13 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>e a plataforma deveria no m</t>
+          <t>de seguran</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2586,13 +2902,13 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>e conseguiu acess</t>
+          <t>dois cursos de idiomas</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2601,28 +2917,28 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>e ele nao chegou quero meu dinheiro de volta ra ad</t>
+          <t>e a plataforma deveria no m</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>e conseguiu acess</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2631,28 +2947,28 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>e ele nao chegou quero meu dinheiro de volta ra ad</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2667,7 +2983,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero</t>
+          <t>fábrica de low ticket</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2676,13 +2992,13 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
+          <t>interactive live</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2691,13 +3007,13 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>manuscrito dos milagres</t>
+          <t>low ticket do zero</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2706,13 +3022,13 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2727,7 +3043,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>manuscrito dos milagres</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2736,13 +3052,13 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>on line rj comercio varejista de acessorios ltda</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2751,58 +3067,58 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>pack canva</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>pelo qual paguei n</t>
+          <t>não conseguiu confirmar a distribuidora</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>ra ads previous slide next slide compartilhe resp</t>
+          <t>on line rj comercio varejista de acessorios ltda</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>retrato da sua alma gêmea</t>
+          <t>pack canva</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -2817,7 +3133,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>pelo qual paguei n</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -2826,13 +3142,13 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>ra ads previous slide next slide compartilhe resp</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2847,22 +3163,22 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
+          <t>retrato da sua alma gêmea</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>stalkeia</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -2871,52 +3187,142 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>validação cadastral: em análise</t>
+          <t>um curso e</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>youclone no dia 28</t>
+          <t>um curso no dia 01</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>um site hoje e quero solicitar o cancelam</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>uma m</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>umgrama de karaoke e est</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>validação cadastral: em análise</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
           <t>zap radar</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>8</v>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -523,12 +523,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>perfect academy</t>
+          <t>stalkeia</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Perfect Academy</t>
+          <t>Stalkeia</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -543,46 +543,50 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria / Cursos online</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>fria</t>
+          <t>morna</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>R$ 87,00</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Comprei um curso na perfect academy, mais o curso veio incompleto, fui tentar pedir meu reembolso, onde me deparei sem suporte algum, não tem a opção de fazer o pedido do reembolso, então fazer meu reembolso na mesma forma de pagamento, por pix, isso não se faz o cliente compra um item e vcs enviar outro RA Ads</t>
+          <t>Realizei a compra do produto &amp;#39;Stalkea AI&amp;#39; intermediado pela plataforma Perfect Pay. O produto trata-se de uma [Editad... Exijo estorno de compra de produto [Editado pelo Reclame Aqui] intermediado pela Perfect Pay</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/curso-incompleto-e-falta-de-suporte-para-reembolso-na-perfect-academy_xfFtbFJD4cncefLz/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/exijo-estorno-de-compra-de-produto-editado-pelo-reclame-aqui-intermediado-pela-perfect-pay_dDCHm8bcfbJi5cGU/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>produto malu</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Produto Malu</t>
+          <t>Método Atlas</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -597,7 +601,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas / Aplicativos</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -606,37 +610,37 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Realizei a compra do produto Malu pela Perfect Pay, acreditando que, após a compra, teria acesso ao produto conforme as informações apresentadas durante a oferta. Porém, após realizar o pagamento, descobri que é necessário fazer um novo pagamento para conseguir ativar o produto, algo que não ficou claro para mim no momento da compra. Essa situação me deixou bastante insatisfeito, pois se eu soubesse que seria necessário pagar novamente para utilizar/ativar o produto, provavelmente não teria real</t>
+          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desa... Clonado cartão</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/produto-malu-exige-novo-pagamento-para-ativacao-solicito-cancelamento-e-reembolso_EGQhjKMbfuFFizV7/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/clonado-cartao_bkNp4YTe6nDKqL90/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>aplicativo n</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>aplicativo N</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -660,7 +664,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
@@ -673,39 +677,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Eu adquiri uma compra pela [Editado pelo Reclame Aqui] prometendo acesso a um app pago e após pagar o aplicativo simplesmente pede um crédito de ***** reais e volta pra tela inicial. Quero meu dinheiro de volta. O pix foi de ***** pq adquiri as redes sociais . RA Ads</t>
+          <t>Quero solicitar um reembolso, pois eu comprei um produto digital, já solicitei o suporte do Produtor, mas não me deram respos... Solicitação de reembolso por produto digital não respondido pelo produtor e suspeita de [Editado pelo Reclame Aqui].</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/cobranca-indevida-e-solicitacao-de-estorno-apos-compra-de-aplicativo_k54KbhcZ8MWgLTn0/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-reembolso-por-produto-digital-nao-respondido-pelo-produtor-e-suspeita-de-editado-pelo-reclame-aqui_4rad2Noh-3EVPiq-/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>mentoria nova profissão</t>
+          <t>plataforma tikspy pelo valor de r</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Mentoria Nova Profissão</t>
+          <t>plataforma TikSpy pelo valor de R</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria / Mentoria</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -718,7 +722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>R$ 297,00,</t>
+          <t>R$ 360,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -731,24 +735,24 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Solicitei o reembolso dentro do prazo legal de garantia pela própria plataforma Cakto, mas fui orientado a tratar diretamente com o produtor. Ocorre que o e-mail de contato fornecido pela própria Cakto é inválido (retorna erro de Postmaster informando que o endereço não existe), e o produtor Gustavo Castro não responde às mensagens enviadas pelo WhatsApp e ignorou minhas dúvidas sobre o conteúdo. O motivo do cancelamento é a propaganda enganosa e divergência de funcionalidade: Antes da compra, p</t>
+          <t>No dia 24/08/2026 adquiri a plataforma TikSpy pelo valor de R$ 360,24Após acessar a plataforma, concluí que ela não... Dificuldade em cancelar compra e solicitar reembolso de plataforma digital</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reclamacao-sobre-mentoria-nova-profissao-propaganda-enganosa-e-falha-na-intermediacao-de-reembolso-pela-cakto-pay_WVFYGdZmjsyF9dv0/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/dificuldade-em-cancelar-compra-e-solicitar-reembolso-de-plataforma-digital_MNsF1CWfu9nJFQaI/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>turminha alfakids</t>
+          <t>mentoria nova profissão</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Turminha Alfakids</t>
+          <t>Mentoria Nova Profissão</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Educação infantil / Materiais didáticos</t>
+          <t>Educação e consultoria / Mentoria</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -772,7 +776,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
@@ -781,28 +785,24 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra da turminha Alfakids de 2750 atividades e não recebi,o email que aparece como suporte não responde RA Ads</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/compra-nao-recebida-e-falta-de-resposta-do-suporte_yWkDvnrLPMHo7aTz/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-mentoria-nova-profissao-propaganda-enganosa-e-falha-na-intermediacao-de-reembolso-pela-cakto-pay_WVFYGdZmjsyF9dv0/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>um curso</t>
+          <t>auks bot</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>um curso</t>
+          <t>Auks Bot</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -828,7 +828,11 @@
       <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>R$ 277,00,</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -837,22 +841,26 @@
       <c r="J7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o produto Auks Bot, pelo valor de R$ 277,00, com pagamento processado pela Perfect Pay.Em 27/08/2026, ainda... Reclamação sobre reembolso negado pela Perfect Pay para o produto Auks Bot</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-de-curso-nao-realizado-apos-solicitacao-dentro-do-prazo_ktvLpzB4DAj5K-_J/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-reembolso-negado-pela-perfect-pay-para-o-produto-auks-bot_KqYsYdFXN1z0_dI5/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>directspeed</t>
+          <t>curso de mandarim</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Directspeed</t>
+          <t>Curso de Mandarim</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -867,7 +875,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de produtividade / Assinatura</t>
+          <t>Educação / Idiomas</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -885,33 +893,29 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Quero cancelar a assinatura de uma ferramenta chamada directspeed meu e-mail é ***** já pedi no e-mail da cakto de compradores e não fui respondido, entrei com o produtor que iria ver com a equipe sendo que é só apertar um botão pra cancelar Vou deixar em anexo o e-mail enviado e as conversas no WhatsApp para cancelamento, só quero o cancelamento para não ser cobrado novamente. Fico no aguardo ! RA Ads</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-de-assinatura-da-ferramenta-directspeed-nao-respondida_G-frs9kFEKvabVpn/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-no-face-book-compra-de-curso-de-mandarim-2099-02092026-190111_uKMKomnheob91qjy/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>curso de mandarim</t>
+          <t>e solicita</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Curso de Mandarim</t>
+          <t>e solicita</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -921,7 +925,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Educação / Idiomas</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -941,15 +945,5069 @@
       <c r="J9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra pela cakto Detalhes do PedidoPedido: *****Data: 02/09/2026Produto: 100 Remédios Naturais ... Reclamação sobre não recebimento de produto e solicitação de estorno do valor pago via PIX.</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/editado-pelo-reclame-aqui-no-face-book-compra-de-curso-de-mandarim-2099-02092026-190111_uKMKomnheob91qjy/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-nao-recebimento-de-produto-e-solicitacao-de-estorno-do-valor-pago-via-pix_19VMI-vOfIlR0IIm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>comunidade mvz no dia 27</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Comunidade MVZ no dia 27</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>R$ 248,89,</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra do produto Comunidade MVZ no dia 27/08/2026, no valor de R$ 248,89, através da plataforma Cakto. Dentro do ... Cliente solicita cancelamento e reembolso de curso online após ser direcionado entre plataforma e produtor.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-solicita-cancelamento-e-reembolso-de-curso-online-apos-ser-direcionado-entre-plataforma-e-produtor_7fIx89P-1ZpAApHx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>na ultima quarta feira</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>na ultima quarta feira</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Boa noite. Fiz a compra de um produto na ultima quarta feira (26/08/20226) e até essa data eu não recebi o produto.Receb... Produto não recebido e dificuldade de acesso ao material digital, com falha no reembolso e suporte ineficaz.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-recebido-e-dificuldade-de-acesso-ao-material-digital-com-falha-no-reembolso-e-suporte-ineficaz_iOzRmbylQ4neQezT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ia academy</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>IA Academy</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>R$ 197,99,</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Realizei no dia 01/09/2026 uma compra através da plataforma Cakto, referente ao produto IA Academy, no valor de R$ 197,99, pa... Solicitação de cancelamento e reembolso de curso online não respondido pelo produtor.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-reembolso-de-curso-online-nao-respondido-pelo-produtor_ddqfFY8ufw0eiA3F/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>comunidade knights club</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>COMUNIDADE KNIGHTS CLUB</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Comunidades / Mentoria de negócios</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO DE REEMBOLSO NÃO CUMPRIDA PAGAMENTO VIA PIXNo dia 21/08/2026, realizei a compra da COMUNIDADE KNIGHTS ... Reembolso de compra via Pix não realizado após solicitação dentro do prazo legal.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-de-compra-via-pix-nao-realizado-apos-solicitacao-dentro-do-prazo-legal_w1bmesmQpVhI5h0M/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>low ticket do zero 2.0 no dia 30</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Low Ticket do Zero 2.0 no dia 30</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra do produto Low Ticket do Zero 2.0 no dia 30/08/2026. Após acessar o produto, constatei que ele não atendeu ... Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>chamado f</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>chamado F</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Dia 27/08/2026 comprei um produto chamado Fábrica Viral, não recebi o material no e-mail e o produtor não respondeu a minha t... Comprei um produto, não recebi e não consigo pedir reembolso</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/comprei-um-produto-nao-recebi-e-nao-consigo-pedir-reembolso_kESf7mBZQ-lYpUvb/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>comunidade vsa</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>COMUNIDADE VSA</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Marketing / Comunidades de negócios</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>R$ 248,89.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-de-compra-com-erro-de-saldo-na-conta-do-vendedor_e5d-tH3gUGahNktM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>retrato da sua alma gêmea</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Retrato da Sua Alma Gêmea</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Arte personalizada / IA generativa</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Olá, equipe da Cakto Pay,No dia 28/08/2026, realizei a compra do produto &amp;quot;Retrato da Sua Alma Gêmea&amp;quot; (Código do Ped... [Editado pelo Reclame Aqui] e solicitação de estorno para produto &amp;quot;Retrato da Sua Alma Gêmea&amp;quot;</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-e-solicitacao-de-estorno-para-produto-retrato-da-sua-alma-gemea_H8ihRLGIEQMZ9WSb/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>perfect academy</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Perfect Academy</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria / Cursos online</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Comprei um curso na perfect academy, mais o curso veio incompleto, fui tentar pedir meu reembolso, onde me deparei sem suport... Curso incompleto e falta de suporte para reembolso na Perfect Academy</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/curso-incompleto-e-falta-de-suporte-para-reembolso-na-perfect-academy_xfFtbFJD4cncefLz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>produto malu</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Produto Malu</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas / Aplicativos</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Título: Produto Malu não correspondeu às minhas expectativas e exige novo pagamento para ativaçãoRealizei a compra ... Produto Malu exige novo pagamento para ativação, solicito cancelamento e reembolso.</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-malu-exige-novo-pagamento-para-ativacao-solicito-cancelamento-e-reembolso_EGQhjKMbfuFFizV7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>aplicativo</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>aplicativo</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Eu adquiri uma compra pela [Editado pelo Reclame Aqui] prometendo acesso a um app pago e após pagar o aplicativo simplesmente... Cobrança indevida e solicitação de estorno após compra de aplicativo</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-solicitacao-de-estorno-apos-compra-de-aplicativo_k54KbhcZ8MWgLTn0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>tikedit pela perfectpay</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>TikEdit pela PerfectPay</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/recusa-de-reembolso-em-renovacao-automatica-de-produto-tikedit-pela-perfectpay_7DczqrMSjVJHqp26/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>vendido pela appluna.net</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>vendido pela Appluna.net</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>A referida empresa, alega ser uma plataforma de gerenciamento de pagamentos online que informa não ter responsabilidade sobre... Perfectpay cobra por serviço, mas não resolve problemas de acesso ao produto vendido pela Appluna.net</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perfectpay-cobra-por-servico-mas-nao-resolve-problemas-de-acesso-ao-produto-vendido-pela_a5_1eWXf4MZ6sZZ7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>aparece na perfect pay mas o mesmo n</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>APARECE NA PERFECT PAY MAS O MESMO N</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Fiz A COMPRA DE UM SERVIÇO NO QUAL É [Editado pelo Reclame Aqui] E O PRODUTO APARECE NA PERFECT PAY MAS O MESMO NÃO SE RESPO... Compra de serviço com promessa de [Editado pelo Reclame Aqui] e Perfect Pay se isenta de responsabilidade</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-com-promessa-de-editado-pelo-reclame-aqui-e-perfect-pay-se-isenta-de-responsabilidade_0DOgqsLTHMXBEQUg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>receb... propaganda enganosa</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>receb... Propaganda enganosa</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/propaganda-enganosa_zOGr7sPQQhH7ROqM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>plataforma home office</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma Home Office</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Solicito o cancelamento e o reembolso do valor pago pelo produto Plataforma Home Office, vinculado ao e-mail ***** . O produt... Solicitação de cancelamento e reembolso de Plataforma Home Office por propaganda enganosa.</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-plataforma-home-office-por-propaganda-enganosa_Z3FnnwZ03NBXKWFQ/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>de postagem autom</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>de postagem autom</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, In... Reclamação sobre produto de postagem automática com cobranças adicionais, sem retorno do suporte , sem liberação do prometido e com acesso restrito ao conteúdo,e falta de reembolso.</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>acesso a conversas do instagram n</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>acesso a conversas do Instagram n</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Crescimento em redes sociais</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-acesso-a-conversas-do-instagram-nao-realizada-e-solicitacao-de-reembolso_bEr04z5n0qvNdmJf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>códigos lucrativos</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Códigos Lucrativos</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>zap radar</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ZAP Radar</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de espionagem / WhatsApp</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o ... Solicitação de estorno de compra no site ZAP Radar por não recebimento de relatório.</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>fica saindo e entrando sozinho</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>fica saindo e entrando sozinho</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-e-nao-recebi_IgLy-Z3TgKa5WfbK/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>chamado protocolo black digital e comprei</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>chamado Protocolo Black Digital e comprei</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Eu comprei um produto chamado Protocolo Black Digital e comprei dois order bumps, e o produto é horrível, na hora de eu pedir... Impossibilidade de solicitar reembolso para o produto Protocolo Black Digital e order bumps.</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/impossibilidade-de-solicitar-reembolso-para-o-produto-protocolo-black-digital-e-order-bumps_KUmvlWU2BBaqoLGc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>aplicativo viewerspy com tr</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>aplicativo ViewerSpy com tr</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de aplicativo ViewerSpy com três pagamentos, mas se tratava de [Editado pelo Reclame Aqui], quero meu dinheiro... [Editado pelo Reclame Aqui] em aplicativo ViewerSpy com cobrança indevida, solicitação de [Editado pelo Reclame Aqui].</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-viewerspy-com-cobranca-indevida-solicitacao-de-editado-pelo-reclame-aqui_4jVYpRQh7FZ9NsuM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>servi</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>servi</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra me garantindo acesso a fotos e conversas de um WhatsApp meu mesmo que perdi acesso, mas fui enganado paguei tu... Compra de serviço para recuperação de WhatsApp que direciona para página de curso.</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-para-recuperacao-de-whatsapp-que-direciona-para-pagina-de-curso_9jbLXBtTk54j7-aK/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>inexistente</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>inexistente</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-editado-pelo-reclame-aqui-e-solicitacao-de-editado-pelo-reclame-aqui-com-base-no-direito-de-arrependimento_SenuNicKKSMOvgEa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>uma ferramenta de automa</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>uma ferramenta de automa</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-ferramenta-de-automacao-nao-recebida_3ia2l_X9I98IiU5Q/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>simplesmente n</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>simplesmente n</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de um sistema multijogos da Retrogame Ramos, porém o produto simplesmente não funcionou. Solicitei o reembolso e... Reclamação sobre sistema multijogos não funcional e falta de reembolso pela Retrogame Ramos</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-sistema-multijogos-nao-funcional-e-falta-de-reembolso-pela-retrogame-ramos_yXzSmLa6zWMj18Hq/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>no valor de 97 reais que nao gostei pedi</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>no valor de 97 reais que nao gostei pedi</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>[Editado pelo Reclame Aqui]. comprei um produto no valor de 97 reais que nao gostei pedi o reembolso e ninguem resolve nada m... Reclamação sobre propaganda enganosa e dificuldade em obter reembolso de produto.</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-propaganda-enganosa-e-dificuldade-em-obter-reembolso-de-produto_NexaAcyAJfkO5zUN/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>quemetia trazer minha conta do free f</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>que prometia trazer minha conta do free f</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Quero reembolso do meu dinheiro, comprei um produto que prometia trazer minha conta do free fire de volta, mais era tudo [Edi... Produto de Free Fire prometia recuperar conta, mas era [Editado pelo Reclame Aqui] e cliente pede reembolso.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-de-free-fire-prometia-recuperar-conta-mas-era-editado-pelo-reclame-aqui-e-cliente-pede-reembolso_6E9DzuuICeSs7-BW/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>spygram</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Spygram</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-reembolso-de-pagamentos-via-pix-para-o-programa-spygram-identificado-como-editado-pelo-reclame-aqui_tx5DRYfAycgJL_5j/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>um curso de arais amador paguei e n</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>um curso de arais amador paguei e n</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um curso de arais amador paguei e não recebi segue comprovante de pagamento Fui vítima de [Editado pelo Reclame Aqui]</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/fui-vitima-de-editado-pelo-reclame-aqui_eaEOE7rI3vDh1NKM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>tudo dentro do prazo tudo certinho e ate</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>tudo dentro do prazo tudo certinho e ate</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso_3QFTCw6-Ygo025v1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>dois aplicativo e n</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>dois aplicativo e n</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>R$ 27,90</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Bom dia ! Fiz uma compra de dois aplicativo e não recebi o aplicativo, no valor de R$ 27,90 e outro de R$ 19,00 às 16:35 h no... Compra de aplicativos não recebidos, solicitação de reembolso.</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-nao-recebidos-solicitacao-de-reembolso_IVdC0jac41EFjNhF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>espia f</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>espia f</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o app espia fácil pro e não me deram o acesso. Quero reembolso Cair em um [Editado pelo Reclame Aqui]</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cair-em-um-editado-pelo-reclame-aqui_3GiaHX5kQ4C877x9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>um aplicativo de monitoramento pelo an</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>um aplicativo de monitoramento pelo an</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um aplicativo de monitoramento pelo anúncio no YouTube paguei 46.90 e levei um [Editado pelo Reclame Aqui] ... [Editado pelo Reclame Aqui] em aplicativo de monitoramento cliente solicita estorno de valor pago por produto não funcional.</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-de-monitoramento-cliente-solicita-estorno-de-valor-pago-por-produto-nao-funcional_nGia5bRqbVr80nh-/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>um vendedor que usa os servi</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>um vendedor que usa os servi</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Efetuei uma compra de um vendedor que usa os serviços da perfect pay para pagamentos. O vendedor não enviou acesso ao produto... Reclamação sobre produto não entregue e solicitação de estorno de valor pago através da Perfect Pay.</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-nao-entregue-e-solicitacao-de-estorno-de-valor-pago-atraves-da-perfect-pay_87chbXy48Qb7cTPa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>no ... reembolso dentro do prazo</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>no ... reembolso dentro do prazo</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Solicitei reembolso dentro do prazo, mas não consigo contato com o vendedorAdquiri através da Perfect Pay um produto no ... reembolso dentro do prazo, mas não consigo contato com o vendedor após compra de produto com conteúdo enganoso.</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-dentro-do-prazo-mas-nao-consigo-contato-com-o-vendedor-apos-compra-de-produto-com-conteudo-enganoso_msDSOKrJ-W3coXfK/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>grupo vip</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>grupo VIP</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Bem, eu fiz uma compra na segunda-feira de um grupo vip do js e não estou satisfeito, quero o meu reembolso, ja vou deixar es... Reembolso negado e falta de contato do suporte após compra de grupo VIP</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-negado-e-falta-de-contato-do-suporte-apos-compra-de-grupo-vip_l-3zMo_MYaiaFQbn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>e n</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>e n</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Serviços financeiros / Pix</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um produto e não recebi, alegam que não foi pago, já reclamei várias vezes com o vendedor e até agora ele n... Produto não recebido e vendedor alega falta de pagamento, sem resolução.</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-nao-recebido-e-vendedor-alega-falta-de-pagamento-sem-resolucao_4ypAxIw4TPAzgFfj/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>de baixa qualidade</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>de baixa qualidade</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra aonde prometia uma reza sagrada que faz prosperar e abrir caminhos, mas a reza não foi feita e me cobraram 3 v... Cobrança indevida e produto de baixa qualidade (PDF de IA) em vez de reza prometida.</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-produto-de-baixa-qualidade-pdf-de-ia-em-vez-de-reza-prometida_S22Bk6Gf4HfO6zVF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>um painel e n</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>um painel e n</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um painel e não funcionou [Editado pelo Reclame Aqui] Solicito reembolso 19.99 [Editado pelo Reclame Aqui]</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui_5xPVEL37uCq2Nl_s/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>um curso chamado geniun shop</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>um curso chamado Geniun Shop</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Adquiri um curso chamado Geniun Shop , em 2 de abril de 2026 , fiZ apenas as primeiras aulas, e agora quando resolvi voltar p... Perda de acesso ao curso Geniun Shop após pagamento, sem retorno do suporte.</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perda-de-acesso-ao-curso-geniun-shop-apos-pagamento-sem-retorno-do-suporte_a6tTJhax8GBOg4xh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>onde dizia que tinha v</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>onde dizia que tinha v</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Comprei um produto onde dizia que tinha vários fornecedores de roupas no Brasil..mas não tinha o que eu eu queria .por isso q... Reclamação sobre produto com fornecedores de roupas limitados e solicitação de reembolso.</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-com-fornecedores-de-roupas-limitados-e-solicitacao-de-reembolso_H7FXu4ussEtUSJQC/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>com defeito e solicita</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>com defeito e solicita</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra no Blackxitoficial (meu Gmail é *****). Meu CPF: *****, no valor de 31 reais. O Painel chegou, mas não funcion... Produto com defeito e solicitação de reembolso</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-com-defeito-e-solicitacao-de-reembolso_GgMl5lRE9VZtuHoJ/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>na plataforma e n</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>na plataforma e n</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>comprei um produto na plataforma e não gostei, quero meu reembolso, foi comprado no pix:Código da compra: ***** Cliente deseja reembolso de aquecedor comprado via Pix por não ter gostado do produto.</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cliente-deseja-reembolso-de-aquecedor-comprado-via-pix-por-nao-ter-gostado-do-produto_2qo_Zk1Eh3qTNpQy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>nessa plataforma</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>nessa plataforma</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Verifiquei a compra de um produto nessa plataforma, solicitei o reembolso junto a produtora do produto e não consegui retorno... Reembolso não resolvido pela plataforma após contato com produtora e cancelamento de cartão.</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-nao-resolvido-pela-plataforma-apos-contato-com-produtora-e-cancelamento-de-cartao_P1PpJ-yUSNmPIVUp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>em um site na internet e ao abrir o email</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>em um site na internet e ao abrir o email</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Serviços financeiros / Pix</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Realizei uma compra de um produto em um site na internet e ao abrir o email enviado me cobraram outra taxa que não estava com... Cobrança de taxa adicional não combinada e falta de acesso ao produto comprado.</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-de-taxa-adicional-nao-combinada-e-falta-de-acesso-ao-produto-comprado__chfFQTX8pupMWB5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>tomei</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Tomei</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tomei-editado-pelo-reclame-aqui_PCEkQCMzbA-5dwgy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>no qual n</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>no qual n</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um produto no qual não corresponde a minha expectativa , então solicito o estorno do meu valor. Email: ****... Solicitação de estorno por produto não correspondente à expectativa</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-por-produto-nao-correspondente-a-expectativa_jZ-08RI4TwV-ynQ4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>um grupo vip no dia 20</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>um grupo vip no dia 20</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Olá, fiz uma compra de um grupo vip no dia 20/08 e dia 23/08 tentei fazer o cancelamento, mas o vendedor ***** - operações nã... Tentativa de cancelamento de grupo VIP e impossibilidade de contato com o vendedor</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tentativa-de-cancelamento-de-grupo-vip-e-impossibilidade-de-contato-com-o-vendedor_SkOpE6e5RhZv8KIr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>turminha alfakids</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Turminha Alfakids</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Educação infantil / Materiais didáticos</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra da turminha Alfakids de 2750 atividades e não recebi,o email que aparece como suporte não responde Compra não recebida e falta de resposta do suporte</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-nao-recebida-e-falta-de-resposta-do-suporte_yWkDvnrLPMHo7aTz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>um curso</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>um curso</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-de-curso-nao-realizado-apos-solicitacao-dentro-do-prazo_ktvLpzB4DAj5K-_J/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>directspeed</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Directspeed</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de produtividade / Assinatura</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-da-ferramenta-directspeed-nao-respondida_G-frs9kFEKvabVpn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>cortes do marques</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Cortes do Marques</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Estou há quase 1 mês tentando cancelar a assinatura do produto Cortes do Marques, adquirido por meio da Cackto, mas até o mom... Cackto não realiza cancelamento de assinatura mesmo após várias solicitações</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cackto-nao-realiza-cancelamento-de-assinatura-mesmo-apos-varias-solicitacoes_WEDpJ2MDQNCpB9xD/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>umgrama de karaoke e est</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>um programa de karaoke e est</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de um programa de karaoke e está dando conteúdo não encontrado paguei via pix. Conteúdo não encontrado</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/conteudo-nao-encontrado_eh2tS2q3T2WGSky_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>uma m</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>uma m</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de uma máscara coreana , fiz o pagamento no PIX e a empresa relatou que eu nao havia pago, eu ,logo a seguir ... Pagamento via PIX não reconhecido e falta de retorno da empresa após envio de comprovante.</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-reconhecido-e-falta-de-retorno-da-empresa-apos-envio-de-comprovante_C6tRKpYDqejq7Cvf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>curso online capsulas gourmet e c</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>curso online capsulas gourmet e c</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/materiais-de-curso-online-de-capsulas-gourmet-e-capuccinos-nao-disponiveis_jlp3yz2MCVJGF1UT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>um curso no dia 01</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>um curso no dia 01</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue_RxHp4cyuljYU2Wtj/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>diferente do anunciado e a plataforma n</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>diferente do anunciado e a plataforma n</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/vendedor-entregou-produto-diferente-do-anunciado-e-a-plataforma-nao-resolve_vkGIXT8UU80pbQbc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>chegou faltando conte</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>chegou faltando conte</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra por lá, produto chegou faltando conteúdo, entro em contato com eles e ZERO atendimento, preciso fazer o estorn... Produto com conteúdo faltante e falta de atendimento para estorno</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-com-conteudo-faltante-e-falta-de-atendimento-para-estorno_S6A780k9_99Ofap-/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>um curso na plataforma deles</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>um curso na plataforma deles</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-estorno-de-curso-online-com-ma-qualidade-e-falta-de-resposta_rDQ1eDeZL9eCjgqm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>auto live shop</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Auto Live Shop</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra do produto Auto Live Shop, porém, após utilizar o produto, constatei que ele não atendeu às minhas expectat... Solicitação de reembolso para produto Auto Live Shop não processada pela plataforma Cakto</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-para-produto-auto-live-shop-nao-processada-pela-plataforma-cakto_Zejb3D4JhCq2o48c/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>pelo pouco que testei</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>pelo pouco que testei</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>R$ 197,99.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o Plano Starter mensal da Cloakby por R$ 197,99. O produto pelo pouco que testei é excelente. Porém, não atendeu as m... Reclamação Sobre Oferta da Cloakby: propaganda enganosa e péssimo atendimento ao solicitar reembolso</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-oferta-da-cloakby-propaganda-enganosa-e-pessimo-atendimento-ao-solicitar-reembolso_DS552Q4NU1VCy-bp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>uma assinatura do site copie</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>uma assinatura do site copie.ai</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>R$ 97,00,</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra de uma assinatura do site copie.ai, no dia 30 de agosto de 2026, às 17h38min, no valor de R$97,00, no site ... Assinatura Copie.ai não liberada após compra e sem retorno do suporte.</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/assinatura-nao-liberada-apos-compra-e-sem-retorno-do-suporte__RpqyPU88WZJtxd1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>pois n</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>pois n</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra mas não gostei do produto pois não atingiu minhas espectativas solicito o reembolso pois está no prazo de gara... Solicitação de reembolso por produto que não atendeu às expectativas dentro do prazo de garantia.</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-que-nao-atendeu-as-expectativas-dentro-do-prazo-de-garantia_4ccUExOzKRUFA4MT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>dois cursos de idiomas</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>dois cursos de idiomas</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de dois cursos de idiomas, no caso Espanhol. Paguei pelos dois cursos via pi, porém só tive acesso a um curso,... Acesso negado a curso de espanhol pago e dificuldade de contato com o suporte para reembolso.</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/acesso-negado-a-curso-de-espanhol-pago-e-dificuldade-de-contato-com-o-suporte-para-reembolso_9d9eJH4OMC_ApZLR/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>um site hoje e quero solicitar o cancelam</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>um site hoje e quero solicitar o cancelam</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>fiz uma compra de um site hoje e quero solicitar o cancelamento e direito a arrependimento dentro de 7 dias, fiz um pedido ma... Solicitação de cancelamento e estorno de 3 pedidos devido a arrependimento e insatisfação com o produto/site.</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-3-pedidos-devido-a-arrependimento-e-insatisfacao-com-o-produtosite_KUDEd8s3eGajQ3-L/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por... Reclamação sobre reembolso de mentoria não processado e falta de suporte</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>estrutura para gera</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>estrutura para gera</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o produto Youclone no dia 28/08, no pix.Quando fui entrar no curso, não abre a área de membros e não consig... Cliente não consegue acessar área de membros do curso Youclone e relata falta de suporte.</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>oduto</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>o produto</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Adquiri o produto &amp;quot;Combo Black&amp;quot; do Gustavo de Castro e recebi um e-mail de aprovação de compra sem acesso ao produt... Cliente não tem acesso ao produto &amp;#x27;Combo Black&amp;#x27; após aprovação de compra e não obtém resposta do suporte.</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-tem-acesso-ao-produto-combo-black-apos-aprovacao-de-compra-e-nao-obtem-resposta-do-suporte_na5373f4sUAHpMsE/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>um curso de ia nao gostei do curso e dent</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>um curso de IA nao gostei do curso e dent</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>fiz uma compra de um curso de IA nao gostei do curso e dentro do prazo de 7 dias solicitei o reembolso pelo email que disponi... Estorno</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/estorno_hMRVrko0Dz8fVqsF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>cuja cobran</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>cuja cobran</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-mensal-nao-efetivada-pela-plataforma-cakto_rOS_H0sA8Ne2Yb4r/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>apostila de psicologia 2025</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Apostila de Psicologia 2025</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Educação / Concursos e certificações</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico.Já entrei em contato por e-mail,... Apostila de Psicologia 2025 não abre e cliente não obtém retorno sobre compra online.</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>fábrica de low ticket</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Fábrica de Low Ticket</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Educação / Marketing digital e low ticket</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Olá,Solicito o reembolso da compra da Fábrica de Low Ticket.Adquiri o curso com base na promessa apresent... Reembolso solicitado por propaganda enganosa sobre suporte individual no curso Fábrica de Low Ticket</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>incompleto dentro da garantia</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>incompleto dentro da garantia</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Gostaria do reembolso dos seguintes produtos que comprei, está dentro do prazo de garantia de 7 dias.Email de Compra: **... Solicitação de reembolso por produto incompleto dentro da garantia</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-incompleto-dentro-da-garantia_DBUjl2QuaruN_QYD/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>mas n</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>mas n</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-me-respondem_ddIIs2OseJhlXI2v/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>de streaming n</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>de streaming n</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Streaming e entretenimento</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-desacordo-comercial-por-servico-de-streaming-nao-recebido-e-falta-de-contato-do-vendedor_xHL_Rnpj7hKZ3vjT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>que eu comprei na plataforma cakto ..o pr</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>que eu comprei na plataforma Cakto ..o pr</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Estou tentando cancelar um produto que eu comprei na plataforma Cakto ..o produto que eu comprei foi calcula chef app não es... Não consigo cancelar o produto Calcula Chef App e não recebo retorno da Cakto.</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-cancelar-o-produto-calcula-chef-app-e-nao-recebo-retorno-da-cakto_mwF3xbe9PnLeIpH4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>um curso na sexta feira e n</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>um curso na sexta feira e n</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>fiz uma compra de um curso na sexta feira e não recebi, também pelo chat de suporte não tenho retorno. Quero o reembolso, poi... Curso não recebido e falta de retorno do suporte, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-nao-recebido-e-falta-de-retorno-do-suporte-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_KD9yrBbG0QhwORjs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>uma planilha e n</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>uma planilha e n</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-suporte_245GAIgR4SjdP8m1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>um aplicativo</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>um aplicativo</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo ... Reclamação sobre aplicativo não funcional e falta de resposta do suporte para reembolso.</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>material de fonoaudiologia e n</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>material de fonoaudiologia e n</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de material de fonoaudiologia e não no momento de baixar o material era mal feito, a fonoaudióloga sequer exis... Material de fonoaudiologia de má qualidade e recusa de reembolso pela Cacto.</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/material-de-fonoaudiologia-de-ma-qualidade-e-recusa-de-reembolso-pela-cacto_zjP5uaGFy2s7z7ZP/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>pela cakto e logo realizei o pedido de re</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>pela cakto e logo realizei o pedido de re</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de um produto pela cakto e logo realizei o pedido de reembolso, porem sem sucesso, pois a plataforma dar erro: &amp;... Erro ao tentar solicitar reembolso de produto na Cakto</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/erro-ao-tentar-solicitar-reembolso-de-produto-na-cakto_ZhxbaEfvn9crLs7c/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>programa n</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>programa n</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra online e o programa não funcionou durante dois dias comecei a enviar para o produtor e para empresa Catho o pe... Reembolso não efetuado e falta de resposta da Catho e do produtor após compra de programa não funcional.</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-nao-efetuado-e-falta-de-resposta-da-catho-e-do-produtor-apos-compra-de-programa-nao-funcional_2BTWhdCr7obnyw-X/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-de-mentoria-nao-encontrada-e-falta-de-suporte-da-cakto-e-do-vendedor_Bt44ofl5iW09TC9d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>com defeito</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>com defeito</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>fiz a comprar de um produto , o produto não rodou no meu pc pedi o reembolso e mandaram falar com o produtor , mandei mensage... Reembolso negado e contato com o produtor indisponível após compra de produto com defeito</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-negado-e-contato-com-o-produtor-indisponivel-apos-compra-de-produto-com-defeito_JT9yPhOIhMRefinl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>frequência da vinci</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Frequência da Vinci</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Saúde / Tratamentos alternativos</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra por impulso,de um programa de cura do zumbido no ouvido e gostaria de cancelar e ter o extorno do valor pago p... Solicitação de cancelamento e estorno de programa de cura de zumbido</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-programa-de-cura-de-zumbido_T3cY3B6mIP4BEv_Y/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>da vav</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>da Vav</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>**Produto não entregue e criador não responde solicito reembolso**Realizei a compra de um produto da Vavá Aca... Produto não entregue e criador não responde, solicito reembolso</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue-e-criador-nao-responde-solicito-reembolso_605Q8ntQ-aQlegi3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>digitalcessada pela cakto</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>digital processada pela Cakto</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-em-compra-de-produto-digital-processada-pela-cakto-com-editado-pelo-reclame-aqui-e-nao-entrega_HJtQooCkVBEfTtMB/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>converza.io</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Converza.io</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Chatbots / Automação de mensagens</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/exijo-reembolso-servico-nao-funciona-e-suporte-nao-responde_OPi-rimJXtkjo2yB/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>comprad... pagamento via pix n</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>comprad... Pagamento via PIX n</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Fiz o pgto via PIX para a empresa seguro-vidasaudavel.site através da Cakto Pay, porém não me foi fornecido o produto comprad... Pagamento via PIX não resultou na entrega do produto, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-resultou-na-entrega-do-produto-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_cbUdm8Fq5-5oanwH/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>curso online</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>curso online</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Crescimento em redes sociais</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de curso online, pgn no Instagran que se chama Amigurumi Brasil, pgn com mais de 1.5 k de seguidores, e até ho... Curso online não entregue após pagamento, com falha na comunicação e solicitação de estorno.</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-online-nao-entregue-apos-pagamento-com-falha-na-comunicacao-e-solicitacao-de-estorno_-bekag5hY78F-1mM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>mas at</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>mas at</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra na loja e quero reembolsar meu produto mas até agora não fui atendido Reembolso</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso_Ou6F1k9zy_0W3ATN/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L9"/>
+  <autoFilter ref="A1:L104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -960,7 +6018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1012,17 +6070,17 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria / Cursos online</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -1031,23 +6089,23 @@
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Ferramentas / Aplicativos</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
@@ -1056,48 +6114,48 @@
         <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria / Mentoria</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
@@ -1106,23 +6164,23 @@
         <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Educação infantil / Materiais didáticos</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
@@ -1131,23 +6189,23 @@
         <v>0</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Crescimento em redes sociais</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
@@ -1156,23 +6214,23 @@
         <v>0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ferramentas de produtividade / Assinatura</t>
+          <t>Serviços financeiros / Pix</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
@@ -1181,31 +6239,406 @@
         <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>Educação e consultoria / Mentoria</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>Educação / Idiomas</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Comunidades / Mentoria de negócios</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Marketing / Comunidades de negócios</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Arte personalizada / IA generativa</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Educação e consultoria / Cursos online</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Ferramentas / Aplicativos</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Ferramentas de espionagem / WhatsApp</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Educação infantil / Materiais didáticos</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Ferramentas de produtividade / Assinatura</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Educação / Concursos e certificações</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Educação / Marketing digital e low ticket</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Streaming e entretenimento</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Saúde / Tratamentos alternativos</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Chatbots / Automação de mensagens</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1220,7 +6653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1248,97 +6681,97 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>adquirido teria condi</t>
+          <t>acesso a conversas do instagram n</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>aparece na perfect pay mas o mesmo n</t>
+          <t>adquirido teria condi</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>aplicativo n</t>
+          <t>aparece na perfect pay mas o mesmo n</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>apostila de psicologia 2025</t>
+          <t>aplicativo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>apostila de psicologia025</t>
+          <t>aplicativo n</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>aristocracy negócios digitais</t>
+          <t>aplicativo viewerspy com tr</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>cloakeuai</t>
+          <t>apostila de psicologia 2025</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1347,13 +6780,13 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>comunidade knights club</t>
+          <t>apostila de psicologia025</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1362,58 +6795,58 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>comunidade vsa</t>
+          <t>aristocracy negócios digitais</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>continua ativo</t>
+          <t>auks bot</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>converza.io</t>
+          <t>auto live shop</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>curso de mandarim</t>
+          <t>chamado f</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1428,37 +6861,37 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>curso online capsulas gourmet e c</t>
+          <t>chamado protocolo black digital e comprei</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>códigos lucrativos</t>
+          <t>chegou faltando conte</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>cloakeuai</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1467,28 +6900,28 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>de seguran</t>
+          <t>com defeito</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>directspeed</t>
+          <t>com defeito e solicita</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1503,22 +6936,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>dois cursos de idiomas</t>
+          <t>comprad... pagamento via pix n</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>e a plataforma deveria no m</t>
+          <t>comunidade knights club</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1533,22 +6966,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>e conseguiu acess</t>
+          <t>comunidade mvz no dia 27</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>e ele nao chegou quero meu dinheiro de volta ra ad</t>
+          <t>comunidade vsa</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -1563,7 +6996,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>continua ativo</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1578,97 +7011,97 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>converza.io</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>cortes do marques</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero</t>
+          <t>cuja cobran</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
+          <t>curso de mandarim</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>manuscrito dos milagres</t>
+          <t>curso online</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>mentoria nova profissão</t>
+          <t>curso online capsulas gourmet e c</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>códigos lucrativos</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -1677,43 +7110,43 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>da vav</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>não conseguiu confirmar a distribuidora</t>
+          <t>de baixa qualidade</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>on line rj comercio varejista de acessorios ltda</t>
+          <t>de postagem autom</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -1722,43 +7155,43 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>pack canva</t>
+          <t>de seguran</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>pelo qual paguei n</t>
+          <t>de streaming n</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>perfect academy</t>
+          <t>diferente do anunciado e a plataforma n</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -1773,7 +7206,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>produto malu</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -1788,27 +7221,27 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>ra ads previous slide next slide compartilhe resp</t>
+          <t>digitalcessada pela cakto</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>retrato da sua alma gêmea</t>
+          <t>directspeed</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
@@ -1818,67 +7251,67 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>dois aplicativo e n</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>turminha alfakids</t>
+          <t>dois cursos de idiomas</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>um curso</t>
+          <t>e a plataforma deveria no m</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>e conseguiu acess</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>um curso no dia 01</t>
+          <t>e ele nao chegou quero meu dinheiro de volta ra ad</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -1893,82 +7326,82 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
+          <t>e n</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>uma m</t>
+          <t>e solicita</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>em um site na internet e ao abrir o email</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>umgrama de karaoke e est</t>
+          <t>espia f</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>validação cadastral: em análise</t>
+          <t>estrutura para gera</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>youclone no dia 28</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -1983,15 +7416,1110 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t>frequência da vinci</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>fábrica de low ticket</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>grupo vip</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>ia academy</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>incompleto dentro da garantia</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>inexistente</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>interactive live</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>low ticket do zero</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>low ticket do zero 2.0 no dia 30</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>manuscrito dos milagres</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>mas at</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>mas n</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>material de fonoaudiologia e n</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>mentoria nova profissão</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>método atlas</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>na plataforma e n</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>na ultima quarta feira</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>nessa plataforma</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>no ... reembolso dentro do prazo</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>no qual n</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>no valor de 97 reais que nao gostei pedi</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>não conseguiu confirmar a distribuidora</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>oduto</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>on line rj comercio varejista de acessorios ltda</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>onde dizia que tinha v</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>pack canva</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>pela cakto e logo realizei o pedido de re</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>pelo pouco que testei</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>pelo qual paguei n</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>perfect academy</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>plataforma home office</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>plataforma tikspy pelo valor de r</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>pois n</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>produto malu</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>programa n</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>que eu comprei na plataforma cakto ..o pr</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>quemetia trazer minha conta do free f</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>ra ads previous slide next slide compartilhe resp</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>receb... propaganda enganosa</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>retrato da sua alma gêmea</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>servi</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>simplesmente n</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>spygram</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>stalkeia</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>tikedit pela perfectpay</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>tomei</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>tudo dentro do prazo tudo certinho e ate</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>turminha alfakids</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>um aplicativo</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>um aplicativo de monitoramento pelo an</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>um curso</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>um curso chamado geniun shop</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>um curso de arais amador paguei e n</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>um curso de ia nao gostei do curso e dent</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>um curso e</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>um curso na plataforma deles</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>um curso na sexta feira e n</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>um curso no dia 01</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>um grupo vip no dia 20</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>um painel e n</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>um site hoje e quero solicitar o cancelam</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>um vendedor que usa os servi</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>uma assinatura do site copie</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>uma ferramenta de automa</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>uma m</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>uma mentoria</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>uma planilha e n</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>umgrama de karaoke e est</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>validação cadastral: em análise</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>vendido pela appluna.net</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
           <t>zap radar</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C124" s="4" t="n">
         <v>10</v>
       </c>
     </row>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -7605,7 +7605,7 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -7620,7 +7620,7 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -7680,7 +7680,7 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -7920,7 +7920,7 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96">
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -8130,7 +8130,7 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -8400,7 +8400,7 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124">
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -7605,7 +7605,7 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -7620,7 +7620,7 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
@@ -7680,7 +7680,7 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -7920,7 +7920,7 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -8130,7 +8130,7 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -8400,7 +8400,7 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124">
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -689,17 +689,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>plataforma tikspy pelo valor de r</t>
+          <t>produto malu</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>plataforma TikSpy pelo valor de R</t>
+          <t>Produto Malu</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas / Aplicativos</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -718,56 +718,52 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>R$ 360,24</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>No dia 24/08/2026 adquiri a plataforma TikSpy pelo valor de R$ 360,24Após acessar a plataforma, concluí que ela não... Dificuldade em cancelar compra e solicitar reembolso de plataforma digital</t>
+          <t>Título: Produto Malu não correspondeu às minhas expectativas e exige novo pagamento para ativaçãoRealizei a compra ... Produto Malu exige novo pagamento para ativação, solicito cancelamento e reembolso.</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/dificuldade-em-cancelar-compra-e-solicitar-reembolso-de-plataforma-digital_MNsF1CWfu9nJFQaI/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-malu-exige-novo-pagamento-para-ativacao-solicito-cancelamento-e-reembolso_EGQhjKMbfuFFizV7/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>mentoria nova profissão</t>
+          <t>plataforma tikspy pelo valor de r</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Mentoria Nova Profissão</t>
+          <t>plataforma TikSpy pelo valor de R</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria / Mentoria</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -776,9 +772,13 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>R$ 360,24</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -787,37 +787,41 @@
       <c r="J6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>No dia 24/08/2026 adquiri a plataforma TikSpy pelo valor de R$ 360,24Após acessar a plataforma, concluí que ela não... Dificuldade em cancelar compra e solicitar reembolso de plataforma digital</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-mentoria-nova-profissao-propaganda-enganosa-e-falha-na-intermediacao-de-reembolso-pela-cakto-pay_WVFYGdZmjsyF9dv0/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/dificuldade-em-cancelar-compra-e-solicitar-reembolso-de-plataforma-digital_MNsF1CWfu9nJFQaI/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>auks bot</t>
+          <t>mentoria nova profissão</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Auks Bot</t>
+          <t>Mentoria Nova Profissão</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Educação e consultoria / Mentoria</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -826,56 +830,48 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>R$ 277,00,</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Comprei o produto Auks Bot, pelo valor de R$ 277,00, com pagamento processado pela Perfect Pay.Em 27/08/2026, ainda... Reclamação sobre reembolso negado pela Perfect Pay para o produto Auks Bot</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-reembolso-negado-pela-perfect-pay-para-o-produto-auks-bot_KqYsYdFXN1z0_dI5/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-mentoria-nova-profissao-propaganda-enganosa-e-falha-na-intermediacao-de-reembolso-pela-cakto-pay_WVFYGdZmjsyF9dv0/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>curso de mandarim</t>
+          <t>auks bot</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Curso de Mandarim</t>
+          <t>Auks Bot</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Educação / Idiomas</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -886,7 +882,11 @@
       <c r="G8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>R$ 277,00,</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -895,27 +895,31 @@
       <c r="J8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o produto Auks Bot, pelo valor de R$ 277,00, com pagamento processado pela Perfect Pay.Em 27/08/2026, ainda... Reclamação sobre reembolso negado pela Perfect Pay para o produto Auks Bot</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-no-face-book-compra-de-curso-de-mandarim-2099-02092026-190111_uKMKomnheob91qjy/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-reembolso-negado-pela-perfect-pay-para-o-produto-auks-bot_KqYsYdFXN1z0_dI5/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>e solicita</t>
+          <t>curso de mandarim</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>e solicita</t>
+          <t>Curso de Mandarim</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -925,7 +929,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação / Idiomas</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -943,28 +947,24 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra pela cakto Detalhes do PedidoPedido: *****Data: 02/09/2026Produto: 100 Remédios Naturais ... Reclamação sobre não recebimento de produto e solicitação de estorno do valor pago via PIX.</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-nao-recebimento-de-produto-e-solicitacao-de-estorno-do-valor-pago-via-pix_19VMI-vOfIlR0IIm/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-no-face-book-compra-de-curso-de-mandarim-2099-02092026-190111_uKMKomnheob91qjy/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>comunidade mvz no dia 27</t>
+          <t>e solicita</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Comunidade MVZ no dia 27</t>
+          <t>e solicita</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -990,39 +990,35 @@
       <c r="G10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>R$ 248,89,</t>
-        </is>
-      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Realizei a compra do produto Comunidade MVZ no dia 27/08/2026, no valor de R$ 248,89, através da plataforma Cakto. Dentro do ... Cliente solicita cancelamento e reembolso de curso online após ser direcionado entre plataforma e produtor.</t>
+          <t>Fiz uma compra pela cakto Detalhes do PedidoPedido: *****Data: 02/09/2026Produto: 100 Remédios Naturais ... Reclamação sobre não recebimento de produto e solicitação de estorno do valor pago via PIX.</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-solicita-cancelamento-e-reembolso-de-curso-online-apos-ser-direcionado-entre-plataforma-e-produtor_7fIx89P-1ZpAApHx/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-nao-recebimento-de-produto-e-solicitacao-de-estorno-do-valor-pago-via-pix_19VMI-vOfIlR0IIm/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>comunidade mvz no dia 27</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>Comunidade MVZ no dia 27</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1037,7 +1033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1048,35 +1044,39 @@
       <c r="G11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>R$ 248,89,</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Boa noite. Fiz a compra de um produto na ultima quarta feira (26/08/20226) e até essa data eu não recebi o produto.Receb... Produto não recebido e dificuldade de acesso ao material digital, com falha no reembolso e suporte ineficaz.</t>
+          <t>Realizei a compra do produto Comunidade MVZ no dia 27/08/2026, no valor de R$ 248,89, através da plataforma Cakto. Dentro do ... Cliente solicita cancelamento e reembolso de curso online após ser direcionado entre plataforma e produtor.</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-recebido-e-dificuldade-de-acesso-ao-material-digital-com-falha-no-reembolso-e-suporte-ineficaz_iOzRmbylQ4neQezT/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-solicita-cancelamento-e-reembolso-de-curso-online-apos-ser-direcionado-entre-plataforma-e-produtor_7fIx89P-1ZpAApHx/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ia academy</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>IA Academy</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1102,39 +1102,35 @@
       <c r="G12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>R$ 197,99,</t>
-        </is>
-      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Realizei no dia 01/09/2026 uma compra através da plataforma Cakto, referente ao produto IA Academy, no valor de R$ 197,99, pa... Solicitação de cancelamento e reembolso de curso online não respondido pelo produtor.</t>
+          <t>Boa noite. Fiz a compra de um produto na ultima quarta feira (26/08/20226) e até essa data eu não recebi o produto.Receb... Produto não recebido e dificuldade de acesso ao material digital, com falha no reembolso e suporte ineficaz.</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-reembolso-de-curso-online-nao-respondido-pelo-produtor_ddqfFY8ufw0eiA3F/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-recebido-e-dificuldade-de-acesso-ao-material-digital-com-falha-no-reembolso-e-suporte-ineficaz_iOzRmbylQ4neQezT/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>comunidade knights club</t>
+          <t>ia academy</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>COMUNIDADE KNIGHTS CLUB</t>
+          <t>IA Academy</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1149,7 +1145,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Comunidades / Mentoria de negócios</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1160,35 +1156,39 @@
       <c r="G13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>R$ 197,99,</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>SOLICITAÇÃO DE REEMBOLSO NÃO CUMPRIDA PAGAMENTO VIA PIXNo dia 21/08/2026, realizei a compra da COMUNIDADE KNIGHTS ... Reembolso de compra via Pix não realizado após solicitação dentro do prazo legal.</t>
+          <t>Realizei no dia 01/09/2026 uma compra através da plataforma Cakto, referente ao produto IA Academy, no valor de R$ 197,99, pa... Solicitação de cancelamento e reembolso de curso online não respondido pelo produtor.</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-de-compra-via-pix-nao-realizado-apos-solicitacao-dentro-do-prazo-legal_w1bmesmQpVhI5h0M/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-reembolso-de-curso-online-nao-respondido-pelo-produtor_ddqfFY8ufw0eiA3F/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
+          <t>comunidade knights club</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Low Ticket do Zero 2.0 no dia 30</t>
+          <t>COMUNIDADE KNIGHTS CLUB</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Comunidades / Mentoria de negócios</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1221,28 +1221,28 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Realizei a compra do produto Low Ticket do Zero 2.0 no dia 30/08/2026. Após acessar o produto, constatei que ele não atendeu ... Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor.</t>
+          <t>SOLICITAÇÃO DE REEMBOLSO NÃO CUMPRIDA PAGAMENTO VIA PIXNo dia 21/08/2026, realizei a compra da COMUNIDADE KNIGHTS ... Reembolso de compra via Pix não realizado após solicitação dentro do prazo legal.</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-de-compra-via-pix-nao-realizado-apos-solicitacao-dentro-do-prazo-legal_w1bmesmQpVhI5h0M/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>chamado f</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>chamado F</t>
+          <t>Low Ticket do Zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1271,37 +1271,37 @@
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Dia 27/08/2026 comprei um produto chamado Fábrica Viral, não recebi o material no e-mail e o produtor não respondeu a minha t... Comprei um produto, não recebi e não consigo pedir reembolso</t>
+          <t>Realizei a compra do produto Low Ticket do Zero 2.0 no dia 30/08/2026. Após acessar o produto, constatei que ele não atendeu ... Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor.</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/comprei-um-produto-nao-recebi-e-nao-consigo-pedir-reembolso_kESf7mBZQ-lYpUvb/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>comunidade vsa</t>
+          <t>chamado f</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>COMUNIDADE VSA</t>
+          <t>chamado F</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Marketing / Comunidades de negócios</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1322,35 +1322,35 @@
       <c r="G16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>R$ 248,89.</t>
-        </is>
-      </c>
+      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Dia 27/08/2026 comprei um produto chamado Fábrica Viral, não recebi o material no e-mail e o produtor não respondeu a minha t... Comprei um produto, não recebi e não consigo pedir reembolso</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-de-compra-com-erro-de-saldo-na-conta-do-vendedor_e5d-tH3gUGahNktM/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/comprei-um-produto-nao-recebi-e-nao-consigo-pedir-reembolso_kESf7mBZQ-lYpUvb/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>retrato da sua alma gêmea</t>
+          <t>comunidade vsa</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Retrato da Sua Alma Gêmea</t>
+          <t>COMUNIDADE VSA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Arte personalizada / IA generativa</t>
+          <t>Marketing / Comunidades de negócios</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1376,35 +1376,35 @@
       <c r="G17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>R$ 248,89.</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Olá, equipe da Cakto Pay,No dia 28/08/2026, realizei a compra do produto &amp;quot;Retrato da Sua Alma Gêmea&amp;quot; (Código do Ped... [Editado pelo Reclame Aqui] e solicitação de estorno para produto &amp;quot;Retrato da Sua Alma Gêmea&amp;quot;</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-e-solicitacao-de-estorno-para-produto-retrato-da-sua-alma-gemea_H8ihRLGIEQMZ9WSb/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-de-compra-com-erro-de-saldo-na-conta-do-vendedor_e5d-tH3gUGahNktM/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>perfect academy</t>
+          <t>retrato da sua alma gêmea</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Perfect Academy</t>
+          <t>Retrato da Sua Alma Gêmea</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria / Cursos online</t>
+          <t>Arte personalizada / IA generativa</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1433,37 +1433,37 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Comprei um curso na perfect academy, mais o curso veio incompleto, fui tentar pedir meu reembolso, onde me deparei sem suport... Curso incompleto e falta de suporte para reembolso na Perfect Academy</t>
+          <t>Olá, equipe da Cakto Pay,No dia 28/08/2026, realizei a compra do produto &amp;quot;Retrato da Sua Alma Gêmea&amp;quot; (Código do Ped... [Editado pelo Reclame Aqui] e solicitação de estorno para produto &amp;quot;Retrato da Sua Alma Gêmea&amp;quot;</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/curso-incompleto-e-falta-de-suporte-para-reembolso-na-perfect-academy_xfFtbFJD4cncefLz/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-e-solicitacao-de-estorno-para-produto-retrato-da-sua-alma-gemea_H8ihRLGIEQMZ9WSb/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>produto malu</t>
+          <t>digital n</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Produto Malu</t>
+          <t>digital n</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas / Aplicativos</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Título: Produto Malu não correspondeu às minhas expectativas e exige novo pagamento para ativaçãoRealizei a compra ... Produto Malu exige novo pagamento para ativação, solicito cancelamento e reembolso.</t>
+          <t>Comprei dois produtos digitais que não foram entregues. RA Ads</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-malu-exige-novo-pagamento-para-ativacao-solicito-cancelamento-e-reembolso_EGQhjKMbfuFFizV7/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/produto-digital-nao-entregue_BJSp7nt8u2UDuoYS/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>aplicativo</t>
+          <t>curso de yoga n</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>aplicativo</t>
+          <t>curso de yoga n</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1545,28 +1545,28 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Eu adquiri uma compra pela [Editado pelo Reclame Aqui] prometendo acesso a um app pago e após pagar o aplicativo simplesmente... Cobrança indevida e solicitação de estorno após compra de aplicativo</t>
+          <t>Prezados, esta manha fiz uma compra (+108 Posturas de Yoga Ilustradas, plano premium). Nao recebi o produto, recebi outra coisa e nao consta na area da Cakto Members. Paguei com Pix. O link do reembolso nao funciona, sempre a mesma mensagem: "Não foi possível confirmar o código. Tente novamente". Entrei em contato com o vendedor, sem resposta. Mandei email para a Cakto, sem resposta.</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-solicitacao-de-estorno-apos-compra-de-aplicativo_k54KbhcZ8MWgLTn0/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/compra-de-curso-de-yoga-nao-recebida-link-de-reembolso-inoperante-e-falta-de-contato-do-vendedorsuporte_zv5I8nnWtCj3LtbF/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>tikedit pela perfectpay</t>
+          <t>que era pelo gmail mandei a mensagem expl</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TikEdit pela PerfectPay</t>
+          <t>que era pelo Gmail mandei a mensagem expl</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1599,29 +1599,33 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de ferramenta inteligência artificial o acesso pelo cakto mas algumas das principais funções da ferramenta, como o motion control usei 121 de crédito a plataforma não gerou o vídeo e não voltou os créditos até então não gostei da ferramenta eu quis meu reembolso quando fui tentar fazer o reembolso a plataforma do cakto falou que era só com o suporte do produto que era pelo Gmail mandei a mensagem explicando que queria o reembolso não tive resposta aí entrei em contato pelo zap ele</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/recusa-de-reembolso-em-renovacao-automatica-de-produto-tikedit-pela-perfectpay_7DczqrMSjVJHqp26/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-negado-e-falta-de-suporte-para-ferramenta-de-ia-nao-funcional_k4Zr32LLud7_uMfl/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>vendido pela appluna.net</t>
+          <t>perfect academy</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>vendido pela Appluna.net</t>
+          <t>Perfect Academy</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1631,7 +1635,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Educação e consultoria / Cursos online</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1649,28 +1653,28 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>A referida empresa, alega ser uma plataforma de gerenciamento de pagamentos online que informa não ter responsabilidade sobre... Perfectpay cobra por serviço, mas não resolve problemas de acesso ao produto vendido pela Appluna.net</t>
+          <t>Comprei um curso na perfect academy, mais o curso veio incompleto, fui tentar pedir meu reembolso, onde me deparei sem suport... Curso incompleto e falta de suporte para reembolso na Perfect Academy</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perfectpay-cobra-por-servico-mas-nao-resolve-problemas-de-acesso-ao-produto-vendido-pela_a5_1eWXf4MZ6sZZ7/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/curso-incompleto-e-falta-de-suporte-para-reembolso-na-perfect-academy_xfFtbFJD4cncefLz/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>aparece na perfect pay mas o mesmo n</t>
+          <t>aplicativo</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>APARECE NA PERFECT PAY MAS O MESMO N</t>
+          <t>aplicativo</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1685,7 +1689,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1699,7 +1703,7 @@
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
@@ -1707,24 +1711,24 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Fiz A COMPRA DE UM SERVIÇO NO QUAL É [Editado pelo Reclame Aqui] E O PRODUTO APARECE NA PERFECT PAY MAS O MESMO NÃO SE RESPO... Compra de serviço com promessa de [Editado pelo Reclame Aqui] e Perfect Pay se isenta de responsabilidade</t>
+          <t>Eu adquiri uma compra pela [Editado pelo Reclame Aqui] prometendo acesso a um app pago e após pagar o aplicativo simplesmente... Cobrança indevida e solicitação de estorno após compra de aplicativo</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-com-promessa-de-editado-pelo-reclame-aqui-e-perfect-pay-se-isenta-de-responsabilidade_0DOgqsLTHMXBEQUg/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-solicitacao-de-estorno-apos-compra-de-aplicativo_k54KbhcZ8MWgLTn0/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>receb... propaganda enganosa</t>
+          <t>tikedit pela perfectpay</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>receb... Propaganda enganosa</t>
+          <t>TikEdit pela PerfectPay</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1739,7 +1743,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1757,24 +1761,24 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/propaganda-enganosa_zOGr7sPQQhH7ROqM/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/recusa-de-reembolso-em-renovacao-automatica-de-produto-tikedit-pela-perfectpay_7DczqrMSjVJHqp26/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>plataforma home office</t>
+          <t>vendido pela appluna.net</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Plataforma Home Office</t>
+          <t>vendido pela Appluna.net</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1789,7 +1793,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1807,28 +1811,28 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Solicito o cancelamento e o reembolso do valor pago pelo produto Plataforma Home Office, vinculado ao e-mail ***** . O produt... Solicitação de cancelamento e reembolso de Plataforma Home Office por propaganda enganosa.</t>
+          <t>A referida empresa, alega ser uma plataforma de gerenciamento de pagamentos online que informa não ter responsabilidade sobre... Perfectpay cobra por serviço, mas não resolve problemas de acesso ao produto vendido pela Appluna.net</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-plataforma-home-office-por-propaganda-enganosa_Z3FnnwZ03NBXKWFQ/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perfectpay-cobra-por-servico-mas-nao-resolve-problemas-de-acesso-ao-produto-vendido-pela_a5_1eWXf4MZ6sZZ7/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>aparece na perfect pay mas o mesmo n</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>APARECE NA PERFECT PAY MAS O MESMO N</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1843,7 +1847,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1857,32 +1861,32 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, In... Reclamação sobre produto de postagem automática com cobranças adicionais, sem retorno do suporte , sem liberação do prometido e com acesso restrito ao conteúdo,e falta de reembolso.</t>
+          <t>Fiz A COMPRA DE UM SERVIÇO NO QUAL É [Editado pelo Reclame Aqui] E O PRODUTO APARECE NA PERFECT PAY MAS O MESMO NÃO SE RESPO... Compra de serviço com promessa de [Editado pelo Reclame Aqui] e Perfect Pay se isenta de responsabilidade</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-com-promessa-de-editado-pelo-reclame-aqui-e-perfect-pay-se-isenta-de-responsabilidade_0DOgqsLTHMXBEQUg/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>acesso a conversas do instagram n</t>
+          <t>receb... propaganda enganosa</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>acesso a conversas do Instagram n</t>
+          <t>receb... Propaganda enganosa</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1897,7 +1901,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Crescimento em redes sociais</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1915,24 +1919,24 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-acesso-a-conversas-do-instagram-nao-realizada-e-solicitacao-de-reembolso_bEr04z5n0qvNdmJf/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/propaganda-enganosa_zOGr7sPQQhH7ROqM/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>códigos lucrativos</t>
+          <t>plataforma home office</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Códigos Lucrativos</t>
+          <t>Plataforma Home Office</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1947,7 +1951,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1961,28 +1965,32 @@
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Solicito o cancelamento e o reembolso do valor pago pelo produto Plataforma Home Office, vinculado ao e-mail ***** . O produt... Solicitação de cancelamento e reembolso de Plataforma Home Office por propaganda enganosa.</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-plataforma-home-office-por-propaganda-enganosa_Z3FnnwZ03NBXKWFQ/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>zap radar</t>
+          <t>de postagem autom</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ZAP Radar</t>
+          <t>de postagem autom</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1997,7 +2005,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de espionagem / WhatsApp</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2015,28 +2023,28 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o ... Solicitação de estorno de compra no site ZAP Radar por não recebimento de relatório.</t>
+          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, In... Reclamação sobre produto de postagem automática com cobranças adicionais, sem retorno do suporte , sem liberação do prometido e com acesso restrito ao conteúdo,e falta de reembolso.</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>acesso a conversas do instagram n</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>acesso a conversas do Instagram n</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2051,7 +2059,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Crescimento em redes sociais</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2065,28 +2073,28 @@
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-acesso-a-conversas-do-instagram-nao-realizada-e-solicitacao-de-reembolso_bEr04z5n0qvNdmJf/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>códigos lucrativos</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>Códigos Lucrativos</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2101,7 +2109,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2115,28 +2123,28 @@
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-e-nao-recebi_IgLy-Z3TgKa5WfbK/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>chamado protocolo black digital e comprei</t>
+          <t>zap radar</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>chamado Protocolo Black Digital e comprei</t>
+          <t>ZAP Radar</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2151,7 +2159,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de espionagem / WhatsApp</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2165,32 +2173,32 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Eu comprei um produto chamado Protocolo Black Digital e comprei dois order bumps, e o produto é horrível, na hora de eu pedir... Impossibilidade de solicitar reembolso para o produto Protocolo Black Digital e order bumps.</t>
+          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o ... Solicitação de estorno de compra no site ZAP Radar por não recebimento de relatório.</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/impossibilidade-de-solicitar-reembolso-para-o-produto-protocolo-black-digital-e-order-bumps_KUmvlWU2BBaqoLGc/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>aplicativo viewerspy com tr</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>aplicativo ViewerSpy com tr</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2205,7 +2213,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2219,32 +2227,28 @@
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra de aplicativo ViewerSpy com três pagamentos, mas se tratava de [Editado pelo Reclame Aqui], quero meu dinheiro... [Editado pelo Reclame Aqui] em aplicativo ViewerSpy com cobrança indevida, solicitação de [Editado pelo Reclame Aqui].</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-viewerspy-com-cobranca-indevida-solicitacao-de-editado-pelo-reclame-aqui_4jVYpRQh7FZ9NsuM/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>servi</t>
+          <t>online</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>servi</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2277,28 +2281,24 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra me garantindo acesso a fotos e conversas de um WhatsApp meu mesmo que perdi acesso, mas fui enganado paguei tu... Compra de serviço para recuperação de WhatsApp que direciona para página de curso.</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-para-recuperacao-de-whatsapp-que-direciona-para-pagina-de-curso_9jbLXBtTk54j7-aK/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-e-nao-recebi_IgLy-Z3TgKa5WfbK/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>chamado protocolo black digital e comprei</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>chamado Protocolo Black Digital e comprei</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2331,24 +2331,28 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Eu comprei um produto chamado Protocolo Black Digital e comprei dois order bumps, e o produto é horrível, na hora de eu pedir... Impossibilidade de solicitar reembolso para o produto Protocolo Black Digital e order bumps.</t>
+        </is>
+      </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-editado-pelo-reclame-aqui-e-solicitacao-de-editado-pelo-reclame-aqui-com-base-no-direito-de-arrependimento_SenuNicKKSMOvgEa/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/impossibilidade-de-solicitar-reembolso-para-o-produto-protocolo-black-digital-e-order-bumps_KUmvlWU2BBaqoLGc/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>uma ferramenta de automa</t>
+          <t>aplicativo viewerspy com tr</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>uma ferramenta de automa</t>
+          <t>aplicativo ViewerSpy com tr</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2363,7 +2367,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2381,24 +2385,28 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de aplicativo ViewerSpy com três pagamentos, mas se tratava de [Editado pelo Reclame Aqui], quero meu dinheiro... [Editado pelo Reclame Aqui] em aplicativo ViewerSpy com cobrança indevida, solicitação de [Editado pelo Reclame Aqui].</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-ferramenta-de-automacao-nao-recebida_3ia2l_X9I98IiU5Q/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-viewerspy-com-cobranca-indevida-solicitacao-de-editado-pelo-reclame-aqui_4jVYpRQh7FZ9NsuM/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>simplesmente n</t>
+          <t>servi</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>simplesmente n</t>
+          <t>servi</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2413,7 +2421,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2431,28 +2439,28 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Fiz a compra de um sistema multijogos da Retrogame Ramos, porém o produto simplesmente não funcionou. Solicitei o reembolso e... Reclamação sobre sistema multijogos não funcional e falta de reembolso pela Retrogame Ramos</t>
+          <t>Fiz uma compra me garantindo acesso a fotos e conversas de um WhatsApp meu mesmo que perdi acesso, mas fui enganado paguei tu... Compra de serviço para recuperação de WhatsApp que direciona para página de curso.</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-sistema-multijogos-nao-funcional-e-falta-de-reembolso-pela-retrogame-ramos_yXzSmLa6zWMj18Hq/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-para-recuperacao-de-whatsapp-que-direciona-para-pagina-de-curso_9jbLXBtTk54j7-aK/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>no valor de 97 reais que nao gostei pedi</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>no valor de 97 reais que nao gostei pedi</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2485,28 +2493,24 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>[Editado pelo Reclame Aqui]. comprei um produto no valor de 97 reais que nao gostei pedi o reembolso e ninguem resolve nada m... Reclamação sobre propaganda enganosa e dificuldade em obter reembolso de produto.</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-propaganda-enganosa-e-dificuldade-em-obter-reembolso-de-produto_NexaAcyAJfkO5zUN/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-editado-pelo-reclame-aqui-e-solicitacao-de-editado-pelo-reclame-aqui-com-base-no-direito-de-arrependimento_SenuNicKKSMOvgEa/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>quemetia trazer minha conta do free f</t>
+          <t>uma ferramenta de automa</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>que prometia trazer minha conta do free f</t>
+          <t>uma ferramenta de automa</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2521,7 +2525,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2539,33 +2543,29 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Quero reembolso do meu dinheiro, comprei um produto que prometia trazer minha conta do free fire de volta, mais era tudo [Edi... Produto de Free Fire prometia recuperar conta, mas era [Editado pelo Reclame Aqui] e cliente pede reembolso.</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-de-free-fire-prometia-recuperar-conta-mas-era-editado-pelo-reclame-aqui-e-cliente-pede-reembolso_6E9DzuuICeSs7-BW/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-ferramenta-de-automacao-nao-recebida_3ia2l_X9I98IiU5Q/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>spygram</t>
+          <t>simplesmente n</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Spygram</t>
+          <t>simplesmente n</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2593,24 +2593,28 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de um sistema multijogos da Retrogame Ramos, porém o produto simplesmente não funcionou. Solicitei o reembolso e... Reclamação sobre sistema multijogos não funcional e falta de reembolso pela Retrogame Ramos</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-reembolso-de-pagamentos-via-pix-para-o-programa-spygram-identificado-como-editado-pelo-reclame-aqui_tx5DRYfAycgJL_5j/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-sistema-multijogos-nao-funcional-e-falta-de-reembolso-pela-retrogame-ramos_yXzSmLa6zWMj18Hq/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>um curso de arais amador paguei e n</t>
+          <t>no valor de 97 reais que nao gostei pedi</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>um curso de arais amador paguei e n</t>
+          <t>no valor de 97 reais que nao gostei pedi</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2625,7 +2629,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2643,28 +2647,28 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um curso de arais amador paguei e não recebi segue comprovante de pagamento Fui vítima de [Editado pelo Reclame Aqui]</t>
+          <t>[Editado pelo Reclame Aqui]. comprei um produto no valor de 97 reais que nao gostei pedi o reembolso e ninguem resolve nada m... Reclamação sobre propaganda enganosa e dificuldade em obter reembolso de produto.</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/fui-vitima-de-editado-pelo-reclame-aqui_eaEOE7rI3vDh1NKM/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-propaganda-enganosa-e-dificuldade-em-obter-reembolso-de-produto_NexaAcyAJfkO5zUN/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>tudo dentro do prazo tudo certinho e ate</t>
+          <t>quemetia trazer minha conta do free f</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>tudo dentro do prazo tudo certinho e ate</t>
+          <t>que prometia trazer minha conta do free f</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2679,7 +2683,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2697,29 +2701,33 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Quero reembolso do meu dinheiro, comprei um produto que prometia trazer minha conta do free fire de volta, mais era tudo [Edi... Produto de Free Fire prometia recuperar conta, mas era [Editado pelo Reclame Aqui] e cliente pede reembolso.</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso_3QFTCw6-Ygo025v1/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-de-free-fire-prometia-recuperar-conta-mas-era-editado-pelo-reclame-aqui-e-cliente-pede-reembolso_6E9DzuuICeSs7-BW/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>dois aplicativo e n</t>
+          <t>spygram</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>dois aplicativo e n</t>
+          <t>Spygram</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2729,7 +2737,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2740,39 +2748,31 @@
       <c r="G43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>R$ 27,90</t>
-        </is>
-      </c>
+      <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Bom dia ! Fiz uma compra de dois aplicativo e não recebi o aplicativo, no valor de R$ 27,90 e outro de R$ 19,00 às 16:35 h no... Compra de aplicativos não recebidos, solicitação de reembolso.</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-nao-recebidos-solicitacao-de-reembolso_IVdC0jac41EFjNhF/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-reembolso-de-pagamentos-via-pix-para-o-programa-spygram-identificado-como-editado-pelo-reclame-aqui_tx5DRYfAycgJL_5j/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>espia f</t>
+          <t>um curso de arais amador paguei e n</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>espia f</t>
+          <t>um curso de arais amador paguei e n</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2805,28 +2805,28 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Comprei o app espia fácil pro e não me deram o acesso. Quero reembolso Cair em um [Editado pelo Reclame Aqui]</t>
+          <t>Fiz uma compra de um curso de arais amador paguei e não recebi segue comprovante de pagamento Fui vítima de [Editado pelo Reclame Aqui]</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cair-em-um-editado-pelo-reclame-aqui_3GiaHX5kQ4C877x9/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/fui-vitima-de-editado-pelo-reclame-aqui_eaEOE7rI3vDh1NKM/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>um aplicativo de monitoramento pelo an</t>
+          <t>tudo dentro do prazo tudo certinho e ate</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>um aplicativo de monitoramento pelo an</t>
+          <t>tudo dentro do prazo tudo certinho e ate</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2859,28 +2859,24 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra de um aplicativo de monitoramento pelo anúncio no YouTube paguei 46.90 e levei um [Editado pelo Reclame Aqui] ... [Editado pelo Reclame Aqui] em aplicativo de monitoramento cliente solicita estorno de valor pago por produto não funcional.</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-de-monitoramento-cliente-solicita-estorno-de-valor-pago-por-produto-nao-funcional_nGia5bRqbVr80nh-/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso_3QFTCw6-Ygo025v1/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>um vendedor que usa os servi</t>
+          <t>dois aplicativo e n</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>um vendedor que usa os servi</t>
+          <t>dois aplicativo e n</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2895,7 +2891,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2906,35 +2902,39 @@
       <c r="G46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>R$ 27,90</t>
+        </is>
+      </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Efetuei uma compra de um vendedor que usa os serviços da perfect pay para pagamentos. O vendedor não enviou acesso ao produto... Reclamação sobre produto não entregue e solicitação de estorno de valor pago através da Perfect Pay.</t>
+          <t>Bom dia ! Fiz uma compra de dois aplicativo e não recebi o aplicativo, no valor de R$ 27,90 e outro de R$ 19,00 às 16:35 h no... Compra de aplicativos não recebidos, solicitação de reembolso.</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-nao-entregue-e-solicitacao-de-estorno-de-valor-pago-atraves-da-perfect-pay_87chbXy48Qb7cTPa/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-nao-recebidos-solicitacao-de-reembolso_IVdC0jac41EFjNhF/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>no ... reembolso dentro do prazo</t>
+          <t>espia f</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>no ... reembolso dentro do prazo</t>
+          <t>espia f</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2967,28 +2967,28 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Solicitei reembolso dentro do prazo, mas não consigo contato com o vendedorAdquiri através da Perfect Pay um produto no ... reembolso dentro do prazo, mas não consigo contato com o vendedor após compra de produto com conteúdo enganoso.</t>
+          <t>Comprei o app espia fácil pro e não me deram o acesso. Quero reembolso Cair em um [Editado pelo Reclame Aqui]</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-dentro-do-prazo-mas-nao-consigo-contato-com-o-vendedor-apos-compra-de-produto-com-conteudo-enganoso_msDSOKrJ-W3coXfK/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cair-em-um-editado-pelo-reclame-aqui_3GiaHX5kQ4C877x9/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>grupo vip</t>
+          <t>um aplicativo de monitoramento pelo an</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>grupo VIP</t>
+          <t>um aplicativo de monitoramento pelo an</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3021,28 +3021,28 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Bem, eu fiz uma compra na segunda-feira de um grupo vip do js e não estou satisfeito, quero o meu reembolso, ja vou deixar es... Reembolso negado e falta de contato do suporte após compra de grupo VIP</t>
+          <t>Fiz uma compra de um aplicativo de monitoramento pelo anúncio no YouTube paguei 46.90 e levei um [Editado pelo Reclame Aqui] ... [Editado pelo Reclame Aqui] em aplicativo de monitoramento cliente solicita estorno de valor pago por produto não funcional.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-negado-e-falta-de-contato-do-suporte-apos-compra-de-grupo-vip_l-3zMo_MYaiaFQbn/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-de-monitoramento-cliente-solicita-estorno-de-valor-pago-por-produto-nao-funcional_nGia5bRqbVr80nh-/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>e n</t>
+          <t>um vendedor que usa os servi</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>e n</t>
+          <t>um vendedor que usa os servi</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Serviços financeiros / Pix</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3075,28 +3075,28 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um produto e não recebi, alegam que não foi pago, já reclamei várias vezes com o vendedor e até agora ele n... Produto não recebido e vendedor alega falta de pagamento, sem resolução.</t>
+          <t>Efetuei uma compra de um vendedor que usa os serviços da perfect pay para pagamentos. O vendedor não enviou acesso ao produto... Reclamação sobre produto não entregue e solicitação de estorno de valor pago através da Perfect Pay.</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-nao-recebido-e-vendedor-alega-falta-de-pagamento-sem-resolucao_4ypAxIw4TPAzgFfj/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-nao-entregue-e-solicitacao-de-estorno-de-valor-pago-atraves-da-perfect-pay_87chbXy48Qb7cTPa/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>de baixa qualidade</t>
+          <t>no ... reembolso dentro do prazo</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>de baixa qualidade</t>
+          <t>no ... reembolso dentro do prazo</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3129,28 +3129,28 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra aonde prometia uma reza sagrada que faz prosperar e abrir caminhos, mas a reza não foi feita e me cobraram 3 v... Cobrança indevida e produto de baixa qualidade (PDF de IA) em vez de reza prometida.</t>
+          <t>Solicitei reembolso dentro do prazo, mas não consigo contato com o vendedorAdquiri através da Perfect Pay um produto no ... reembolso dentro do prazo, mas não consigo contato com o vendedor após compra de produto com conteúdo enganoso.</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-produto-de-baixa-qualidade-pdf-de-ia-em-vez-de-reza-prometida_S22Bk6Gf4HfO6zVF/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-dentro-do-prazo-mas-nao-consigo-contato-com-o-vendedor-apos-compra-de-produto-com-conteudo-enganoso_msDSOKrJ-W3coXfK/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>um painel e n</t>
+          <t>grupo vip</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>um painel e n</t>
+          <t>grupo VIP</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3183,28 +3183,28 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um painel e não funcionou [Editado pelo Reclame Aqui] Solicito reembolso 19.99 [Editado pelo Reclame Aqui]</t>
+          <t>Bem, eu fiz uma compra na segunda-feira de um grupo vip do js e não estou satisfeito, quero o meu reembolso, ja vou deixar es... Reembolso negado e falta de contato do suporte após compra de grupo VIP</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui_5xPVEL37uCq2Nl_s/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-negado-e-falta-de-contato-do-suporte-apos-compra-de-grupo-vip_l-3zMo_MYaiaFQbn/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>um curso chamado geniun shop</t>
+          <t>e n</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>um curso chamado Geniun Shop</t>
+          <t>e n</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Serviços financeiros / Pix</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3237,28 +3237,28 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Adquiri um curso chamado Geniun Shop , em 2 de abril de 2026 , fiZ apenas as primeiras aulas, e agora quando resolvi voltar p... Perda de acesso ao curso Geniun Shop após pagamento, sem retorno do suporte.</t>
+          <t>Fiz uma compra de um produto e não recebi, alegam que não foi pago, já reclamei várias vezes com o vendedor e até agora ele n... Produto não recebido e vendedor alega falta de pagamento, sem resolução.</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perda-de-acesso-ao-curso-geniun-shop-apos-pagamento-sem-retorno-do-suporte_a6tTJhax8GBOg4xh/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-nao-recebido-e-vendedor-alega-falta-de-pagamento-sem-resolucao_4ypAxIw4TPAzgFfj/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>onde dizia que tinha v</t>
+          <t>de baixa qualidade</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>onde dizia que tinha v</t>
+          <t>de baixa qualidade</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3291,28 +3291,28 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Comprei um produto onde dizia que tinha vários fornecedores de roupas no Brasil..mas não tinha o que eu eu queria .por isso q... Reclamação sobre produto com fornecedores de roupas limitados e solicitação de reembolso.</t>
+          <t>Fiz uma compra aonde prometia uma reza sagrada que faz prosperar e abrir caminhos, mas a reza não foi feita e me cobraram 3 v... Cobrança indevida e produto de baixa qualidade (PDF de IA) em vez de reza prometida.</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-com-fornecedores-de-roupas-limitados-e-solicitacao-de-reembolso_H7FXu4ussEtUSJQC/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-produto-de-baixa-qualidade-pdf-de-ia-em-vez-de-reza-prometida_S22Bk6Gf4HfO6zVF/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>com defeito e solicita</t>
+          <t>um painel e n</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>com defeito e solicita</t>
+          <t>um painel e n</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3345,28 +3345,28 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra no Blackxitoficial (meu Gmail é *****). Meu CPF: *****, no valor de 31 reais. O Painel chegou, mas não funcion... Produto com defeito e solicitação de reembolso</t>
+          <t>Fiz uma compra de um painel e não funcionou [Editado pelo Reclame Aqui] Solicito reembolso 19.99 [Editado pelo Reclame Aqui]</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-com-defeito-e-solicitacao-de-reembolso_GgMl5lRE9VZtuHoJ/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui_5xPVEL37uCq2Nl_s/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>na plataforma e n</t>
+          <t>um curso chamado geniun shop</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>na plataforma e n</t>
+          <t>um curso chamado Geniun Shop</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3399,28 +3399,28 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>comprei um produto na plataforma e não gostei, quero meu reembolso, foi comprado no pix:Código da compra: ***** Cliente deseja reembolso de aquecedor comprado via Pix por não ter gostado do produto.</t>
+          <t>Adquiri um curso chamado Geniun Shop , em 2 de abril de 2026 , fiZ apenas as primeiras aulas, e agora quando resolvi voltar p... Perda de acesso ao curso Geniun Shop após pagamento, sem retorno do suporte.</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cliente-deseja-reembolso-de-aquecedor-comprado-via-pix-por-nao-ter-gostado-do-produto_2qo_Zk1Eh3qTNpQy/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perda-de-acesso-ao-curso-geniun-shop-apos-pagamento-sem-retorno-do-suporte_a6tTJhax8GBOg4xh/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>nessa plataforma</t>
+          <t>onde dizia que tinha v</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>nessa plataforma</t>
+          <t>onde dizia que tinha v</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3453,28 +3453,28 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Verifiquei a compra de um produto nessa plataforma, solicitei o reembolso junto a produtora do produto e não consegui retorno... Reembolso não resolvido pela plataforma após contato com produtora e cancelamento de cartão.</t>
+          <t>Comprei um produto onde dizia que tinha vários fornecedores de roupas no Brasil..mas não tinha o que eu eu queria .por isso q... Reclamação sobre produto com fornecedores de roupas limitados e solicitação de reembolso.</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-nao-resolvido-pela-plataforma-apos-contato-com-produtora-e-cancelamento-de-cartao_P1PpJ-yUSNmPIVUp/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-com-fornecedores-de-roupas-limitados-e-solicitacao-de-reembolso_H7FXu4ussEtUSJQC/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>em um site na internet e ao abrir o email</t>
+          <t>com defeito e solicita</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>em um site na internet e ao abrir o email</t>
+          <t>com defeito e solicita</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Serviços financeiros / Pix</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3507,28 +3507,28 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Realizei uma compra de um produto em um site na internet e ao abrir o email enviado me cobraram outra taxa que não estava com... Cobrança de taxa adicional não combinada e falta de acesso ao produto comprado.</t>
+          <t>Fiz uma compra no Blackxitoficial (meu Gmail é *****). Meu CPF: *****, no valor de 31 reais. O Painel chegou, mas não funcion... Produto com defeito e solicitação de reembolso</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-de-taxa-adicional-nao-combinada-e-falta-de-acesso-ao-produto-comprado__chfFQTX8pupMWB5/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-com-defeito-e-solicitacao-de-reembolso_GgMl5lRE9VZtuHoJ/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>tomei</t>
+          <t>na plataforma e n</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Tomei</t>
+          <t>na plataforma e n</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3561,24 +3561,28 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>comprei um produto na plataforma e não gostei, quero meu reembolso, foi comprado no pix:Código da compra: ***** Cliente deseja reembolso de aquecedor comprado via Pix por não ter gostado do produto.</t>
+        </is>
+      </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tomei-editado-pelo-reclame-aqui_PCEkQCMzbA-5dwgy/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cliente-deseja-reembolso-de-aquecedor-comprado-via-pix-por-nao-ter-gostado-do-produto_2qo_Zk1Eh3qTNpQy/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>no qual n</t>
+          <t>nessa plataforma</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>no qual n</t>
+          <t>nessa plataforma</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3611,28 +3615,28 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um produto no qual não corresponde a minha expectativa , então solicito o estorno do meu valor. Email: ****... Solicitação de estorno por produto não correspondente à expectativa</t>
+          <t>Verifiquei a compra de um produto nessa plataforma, solicitei o reembolso junto a produtora do produto e não consegui retorno... Reembolso não resolvido pela plataforma após contato com produtora e cancelamento de cartão.</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-por-produto-nao-correspondente-a-expectativa_jZ-08RI4TwV-ynQ4/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-nao-resolvido-pela-plataforma-apos-contato-com-produtora-e-cancelamento-de-cartao_P1PpJ-yUSNmPIVUp/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>um grupo vip no dia 20</t>
+          <t>em um site na internet e ao abrir o email</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>um grupo vip no dia 20</t>
+          <t>em um site na internet e ao abrir o email</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Serviços financeiros / Pix</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3665,43 +3669,43 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Olá, fiz uma compra de um grupo vip no dia 20/08 e dia 23/08 tentei fazer o cancelamento, mas o vendedor ***** - operações nã... Tentativa de cancelamento de grupo VIP e impossibilidade de contato com o vendedor</t>
+          <t>Realizei uma compra de um produto em um site na internet e ao abrir o email enviado me cobraram outra taxa que não estava com... Cobrança de taxa adicional não combinada e falta de acesso ao produto comprado.</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tentativa-de-cancelamento-de-grupo-vip-e-impossibilidade-de-contato-com-o-vendedor_SkOpE6e5RhZv8KIr/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-de-taxa-adicional-nao-combinada-e-falta-de-acesso-ao-produto-comprado__chfFQTX8pupMWB5/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>turminha alfakids</t>
+          <t>tomei</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Turminha Alfakids</t>
+          <t>Tomei</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Educação infantil / Materiais didáticos</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3721,26 +3725,22 @@
       <c r="J61" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra da turminha Alfakids de 2750 atividades e não recebi,o email que aparece como suporte não responde Compra não recebida e falta de resposta do suporte</t>
-        </is>
-      </c>
+      <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-nao-recebida-e-falta-de-resposta-do-suporte_yWkDvnrLPMHo7aTz/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tomei-editado-pelo-reclame-aqui_PCEkQCMzbA-5dwgy/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>um curso</t>
+          <t>no qual n</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>um curso</t>
+          <t>no qual n</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3775,37 +3775,41 @@
       <c r="J62" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um produto no qual não corresponde a minha expectativa , então solicito o estorno do meu valor. Email: ****... Solicitação de estorno por produto não correspondente à expectativa</t>
+        </is>
+      </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-de-curso-nao-realizado-apos-solicitacao-dentro-do-prazo_ktvLpzB4DAj5K-_J/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-por-produto-nao-correspondente-a-expectativa_jZ-08RI4TwV-ynQ4/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>directspeed</t>
+          <t>um grupo vip no dia 20</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Directspeed</t>
+          <t>um grupo vip no dia 20</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de produtividade / Assinatura</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3825,27 +3829,31 @@
       <c r="J63" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Olá, fiz uma compra de um grupo vip no dia 20/08 e dia 23/08 tentei fazer o cancelamento, mas o vendedor ***** - operações nã... Tentativa de cancelamento de grupo VIP e impossibilidade de contato com o vendedor</t>
+        </is>
+      </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-da-ferramenta-directspeed-nao-respondida_G-frs9kFEKvabVpn/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tentativa-de-cancelamento-de-grupo-vip-e-impossibilidade-de-contato-com-o-vendedor_SkOpE6e5RhZv8KIr/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>cortes do marques</t>
+          <t>turminha alfakids</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Cortes do Marques</t>
+          <t>Turminha Alfakids</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3855,7 +3863,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Educação infantil / Materiais didáticos</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3873,28 +3881,28 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Estou há quase 1 mês tentando cancelar a assinatura do produto Cortes do Marques, adquirido por meio da Cackto, mas até o mom... Cackto não realiza cancelamento de assinatura mesmo após várias solicitações</t>
+          <t>Fiz uma compra da turminha Alfakids de 2750 atividades e não recebi,o email que aparece como suporte não responde Compra não recebida e falta de resposta do suporte</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cackto-nao-realiza-cancelamento-de-assinatura-mesmo-apos-varias-solicitacoes_WEDpJ2MDQNCpB9xD/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-nao-recebida-e-falta-de-resposta-do-suporte_yWkDvnrLPMHo7aTz/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>umgrama de karaoke e est</t>
+          <t>um curso</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>um programa de karaoke e est</t>
+          <t>um curso</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3909,7 +3917,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3923,37 +3931,33 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Fiz a compra de um programa de karaoke e está dando conteúdo não encontrado paguei via pix. Conteúdo não encontrado</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/conteudo-nao-encontrado_eh2tS2q3T2WGSky_/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-de-curso-nao-realizado-apos-solicitacao-dentro-do-prazo_ktvLpzB4DAj5K-_J/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>uma m</t>
+          <t>directspeed</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>uma m</t>
+          <t>Directspeed</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3963,7 +3967,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Ferramentas de produtividade / Assinatura</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3977,32 +3981,28 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra de uma máscara coreana , fiz o pagamento no PIX e a empresa relatou que eu nao havia pago, eu ,logo a seguir ... Pagamento via PIX não reconhecido e falta de retorno da empresa após envio de comprovante.</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-reconhecido-e-falta-de-retorno-da-empresa-apos-envio-de-comprovante_C6tRKpYDqejq7Cvf/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-da-ferramenta-directspeed-nao-respondida_G-frs9kFEKvabVpn/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>curso online capsulas gourmet e c</t>
+          <t>cortes do marques</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>curso online capsulas gourmet e c</t>
+          <t>Cortes do Marques</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -4031,28 +4031,32 @@
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Estou há quase 1 mês tentando cancelar a assinatura do produto Cortes do Marques, adquirido por meio da Cackto, mas até o mom... Cackto não realiza cancelamento de assinatura mesmo após várias solicitações</t>
+        </is>
+      </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/materiais-de-curso-online-de-capsulas-gourmet-e-capuccinos-nao-disponiveis_jlp3yz2MCVJGF1UT/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cackto-nao-realiza-cancelamento-de-assinatura-mesmo-apos-varias-solicitacoes_WEDpJ2MDQNCpB9xD/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>um curso no dia 01</t>
+          <t>umgrama de karaoke e est</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>um curso no dia 01</t>
+          <t>um programa de karaoke e est</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4085,24 +4089,28 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de um programa de karaoke e está dando conteúdo não encontrado paguei via pix. Conteúdo não encontrado</t>
+        </is>
+      </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue_RxHp4cyuljYU2Wtj/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/conteudo-nao-encontrado_eh2tS2q3T2WGSky_/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>diferente do anunciado e a plataforma n</t>
+          <t>uma m</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>diferente do anunciado e a plataforma n</t>
+          <t>uma m</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4131,28 +4139,32 @@
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K69" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de uma máscara coreana , fiz o pagamento no PIX e a empresa relatou que eu nao havia pago, eu ,logo a seguir ... Pagamento via PIX não reconhecido e falta de retorno da empresa após envio de comprovante.</t>
+        </is>
+      </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/vendedor-entregou-produto-diferente-do-anunciado-e-a-plataforma-nao-resolve_vkGIXT8UU80pbQbc/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-reconhecido-e-falta-de-retorno-da-empresa-apos-envio-de-comprovante_C6tRKpYDqejq7Cvf/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>chegou faltando conte</t>
+          <t>curso online capsulas gourmet e c</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>chegou faltando conte</t>
+          <t>curso online capsulas gourmet e c</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4167,7 +4179,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4181,32 +4193,28 @@
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra por lá, produto chegou faltando conteúdo, entro em contato com eles e ZERO atendimento, preciso fazer o estorn... Produto com conteúdo faltante e falta de atendimento para estorno</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-com-conteudo-faltante-e-falta-de-atendimento-para-estorno_S6A780k9_99Ofap-/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/materiais-de-curso-online-de-capsulas-gourmet-e-capuccinos-nao-disponiveis_jlp3yz2MCVJGF1UT/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>um curso na plataforma deles</t>
+          <t>um curso no dia 01</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>um curso na plataforma deles</t>
+          <t>um curso no dia 01</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4235,28 +4243,28 @@
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-estorno-de-curso-online-com-ma-qualidade-e-falta-de-resposta_rDQ1eDeZL9eCjgqm/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue_RxHp4cyuljYU2Wtj/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>auto live shop</t>
+          <t>diferente do anunciado e a plataforma n</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Auto Live Shop</t>
+          <t>diferente do anunciado e a plataforma n</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4271,7 +4279,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4289,28 +4297,24 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Realizei a compra do produto Auto Live Shop, porém, após utilizar o produto, constatei que ele não atendeu às minhas expectat... Solicitação de reembolso para produto Auto Live Shop não processada pela plataforma Cakto</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-para-produto-auto-live-shop-nao-processada-pela-plataforma-cakto_Zejb3D4JhCq2o48c/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/vendedor-entregou-produto-diferente-do-anunciado-e-a-plataforma-nao-resolve_vkGIXT8UU80pbQbc/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>pelo pouco que testei</t>
+          <t>chegou faltando conte</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>pelo pouco que testei</t>
+          <t>chegou faltando conte</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4336,39 +4340,35 @@
       <c r="G73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>R$ 197,99.</t>
-        </is>
-      </c>
+      <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Comprei o Plano Starter mensal da Cloakby por R$ 197,99. O produto pelo pouco que testei é excelente. Porém, não atendeu as m... Reclamação Sobre Oferta da Cloakby: propaganda enganosa e péssimo atendimento ao solicitar reembolso</t>
+          <t>Fiz uma compra por lá, produto chegou faltando conteúdo, entro em contato com eles e ZERO atendimento, preciso fazer o estorn... Produto com conteúdo faltante e falta de atendimento para estorno</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-oferta-da-cloakby-propaganda-enganosa-e-pessimo-atendimento-ao-solicitar-reembolso_DS552Q4NU1VCy-bp/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-com-conteudo-faltante-e-falta-de-atendimento-para-estorno_S6A780k9_99Ofap-/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>uma assinatura do site copie</t>
+          <t>um curso na plataforma deles</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>uma assinatura do site copie.ai</t>
+          <t>um curso na plataforma deles</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4394,39 +4394,31 @@
       <c r="G74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>R$ 97,00,</t>
-        </is>
-      </c>
+      <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Realizei a compra de uma assinatura do site copie.ai, no dia 30 de agosto de 2026, às 17h38min, no valor de R$97,00, no site ... Assinatura Copie.ai não liberada após compra e sem retorno do suporte.</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/assinatura-nao-liberada-apos-compra-e-sem-retorno-do-suporte__RpqyPU88WZJtxd1/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-estorno-de-curso-online-com-ma-qualidade-e-falta-de-resposta_rDQ1eDeZL9eCjgqm/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>pois n</t>
+          <t>auto live shop</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>pois n</t>
+          <t>Auto Live Shop</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4459,28 +4451,28 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra mas não gostei do produto pois não atingiu minhas espectativas solicito o reembolso pois está no prazo de gara... Solicitação de reembolso por produto que não atendeu às expectativas dentro do prazo de garantia.</t>
+          <t>Realizei a compra do produto Auto Live Shop, porém, após utilizar o produto, constatei que ele não atendeu às minhas expectat... Solicitação de reembolso para produto Auto Live Shop não processada pela plataforma Cakto</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-que-nao-atendeu-as-expectativas-dentro-do-prazo-de-garantia_4ccUExOzKRUFA4MT/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-para-produto-auto-live-shop-nao-processada-pela-plataforma-cakto_Zejb3D4JhCq2o48c/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>dois cursos de idiomas</t>
+          <t>pelo pouco que testei</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>dois cursos de idiomas</t>
+          <t>pelo pouco que testei</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4495,7 +4487,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4506,35 +4498,39 @@
       <c r="G76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>R$ 197,99.</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de dois cursos de idiomas, no caso Espanhol. Paguei pelos dois cursos via pi, porém só tive acesso a um curso,... Acesso negado a curso de espanhol pago e dificuldade de contato com o suporte para reembolso.</t>
+          <t>Comprei o Plano Starter mensal da Cloakby por R$ 197,99. O produto pelo pouco que testei é excelente. Porém, não atendeu as m... Reclamação Sobre Oferta da Cloakby: propaganda enganosa e péssimo atendimento ao solicitar reembolso</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/acesso-negado-a-curso-de-espanhol-pago-e-dificuldade-de-contato-com-o-suporte-para-reembolso_9d9eJH4OMC_ApZLR/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-oferta-da-cloakby-propaganda-enganosa-e-pessimo-atendimento-ao-solicitar-reembolso_DS552Q4NU1VCy-bp/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
+          <t>uma assinatura do site copie</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
+          <t>uma assinatura do site copie.ai</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4549,7 +4545,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -4560,35 +4556,39 @@
       <c r="G77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 97,00,</t>
+        </is>
+      </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>fiz uma compra de um site hoje e quero solicitar o cancelamento e direito a arrependimento dentro de 7 dias, fiz um pedido ma... Solicitação de cancelamento e estorno de 3 pedidos devido a arrependimento e insatisfação com o produto/site.</t>
+          <t>Realizei a compra de uma assinatura do site copie.ai, no dia 30 de agosto de 2026, às 17h38min, no valor de R$97,00, no site ... Assinatura Copie.ai não liberada após compra e sem retorno do suporte.</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-3-pedidos-devido-a-arrependimento-e-insatisfacao-com-o-produtosite_KUDEd8s3eGajQ3-L/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/assinatura-nao-liberada-apos-compra-e-sem-retorno-do-suporte__RpqyPU88WZJtxd1/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>pois n</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>pois n</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4617,32 +4617,32 @@
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por... Reclamação sobre reembolso de mentoria não processado e falta de suporte</t>
+          <t>Fiz uma compra mas não gostei do produto pois não atingiu minhas espectativas solicito o reembolso pois está no prazo de gara... Solicitação de reembolso por produto que não atendeu às expectativas dentro do prazo de garantia.</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-que-nao-atendeu-as-expectativas-dentro-do-prazo-de-garantia_4ccUExOzKRUFA4MT/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>estrutura para gera</t>
+          <t>dois cursos de idiomas</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>estrutura para gera</t>
+          <t>dois cursos de idiomas</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4671,28 +4671,32 @@
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K79" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de dois cursos de idiomas, no caso Espanhol. Paguei pelos dois cursos via pi, porém só tive acesso a um curso,... Acesso negado a curso de espanhol pago e dificuldade de contato com o suporte para reembolso.</t>
+        </is>
+      </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/acesso-negado-a-curso-de-espanhol-pago-e-dificuldade-de-contato-com-o-suporte-para-reembolso_9d9eJH4OMC_ApZLR/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>youclone no dia 28</t>
+          <t>um site hoje e quero solicitar o cancelam</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Youclone no dia 28</t>
+          <t>um site hoje e quero solicitar o cancelam</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4707,7 +4711,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4725,28 +4729,28 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Comprei o produto Youclone no dia 28/08, no pix.Quando fui entrar no curso, não abre a área de membros e não consig... Cliente não consegue acessar área de membros do curso Youclone e relata falta de suporte.</t>
+          <t>fiz uma compra de um site hoje e quero solicitar o cancelamento e direito a arrependimento dentro de 7 dias, fiz um pedido ma... Solicitação de cancelamento e estorno de 3 pedidos devido a arrependimento e insatisfação com o produto/site.</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-3-pedidos-devido-a-arrependimento-e-insatisfacao-com-o-produtosite_KUDEd8s3eGajQ3-L/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>oduto</t>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>o produto</t>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4761,7 +4765,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4775,32 +4779,32 @@
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Adquiri o produto &amp;quot;Combo Black&amp;quot; do Gustavo de Castro e recebi um e-mail de aprovação de compra sem acesso ao produt... Cliente não tem acesso ao produto &amp;#x27;Combo Black&amp;#x27; após aprovação de compra e não obtém resposta do suporte.</t>
+          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por... Reclamação sobre reembolso de mentoria não processado e falta de suporte</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-tem-acesso-ao-produto-combo-black-apos-aprovacao-de-compra-e-nao-obtem-resposta-do-suporte_na5373f4sUAHpMsE/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>um curso de ia nao gostei do curso e dent</t>
+          <t>estrutura para gera</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>um curso de IA nao gostei do curso e dent</t>
+          <t>estrutura para gera</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4815,7 +4819,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4833,28 +4837,24 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>fiz uma compra de um curso de IA nao gostei do curso e dentro do prazo de 7 dias solicitei o reembolso pelo email que disponi... Estorno</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/estorno_hMRVrko0Dz8fVqsF/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>cuja cobran</t>
+          <t>youclone no dia 28</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>cuja cobran</t>
+          <t>Youclone no dia 28</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4883,28 +4883,32 @@
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K83" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o produto Youclone no dia 28/08, no pix.Quando fui entrar no curso, não abre a área de membros e não consig... Cliente não consegue acessar área de membros do curso Youclone e relata falta de suporte.</t>
+        </is>
+      </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-mensal-nao-efetivada-pela-plataforma-cakto_rOS_H0sA8Ne2Yb4r/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>apostila de psicologia 2025</t>
+          <t>oduto</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Apostila de Psicologia 2025</t>
+          <t>o produto</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4919,7 +4923,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Educação / Concursos e certificações</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4933,32 +4937,32 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico.Já entrei em contato por e-mail,... Apostila de Psicologia 2025 não abre e cliente não obtém retorno sobre compra online.</t>
+          <t>Adquiri o produto &amp;quot;Combo Black&amp;quot; do Gustavo de Castro e recebi um e-mail de aprovação de compra sem acesso ao produt... Cliente não tem acesso ao produto &amp;#x27;Combo Black&amp;#x27; após aprovação de compra e não obtém resposta do suporte.</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-tem-acesso-ao-produto-combo-black-apos-aprovacao-de-compra-e-nao-obtem-resposta-do-suporte_na5373f4sUAHpMsE/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>um curso de ia nao gostei do curso e dent</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Fábrica de Low Ticket</t>
+          <t>um curso de IA nao gostei do curso e dent</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4973,7 +4977,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Educação / Marketing digital e low ticket</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4987,32 +4991,32 @@
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Olá,Solicito o reembolso da compra da Fábrica de Low Ticket.Adquiri o curso com base na promessa apresent... Reembolso solicitado por propaganda enganosa sobre suporte individual no curso Fábrica de Low Ticket</t>
+          <t>fiz uma compra de um curso de IA nao gostei do curso e dentro do prazo de 7 dias solicitei o reembolso pelo email que disponi... Estorno</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/estorno_hMRVrko0Dz8fVqsF/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>incompleto dentro da garantia</t>
+          <t>cuja cobran</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>incompleto dentro da garantia</t>
+          <t>cuja cobran</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5027,7 +5031,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -5045,28 +5049,24 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>Gostaria do reembolso dos seguintes produtos que comprei, está dentro do prazo de garantia de 7 dias.Email de Compra: **... Solicitação de reembolso por produto incompleto dentro da garantia</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-incompleto-dentro-da-garantia_DBUjl2QuaruN_QYD/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-mensal-nao-efetivada-pela-plataforma-cakto_rOS_H0sA8Ne2Yb4r/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>mas n</t>
+          <t>apostila de psicologia 2025</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>mas n</t>
+          <t>Apostila de Psicologia 2025</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Educação / Concursos e certificações</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -5095,28 +5095,32 @@
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K87" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico.Já entrei em contato por e-mail,... Apostila de Psicologia 2025 não abre e cliente não obtém retorno sobre compra online.</t>
+        </is>
+      </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-me-respondem_ddIIs2OseJhlXI2v/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>de streaming n</t>
+          <t>fábrica de low ticket</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>de streaming n</t>
+          <t>Fábrica de Low Ticket</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5131,7 +5135,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Streaming e entretenimento</t>
+          <t>Educação / Marketing digital e low ticket</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5145,28 +5149,32 @@
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K88" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Olá,Solicito o reembolso da compra da Fábrica de Low Ticket.Adquiri o curso com base na promessa apresent... Reembolso solicitado por propaganda enganosa sobre suporte individual no curso Fábrica de Low Ticket</t>
+        </is>
+      </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-desacordo-comercial-por-servico-de-streaming-nao-recebido-e-falta-de-contato-do-vendedor_xHL_Rnpj7hKZ3vjT/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>que eu comprei na plataforma cakto ..o pr</t>
+          <t>incompleto dentro da garantia</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>que eu comprei na plataforma Cakto ..o pr</t>
+          <t>incompleto dentro da garantia</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5181,7 +5189,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -5199,28 +5207,28 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Estou tentando cancelar um produto que eu comprei na plataforma Cakto ..o produto que eu comprei foi calcula chef app não es... Não consigo cancelar o produto Calcula Chef App e não recebo retorno da Cakto.</t>
+          <t>Gostaria do reembolso dos seguintes produtos que comprei, está dentro do prazo de garantia de 7 dias.Email de Compra: **... Solicitação de reembolso por produto incompleto dentro da garantia</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-cancelar-o-produto-calcula-chef-app-e-nao-recebo-retorno-da-cakto_mwF3xbe9PnLeIpH4/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-incompleto-dentro-da-garantia_DBUjl2QuaruN_QYD/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>um curso na sexta feira e n</t>
+          <t>mas n</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>um curso na sexta feira e n</t>
+          <t>mas n</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5235,7 +5243,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -5253,28 +5261,24 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>fiz uma compra de um curso na sexta feira e não recebi, também pelo chat de suporte não tenho retorno. Quero o reembolso, poi... Curso não recebido e falta de retorno do suporte, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-nao-recebido-e-falta-de-retorno-do-suporte-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_KD9yrBbG0QhwORjs/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-me-respondem_ddIIs2OseJhlXI2v/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>uma planilha e n</t>
+          <t>de streaming n</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>uma planilha e n</t>
+          <t>de streaming n</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5289,7 +5293,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Streaming e entretenimento</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -5307,24 +5311,24 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-suporte_245GAIgR4SjdP8m1/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-desacordo-comercial-por-servico-de-streaming-nao-recebido-e-falta-de-contato-do-vendedor_xHL_Rnpj7hKZ3vjT/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>um aplicativo</t>
+          <t>que eu comprei na plataforma cakto ..o pr</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>um aplicativo</t>
+          <t>que eu comprei na plataforma Cakto ..o pr</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5339,7 +5343,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -5357,28 +5361,28 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo ... Reclamação sobre aplicativo não funcional e falta de resposta do suporte para reembolso.</t>
+          <t>Estou tentando cancelar um produto que eu comprei na plataforma Cakto ..o produto que eu comprei foi calcula chef app não es... Não consigo cancelar o produto Calcula Chef App e não recebo retorno da Cakto.</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-cancelar-o-produto-calcula-chef-app-e-nao-recebo-retorno-da-cakto_mwF3xbe9PnLeIpH4/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>material de fonoaudiologia e n</t>
+          <t>um curso na sexta feira e n</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>material de fonoaudiologia e n</t>
+          <t>um curso na sexta feira e n</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5393,7 +5397,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -5411,28 +5415,28 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de material de fonoaudiologia e não no momento de baixar o material era mal feito, a fonoaudióloga sequer exis... Material de fonoaudiologia de má qualidade e recusa de reembolso pela Cacto.</t>
+          <t>fiz uma compra de um curso na sexta feira e não recebi, também pelo chat de suporte não tenho retorno. Quero o reembolso, poi... Curso não recebido e falta de retorno do suporte, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/material-de-fonoaudiologia-de-ma-qualidade-e-recusa-de-reembolso-pela-cacto_zjP5uaGFy2s7z7ZP/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-nao-recebido-e-falta-de-retorno-do-suporte-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_KD9yrBbG0QhwORjs/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>pela cakto e logo realizei o pedido de re</t>
+          <t>uma planilha e n</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>pela cakto e logo realizei o pedido de re</t>
+          <t>uma planilha e n</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5465,28 +5469,24 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>Fiz a compra de um produto pela cakto e logo realizei o pedido de reembolso, porem sem sucesso, pois a plataforma dar erro: &amp;... Erro ao tentar solicitar reembolso de produto na Cakto</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/erro-ao-tentar-solicitar-reembolso-de-produto-na-cakto_ZhxbaEfvn9crLs7c/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-suporte_245GAIgR4SjdP8m1/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>programa n</t>
+          <t>um aplicativo</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>programa n</t>
+          <t>um aplicativo</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5519,28 +5519,28 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra online e o programa não funcionou durante dois dias comecei a enviar para o produtor e para empresa Catho o pe... Reembolso não efetuado e falta de resposta da Catho e do produtor após compra de programa não funcional.</t>
+          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo ... Reclamação sobre aplicativo não funcional e falta de resposta do suporte para reembolso.</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-nao-efetuado-e-falta-de-resposta-da-catho-e-do-produtor-apos-compra-de-programa-nao-funcional_2BTWhdCr7obnyw-X/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria</t>
+          <t>material de fonoaudiologia e n</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria</t>
+          <t>material de fonoaudiologia e n</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5573,24 +5573,28 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K96" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de material de fonoaudiologia e não no momento de baixar o material era mal feito, a fonoaudióloga sequer exis... Material de fonoaudiologia de má qualidade e recusa de reembolso pela Cacto.</t>
+        </is>
+      </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-de-mentoria-nao-encontrada-e-falta-de-suporte-da-cakto-e-do-vendedor_Bt44ofl5iW09TC9d/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/material-de-fonoaudiologia-de-ma-qualidade-e-recusa-de-reembolso-pela-cacto_zjP5uaGFy2s7z7ZP/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>com defeito</t>
+          <t>pela cakto e logo realizei o pedido de re</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>com defeito</t>
+          <t>pela cakto e logo realizei o pedido de re</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5623,33 +5627,33 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>fiz a comprar de um produto , o produto não rodou no meu pc pedi o reembolso e mandaram falar com o produtor , mandei mensage... Reembolso negado e contato com o produtor indisponível após compra de produto com defeito</t>
+          <t>Fiz a compra de um produto pela cakto e logo realizei o pedido de reembolso, porem sem sucesso, pois a plataforma dar erro: &amp;... Erro ao tentar solicitar reembolso de produto na Cakto</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-negado-e-contato-com-o-produtor-indisponivel-apos-compra-de-produto-com-defeito_JT9yPhOIhMRefinl/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/erro-ao-tentar-solicitar-reembolso-de-produto-na-cakto_ZhxbaEfvn9crLs7c/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>frequência da vinci</t>
+          <t>programa n</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Frequência da Vinci</t>
+          <t>programa n</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5659,7 +5663,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Saúde / Tratamentos alternativos</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5677,28 +5681,28 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra por impulso,de um programa de cura do zumbido no ouvido e gostaria de cancelar e ter o extorno do valor pago p... Solicitação de cancelamento e estorno de programa de cura de zumbido</t>
+          <t>Fiz uma compra online e o programa não funcionou durante dois dias comecei a enviar para o produtor e para empresa Catho o pe... Reembolso não efetuado e falta de resposta da Catho e do produtor após compra de programa não funcional.</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-programa-de-cura-de-zumbido_T3cY3B6mIP4BEv_Y/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-nao-efetuado-e-falta-de-resposta-da-catho-e-do-produtor-apos-compra-de-programa-nao-funcional_2BTWhdCr7obnyw-X/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>da vav</t>
+          <t>uma mentoria</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>da Vav</t>
+          <t>uma mentoria</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5713,7 +5717,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -5731,28 +5735,24 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>**Produto não entregue e criador não responde solicito reembolso**Realizei a compra de um produto da Vavá Aca... Produto não entregue e criador não responde, solicito reembolso</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue-e-criador-nao-responde-solicito-reembolso_605Q8ntQ-aQlegi3/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-de-mentoria-nao-encontrada-e-falta-de-suporte-da-cakto-e-do-vendedor_Bt44ofl5iW09TC9d/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>digitalcessada pela cakto</t>
+          <t>com defeito</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>digital processada pela Cakto</t>
+          <t>com defeito</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5785,24 +5785,28 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K100" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>fiz a comprar de um produto , o produto não rodou no meu pc pedi o reembolso e mandaram falar com o produtor , mandei mensage... Reembolso negado e contato com o produtor indisponível após compra de produto com defeito</t>
+        </is>
+      </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-em-compra-de-produto-digital-processada-pela-cakto-com-editado-pelo-reclame-aqui-e-nao-entrega_HJtQooCkVBEfTtMB/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-negado-e-contato-com-o-produtor-indisponivel-apos-compra-de-produto-com-defeito_JT9yPhOIhMRefinl/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>converza.io</t>
+          <t>frequência da vinci</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Converza.io</t>
+          <t>Frequência da Vinci</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5817,7 +5821,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Chatbots / Automação de mensagens</t>
+          <t>Saúde / Tratamentos alternativos</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -5831,28 +5835,32 @@
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra por impulso,de um programa de cura do zumbido no ouvido e gostaria de cancelar e ter o extorno do valor pago p... Solicitação de cancelamento e estorno de programa de cura de zumbido</t>
+        </is>
+      </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/exijo-reembolso-servico-nao-funciona-e-suporte-nao-responde_OPi-rimJXtkjo2yB/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-programa-de-cura-de-zumbido_T3cY3B6mIP4BEv_Y/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>comprad... pagamento via pix n</t>
+          <t>da vav</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>comprad... Pagamento via PIX n</t>
+          <t>da Vav</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5867,7 +5875,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -5885,28 +5893,28 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Fiz o pgto via PIX para a empresa seguro-vidasaudavel.site através da Cakto Pay, porém não me foi fornecido o produto comprad... Pagamento via PIX não resultou na entrega do produto, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
+          <t>**Produto não entregue e criador não responde solicito reembolso**Realizei a compra de um produto da Vavá Aca... Produto não entregue e criador não responde, solicito reembolso</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-resultou-na-entrega-do-produto-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_cbUdm8Fq5-5oanwH/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue-e-criador-nao-responde-solicito-reembolso_605Q8ntQ-aQlegi3/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>curso online</t>
+          <t>digitalcessada pela cakto</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>curso online</t>
+          <t>digital processada pela Cakto</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5921,7 +5929,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Crescimento em redes sociais</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5939,33 +5947,29 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra de curso online, pgn no Instagran que se chama Amigurumi Brasil, pgn com mais de 1.5 k de seguidores, e até ho... Curso online não entregue após pagamento, com falha na comunicação e solicitação de estorno.</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-online-nao-entregue-apos-pagamento-com-falha-na-comunicacao-e-solicitacao-de-estorno_-bekag5hY78F-1mM/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-em-compra-de-produto-digital-processada-pela-cakto-com-editado-pelo-reclame-aqui-e-nao-entrega_HJtQooCkVBEfTtMB/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>mas at</t>
+          <t>converza.io</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>mas at</t>
+          <t>Converza.io</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -5975,7 +5979,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Chatbots / Automação de mensagens</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5989,25 +5993,183 @@
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/exijo-reembolso-servico-nao-funciona-e-suporte-nao-responde_OPi-rimJXtkjo2yB/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>comprad... pagamento via pix n</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>comprad... Pagamento via PIX n</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Fiz o pgto via PIX para a empresa seguro-vidasaudavel.site através da Cakto Pay, porém não me foi fornecido o produto comprad... Pagamento via PIX não resultou na entrega do produto, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-resultou-na-entrega-do-produto-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_cbUdm8Fq5-5oanwH/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>curso online</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>curso online</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Crescimento em redes sociais</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de curso online, pgn no Instagran que se chama Amigurumi Brasil, pgn com mais de 1.5 k de seguidores, e até ho... Curso online não entregue após pagamento, com falha na comunicação e solicitação de estorno.</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-online-nao-entregue-apos-pagamento-com-falha-na-comunicacao-e-solicitacao-de-estorno_-bekag5hY78F-1mM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>mas at</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>mas at</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
         <is>
           <t>Fiz uma compra na loja e quero reembolsar meu produto mas até agora não fui atendido Reembolso</t>
         </is>
       </c>
-      <c r="L104" s="2" t="inlineStr">
+      <c r="L107" s="2" t="inlineStr">
         <is>
           <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso_Ou6F1k9zy_0W3ATN/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L104"/>
+  <autoFilter ref="A1:L107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6074,13 +6236,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -6089,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -6099,13 +6261,13 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
@@ -6114,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -6145,17 +6307,17 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
@@ -6170,17 +6332,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
@@ -6189,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -6245,7 +6407,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria / Mentoria</t>
+          <t>Ferramentas / Aplicativos</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -6270,7 +6432,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Educação / Idiomas</t>
+          <t>Educação e consultoria / Mentoria</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -6295,17 +6457,17 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Comunidades / Mentoria de negócios</t>
+          <t>Educação / Idiomas</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -6320,17 +6482,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Marketing / Comunidades de negócios</t>
+          <t>Comunidades / Mentoria de negócios</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
@@ -6345,7 +6507,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Arte personalizada / IA generativa</t>
+          <t>Marketing / Comunidades de negócios</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -6370,7 +6532,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria / Cursos online</t>
+          <t>Arte personalizada / IA generativa</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -6395,7 +6557,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Ferramentas / Aplicativos</t>
+          <t>Educação e consultoria / Cursos online</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -6653,7 +6815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -6690,7 +6852,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -6720,7 +6882,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -6735,7 +6897,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6765,7 +6927,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6780,7 +6942,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -6825,7 +6987,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6840,7 +7002,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -6855,7 +7017,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -6870,7 +7032,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -6885,7 +7047,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -6915,7 +7077,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -6930,7 +7092,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -6945,7 +7107,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -6960,7 +7122,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -6975,7 +7137,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -6990,7 +7152,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -7020,7 +7182,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -7035,7 +7197,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -7050,7 +7212,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -7065,13 +7227,13 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>curso online</t>
+          <t>curso de yoga n</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -7080,18 +7242,18 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>curso online capsulas gourmet e c</t>
+          <t>curso online</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
@@ -7101,37 +7263,37 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>códigos lucrativos</t>
+          <t>curso online capsulas gourmet e c</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>da vav</t>
+          <t>códigos lucrativos</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>de baixa qualidade</t>
+          <t>da vav</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -7140,28 +7302,28 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>de baixa qualidade</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>de seguran</t>
+          <t>de postagem autom</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -7170,28 +7332,28 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>de streaming n</t>
+          <t>de seguran</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>diferente do anunciado e a plataforma n</t>
+          <t>de streaming n</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -7200,13 +7362,13 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>digital</t>
+          <t>diferente do anunciado e a plataforma n</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -7215,13 +7377,13 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>digitalcessada pela cakto</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -7230,13 +7392,13 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>directspeed</t>
+          <t>digital n</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -7245,13 +7407,13 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>dois aplicativo e n</t>
+          <t>digitalcessada pela cakto</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -7260,43 +7422,43 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>dois cursos de idiomas</t>
+          <t>directspeed</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>e a plataforma deveria no m</t>
+          <t>dois aplicativo e n</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>e conseguiu acess</t>
+          <t>dois cursos de idiomas</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -7305,58 +7467,58 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>e ele nao chegou quero meu dinheiro de volta ra ad</t>
+          <t>e a plataforma deveria no m</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>e n</t>
+          <t>e conseguiu acess</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>e solicita</t>
+          <t>e ele nao chegou quero meu dinheiro de volta ra ad</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>em um site na internet e ao abrir o email</t>
+          <t>e n</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -7365,13 +7527,13 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>espia f</t>
+          <t>e solicita</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -7380,13 +7542,13 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>estrutura para gera</t>
+          <t>em um site na internet e ao abrir o email</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -7395,28 +7557,28 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>espia f</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>frequência da vinci</t>
+          <t>estrutura para gera</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -7425,13 +7587,13 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -7440,13 +7602,13 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>grupo vip</t>
+          <t>frequência da vinci</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -7455,28 +7617,28 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>ia academy</t>
+          <t>fábrica de low ticket</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>incompleto dentro da garantia</t>
+          <t>grupo vip</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -7485,13 +7647,13 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>ia academy</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -7500,43 +7662,43 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>incompleto dentro da garantia</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
+          <t>interactive live</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -7545,13 +7707,13 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>manuscrito dos milagres</t>
+          <t>low ticket do zero</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -7560,43 +7722,43 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>mas at</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>mas n</t>
+          <t>manuscrito dos milagres</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>material de fonoaudiologia e n</t>
+          <t>mas at</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -7605,13 +7767,13 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>mentoria nova profissão</t>
+          <t>mas n</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -7626,22 +7788,22 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>material de fonoaudiologia e n</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>na plataforma e n</t>
+          <t>mentoria nova profissão</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -7650,13 +7812,13 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -7665,13 +7827,13 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>nessa plataforma</t>
+          <t>na plataforma e n</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -7680,28 +7842,28 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>no ... reembolso dentro do prazo</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>no qual n</t>
+          <t>nessa plataforma</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -7710,13 +7872,13 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>no valor de 97 reais que nao gostei pedi</t>
+          <t>no ... reembolso dentro do prazo</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -7725,28 +7887,28 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>não conseguiu confirmar a distribuidora</t>
+          <t>no qual n</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>oduto</t>
+          <t>no valor de 97 reais que nao gostei pedi</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -7755,28 +7917,28 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>on line rj comercio varejista de acessorios ltda</t>
+          <t>não conseguiu confirmar a distribuidora</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>onde dizia que tinha v</t>
+          <t>oduto</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7785,43 +7947,43 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>on line rj comercio varejista de acessorios ltda</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>pack canva</t>
+          <t>onde dizia que tinha v</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>pela cakto e logo realizei o pedido de re</t>
+          <t>online</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -7830,43 +7992,43 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>pelo pouco que testei</t>
+          <t>pack canva</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>pelo qual paguei n</t>
+          <t>pela cakto e logo realizei o pedido de re</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>perfect academy</t>
+          <t>pelo pouco que testei</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -7881,22 +8043,22 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>plataforma home office</t>
+          <t>pelo qual paguei n</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>plataforma tikspy pelo valor de r</t>
+          <t>perfect academy</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -7905,13 +8067,13 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>pois n</t>
+          <t>plataforma home office</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -7920,13 +8082,13 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>produto malu</t>
+          <t>plataforma tikspy pelo valor de r</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -7941,7 +8103,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>programa n</t>
+          <t>pois n</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -7950,13 +8112,13 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>que eu comprei na plataforma cakto ..o pr</t>
+          <t>produto malu</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -7965,13 +8127,13 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>quemetia trazer minha conta do free f</t>
+          <t>programa n</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -7980,28 +8142,28 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>ra ads previous slide next slide compartilhe resp</t>
+          <t>que era pelo gmail mandei a mensagem expl</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>receb... propaganda enganosa</t>
+          <t>que eu comprei na plataforma cakto ..o pr</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -8010,18 +8172,18 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>retrato da sua alma gêmea</t>
+          <t>quemetia trazer minha conta do free f</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
@@ -8031,22 +8193,22 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>servi</t>
+          <t>ra ads previous slide next slide compartilhe resp</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>simplesmente n</t>
+          <t>receb... propaganda enganosa</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8055,43 +8217,43 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>spygram</t>
+          <t>retrato da sua alma gêmea</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>servi</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>tikedit pela perfectpay</t>
+          <t>simplesmente n</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -8100,13 +8262,13 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>tomei</t>
+          <t>spygram</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -8115,28 +8277,28 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>tudo dentro do prazo tudo certinho e ate</t>
+          <t>stalkeia</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>turminha alfakids</t>
+          <t>tikedit pela perfectpay</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -8151,7 +8313,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>um aplicativo</t>
+          <t>tomei</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -8160,13 +8322,13 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>um aplicativo de monitoramento pelo an</t>
+          <t>tudo dentro do prazo tudo certinho e ate</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -8175,13 +8337,13 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>um curso</t>
+          <t>turminha alfakids</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -8190,13 +8352,13 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>um curso chamado geniun shop</t>
+          <t>um aplicativo</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -8205,13 +8367,13 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>um curso de arais amador paguei e n</t>
+          <t>um aplicativo de monitoramento pelo an</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -8220,13 +8382,13 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>um curso de ia nao gostei do curso e dent</t>
+          <t>um curso</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -8235,28 +8397,28 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>um curso chamado geniun shop</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>um curso na plataforma deles</t>
+          <t>um curso de arais amador paguei e n</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -8265,13 +8427,13 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>um curso na sexta feira e n</t>
+          <t>um curso de ia nao gostei do curso e dent</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -8280,13 +8442,13 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>um curso no dia 01</t>
+          <t>um curso e</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -8295,13 +8457,13 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>um grupo vip no dia 20</t>
+          <t>um curso na plataforma deles</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
@@ -8310,13 +8472,13 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>um painel e n</t>
+          <t>um curso na sexta feira e n</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -8325,28 +8487,28 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
+          <t>um curso no dia 01</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>um vendedor que usa os servi</t>
+          <t>um grupo vip no dia 20</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -8355,13 +8517,13 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>uma assinatura do site copie</t>
+          <t>um painel e n</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -8370,33 +8532,33 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>uma ferramenta de automa</t>
+          <t>um site hoje e quero solicitar o cancelam</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>uma m</t>
+          <t>um vendedor que usa os servi</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
@@ -8406,7 +8568,7 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>uma mentoria</t>
+          <t>uma assinatura do site copie</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -8415,48 +8577,48 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>uma ferramenta de automa</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>uma planilha e n</t>
+          <t>uma m</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>umgrama de karaoke e est</t>
+          <t>uma mentoria</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
@@ -8466,7 +8628,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>validação cadastral: em análise</t>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -8475,13 +8637,13 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>vendido pela appluna.net</t>
+          <t>uma planilha e n</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -8490,37 +8652,82 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>youclone no dia 28</t>
+          <t>umgrama de karaoke e est</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
+          <t>validação cadastral: em análise</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>vendido pela appluna.net</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
           <t>zap radar</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="C124" s="4" t="n">
-        <v>12</v>
+      <c r="C127" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -6882,7 +6882,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -7152,7 +7152,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -7332,7 +7332,7 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -7377,7 +7377,7 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -7467,7 +7467,7 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -7632,7 +7632,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
@@ -7647,7 +7647,7 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -7737,7 +7737,7 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68">
@@ -7842,7 +7842,7 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -7857,7 +7857,7 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -7887,7 +7887,7 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -8067,7 +8067,7 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
@@ -8142,7 +8142,7 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -8157,7 +8157,7 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99">
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -8322,7 +8322,7 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -8337,7 +8337,7 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -8352,7 +8352,7 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -8427,7 +8427,7 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
@@ -8472,7 +8472,7 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116">
@@ -8562,7 +8562,7 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -8592,7 +8592,7 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
@@ -8607,7 +8607,7 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120">
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122">
@@ -8652,7 +8652,7 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127">
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -561,11 +561,11 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -615,11 +615,11 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -669,11 +669,11 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -723,11 +723,11 @@
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -781,11 +781,11 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -835,11 +835,11 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
@@ -889,11 +889,11 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -943,11 +943,11 @@
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
@@ -993,11 +993,11 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1051,11 +1051,11 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1105,11 +1105,11 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1163,11 +1163,11 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1217,11 +1217,11 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1271,11 +1271,11 @@
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1325,11 +1325,11 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -1383,11 +1383,11 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
@@ -1433,11 +1433,11 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1541,11 +1541,11 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1595,11 +1595,11 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1615,17 +1615,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>perfect academy</t>
+          <t>digital apexshop vital</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Perfect Academy</t>
+          <t>digital ApexShop Vital</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria / Cursos online</t>
+          <t>Streaming e entretenimento</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1646,35 +1646,39 @@
       <c r="G22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>R$ 179,90,</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Comprei um curso na perfect academy, mais o curso veio incompleto, fui tentar pedir meu reembolso, onde me deparei sem suport... Curso incompleto e falta de suporte para reembolso na Perfect Academy</t>
+          <t>Realizei em 24/08/2026 a compra do produto digital ApexShop Vitalício, no valor de R$ 179,90, por meio da plataforma Perfect Pay. Logo após a contratação, solicitei formalmente o cancelamento da compra e a restituição integral do valor pago, dentro do prazo informado e previsto para o direito de arrependimento. Ao entrar em contato com a Perfect Pay, fui orientada a procurar diretamente o suporte do produto e, caso não recebesse resposta em até 2 dias úteis, deveria encaminhar os comprovantes da</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/curso-incompleto-e-falta-de-suporte-para-reembolso-na-perfect-academy_xfFtbFJD4cncefLz/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/perfect-pay-nao-resolve-cancelamento-e-reembolso-repetindo-orientacoes_zJl8k8FgpoKAMXba/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>aplicativo</t>
+          <t>um usu</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>aplicativo</t>
+          <t>um usu</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1703,32 +1707,32 @@
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Eu adquiri uma compra pela [Editado pelo Reclame Aqui] prometendo acesso a um app pago e após pagar o aplicativo simplesmente... Cobrança indevida e solicitação de estorno após compra de aplicativo</t>
+          <t>Fiz uma compra de um usuário da aplicação e não recebi o que estava sendo anunciado e pedir reembolso e enviei vários e-mails e sempre dando uma desculpa e não fez o reembolso mandando entrar em contato com o vendedor e ao entrar em contato o e-mail do vendedor não funciona e não tem telefone pra contato sendo assim a perfectpay fica enrolando pra fazer o [Editado pelo Reclame Aqui] RA Ads</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-solicitacao-de-estorno-apos-compra-de-aplicativo_k54KbhcZ8MWgLTn0/</t>
+          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-nao-recebido-e-dificuldade-de-reembolso-na-perfect-pay_zlFPokdZpRPcKoYM/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>tikedit pela perfectpay</t>
+          <t>digital ap</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TikEdit pela PerfectPay</t>
+          <t>digital ap</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1738,12 +1742,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1754,31 +1758,39 @@
       <c r="G24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>R$ 88,19,</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra do produto +600 Horas de Roteiros Prontos para Live Shop, no dia 19/08/2026, pelo valor de R$ 88,19, pago via PIX. Após a compra, decidi não continuar com o produto e solicitei o cancelamento da compra e o reembolso do valor pago. No dia 24/08/2026, enviei uma solicitação por escrito pedindo formalmente o cancelamento e o reembolso, informando os dados da compra e o número do pedido. Até o momento, porém, não obtive uma solução para o meu pedido. Também tive dificuldades para e</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/recusa-de-reembolso-em-renovacao-automatica-de-produto-tikedit-pela-perfectpay_7DczqrMSjVJHqp26/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/cliente-solicita-cancelamento-e-reembolso-de-produto-digital-apos-dificuldades-de-contato-e-falta-de-solucao_iqfFFkNKnKahBQk5/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>vendido pela appluna.net</t>
+          <t>no dia</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>vendido pela Appluna.net</t>
+          <t>no dia</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1788,12 +1800,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1804,35 +1816,39 @@
       <c r="G25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>R$ 86,80</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>A referida empresa, alega ser uma plataforma de gerenciamento de pagamentos online que informa não ter responsabilidade sobre... Perfectpay cobra por serviço, mas não resolve problemas de acesso ao produto vendido pela Appluna.net</t>
+          <t>Comprei um produto no dia **26/08** e, no mesmo dia, solicitei o reembolso, pois o produto recebido não correspondia ao que era prometido na oferta. Ao entrar em contato com a **Cakto**, fui informado de que o reembolso deveria ser solicitado diretamente ao produtor. Tentei contato com o produtor durante **3 dias**, mas não obtive nenhum retorno. No dia **29/08**, entrei novamente em contato com um atendente da Cakto pelo WhatsApp, porém também não tive retorno. Fiz uma nova tentativa de contato</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perfectpay-cobra-por-servico-mas-nao-resolve-problemas-de-acesso-ao-produto-vendido-pela_a5_1eWXf4MZ6sZZ7/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-de-produto-nao-correspondente-a-oferta-apos-8-dias-de-tentativas-de-contato-sem-sucesso_vgLnIAw9NhALvEvt/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>aparece na perfect pay mas o mesmo n</t>
+          <t>incompleto dentro do prazo de 7 dias. n</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>APARECE NA PERFECT PAY MAS O MESMO N</t>
+          <t>incompleto dentro do prazo de 7 dias. N</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1842,12 +1858,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1861,32 +1877,32 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Fiz A COMPRA DE UM SERVIÇO NO QUAL É [Editado pelo Reclame Aqui] E O PRODUTO APARECE NA PERFECT PAY MAS O MESMO NÃO SE RESPO... Compra de serviço com promessa de [Editado pelo Reclame Aqui] e Perfect Pay se isenta de responsabilidade</t>
+          <t>Fiz uma compra na caktos mais o produto veio incompleto pedi o reembolso dentro do 7 dias ..eles nao fizeram o reembolso. RA Ads</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-com-promessa-de-editado-pelo-reclame-aqui-e-perfect-pay-se-isenta-de-responsabilidade_0DOgqsLTHMXBEQUg/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-nao-realizado-apos-devolucao-de-produto-incompleto-dentro-do-prazo-de-7-dias_ESBgjxHcHH6maS_a/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>receb... propaganda enganosa</t>
+          <t>para poder solicitar o cancelamento</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>receb... Propaganda enganosa</t>
+          <t>para poder solicitar o cancelamento</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1896,12 +1912,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>PerfectPay</t>
+          <t>Cakto</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1915,33 +1931,37 @@
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de uma assinatura online, porém o serviço não me atendeu, eu solicitei o cancelamento dentro do prazo de 7 dias por e-mail no suporte da empresa, porém até hoje não tive o retorno sobre o cancelamento do pedido. Solicito o cancelamento e estorno eu valor. A empresa não tem nenhum campo no site deles ou do produto para poder solicitar o cancelamento, somente por e-mail, quando enviamos um e-mail só vem resposta automática, aguardo previdências. RA Ads</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/propaganda-enganosa_zOGr7sPQQhH7ROqM/</t>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-assinatura-online-nao-respondida-pelo-suporte_t696AVuN0Vj7PGWm/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>plataforma home office</t>
+          <t>perfect academy</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Plataforma Home Office</t>
+          <t>Perfect Academy</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1951,7 +1971,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Educação e consultoria / Cursos online</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1965,32 +1985,32 @@
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Solicito o cancelamento e o reembolso do valor pago pelo produto Plataforma Home Office, vinculado ao e-mail ***** . O produt... Solicitação de cancelamento e reembolso de Plataforma Home Office por propaganda enganosa.</t>
+          <t>Comprei um curso na perfect academy, mais o curso veio incompleto, fui tentar pedir meu reembolso, onde me deparei sem suport... Curso incompleto e falta de suporte para reembolso na Perfect Academy</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-plataforma-home-office-por-propaganda-enganosa_Z3FnnwZ03NBXKWFQ/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/curso-incompleto-e-falta-de-suporte-para-reembolso-na-perfect-academy_xfFtbFJD4cncefLz/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>aplicativo</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>aplicativo</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2005,7 +2025,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2019,32 +2039,32 @@
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, In... Reclamação sobre produto de postagem automática com cobranças adicionais, sem retorno do suporte , sem liberação do prometido e com acesso restrito ao conteúdo,e falta de reembolso.</t>
+          <t>Eu adquiri uma compra pela [Editado pelo Reclame Aqui] prometendo acesso a um app pago e após pagar o aplicativo simplesmente... Cobrança indevida e solicitação de estorno após compra de aplicativo</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-solicitacao-de-estorno-apos-compra-de-aplicativo_k54KbhcZ8MWgLTn0/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>acesso a conversas do instagram n</t>
+          <t>tikedit pela perfectpay</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>acesso a conversas do Instagram n</t>
+          <t>TikEdit pela PerfectPay</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2059,7 +2079,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Crescimento em redes sociais</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2073,28 +2093,28 @@
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-acesso-a-conversas-do-instagram-nao-realizada-e-solicitacao-de-reembolso_bEr04z5n0qvNdmJf/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/recusa-de-reembolso-em-renovacao-automatica-de-produto-tikedit-pela-perfectpay_7DczqrMSjVJHqp26/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>códigos lucrativos</t>
+          <t>vendido pela appluna.net</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Códigos Lucrativos</t>
+          <t>vendido pela Appluna.net</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2109,7 +2129,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2123,28 +2143,32 @@
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>A referida empresa, alega ser uma plataforma de gerenciamento de pagamentos online que informa não ter responsabilidade sobre... Perfectpay cobra por serviço, mas não resolve problemas de acesso ao produto vendido pela Appluna.net</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perfectpay-cobra-por-servico-mas-nao-resolve-problemas-de-acesso-ao-produto-vendido-pela_a5_1eWXf4MZ6sZZ7/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>zap radar</t>
+          <t>aparece na perfect pay mas o mesmo n</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ZAP Radar</t>
+          <t>APARECE NA PERFECT PAY MAS O MESMO N</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2159,7 +2183,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de espionagem / WhatsApp</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2173,32 +2197,32 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o ... Solicitação de estorno de compra no site ZAP Radar por não recebimento de relatório.</t>
+          <t>Fiz A COMPRA DE UM SERVIÇO NO QUAL É [Editado pelo Reclame Aqui] E O PRODUTO APARECE NA PERFECT PAY MAS O MESMO NÃO SE RESPO... Compra de serviço com promessa de [Editado pelo Reclame Aqui] e Perfect Pay se isenta de responsabilidade</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-com-promessa-de-editado-pelo-reclame-aqui-e-perfect-pay-se-isenta-de-responsabilidade_0DOgqsLTHMXBEQUg/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>receb... propaganda enganosa</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>receb... Propaganda enganosa</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2227,28 +2251,28 @@
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/propaganda-enganosa_zOGr7sPQQhH7ROqM/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>plataforma home office</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>Plataforma Home Office</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2263,7 +2287,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2277,28 +2301,32 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Solicito o cancelamento e o reembolso do valor pago pelo produto Plataforma Home Office, vinculado ao e-mail ***** . O produt... Solicitação de cancelamento e reembolso de Plataforma Home Office por propaganda enganosa.</t>
+        </is>
+      </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-e-nao-recebi_IgLy-Z3TgKa5WfbK/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-plataforma-home-office-por-propaganda-enganosa_Z3FnnwZ03NBXKWFQ/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>chamado protocolo black digital e comprei</t>
+          <t>de postagem autom</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>chamado Protocolo Black Digital e comprei</t>
+          <t>de postagem autom</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2313,7 +2341,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2327,32 +2355,32 @@
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Eu comprei um produto chamado Protocolo Black Digital e comprei dois order bumps, e o produto é horrível, na hora de eu pedir... Impossibilidade de solicitar reembolso para o produto Protocolo Black Digital e order bumps.</t>
+          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, In... Reclamação sobre produto de postagem automática com cobranças adicionais, sem retorno do suporte , sem liberação do prometido e com acesso restrito ao conteúdo,e falta de reembolso.</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/impossibilidade-de-solicitar-reembolso-para-o-produto-protocolo-black-digital-e-order-bumps_KUmvlWU2BBaqoLGc/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>aplicativo viewerspy com tr</t>
+          <t>acesso a conversas do instagram n</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>aplicativo ViewerSpy com tr</t>
+          <t>acesso a conversas do Instagram n</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2367,7 +2395,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Crescimento em redes sociais</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2381,32 +2409,28 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra de aplicativo ViewerSpy com três pagamentos, mas se tratava de [Editado pelo Reclame Aqui], quero meu dinheiro... [Editado pelo Reclame Aqui] em aplicativo ViewerSpy com cobrança indevida, solicitação de [Editado pelo Reclame Aqui].</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-viewerspy-com-cobranca-indevida-solicitacao-de-editado-pelo-reclame-aqui_4jVYpRQh7FZ9NsuM/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-acesso-a-conversas-do-instagram-nao-realizada-e-solicitacao-de-reembolso_bEr04z5n0qvNdmJf/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>servi</t>
+          <t>códigos lucrativos</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>servi</t>
+          <t>Códigos Lucrativos</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2421,7 +2445,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2435,32 +2459,28 @@
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra me garantindo acesso a fotos e conversas de um WhatsApp meu mesmo que perdi acesso, mas fui enganado paguei tu... Compra de serviço para recuperação de WhatsApp que direciona para página de curso.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-para-recuperacao-de-whatsapp-que-direciona-para-pagina-de-curso_9jbLXBtTk54j7-aK/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>zap radar</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>ZAP Radar</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2475,7 +2495,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de espionagem / WhatsApp</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2489,28 +2509,32 @@
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o ... Solicitação de estorno de compra no site ZAP Radar por não recebimento de relatório.</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-editado-pelo-reclame-aqui-e-solicitacao-de-editado-pelo-reclame-aqui-com-base-no-direito-de-arrependimento_SenuNicKKSMOvgEa/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>uma ferramenta de automa</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>uma ferramenta de automa</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2525,7 +2549,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2539,28 +2563,28 @@
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-ferramenta-de-automacao-nao-recebida_3ia2l_X9I98IiU5Q/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>simplesmente n</t>
+          <t>online</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>simplesmente n</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2575,7 +2599,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2589,32 +2613,28 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Fiz a compra de um sistema multijogos da Retrogame Ramos, porém o produto simplesmente não funcionou. Solicitei o reembolso e... Reclamação sobre sistema multijogos não funcional e falta de reembolso pela Retrogame Ramos</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-sistema-multijogos-nao-funcional-e-falta-de-reembolso-pela-retrogame-ramos_yXzSmLa6zWMj18Hq/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-e-nao-recebi_IgLy-Z3TgKa5WfbK/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>no valor de 97 reais que nao gostei pedi</t>
+          <t>chamado protocolo black digital e comprei</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>no valor de 97 reais que nao gostei pedi</t>
+          <t>chamado Protocolo Black Digital e comprei</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2643,32 +2663,32 @@
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>[Editado pelo Reclame Aqui]. comprei um produto no valor de 97 reais que nao gostei pedi o reembolso e ninguem resolve nada m... Reclamação sobre propaganda enganosa e dificuldade em obter reembolso de produto.</t>
+          <t>Eu comprei um produto chamado Protocolo Black Digital e comprei dois order bumps, e o produto é horrível, na hora de eu pedir... Impossibilidade de solicitar reembolso para o produto Protocolo Black Digital e order bumps.</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-propaganda-enganosa-e-dificuldade-em-obter-reembolso-de-produto_NexaAcyAJfkO5zUN/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/impossibilidade-de-solicitar-reembolso-para-o-produto-protocolo-black-digital-e-order-bumps_KUmvlWU2BBaqoLGc/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>quemetia trazer minha conta do free f</t>
+          <t>aplicativo viewerspy com tr</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>que prometia trazer minha conta do free f</t>
+          <t>aplicativo ViewerSpy com tr</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2683,7 +2703,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2697,37 +2717,37 @@
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Quero reembolso do meu dinheiro, comprei um produto que prometia trazer minha conta do free fire de volta, mais era tudo [Edi... Produto de Free Fire prometia recuperar conta, mas era [Editado pelo Reclame Aqui] e cliente pede reembolso.</t>
+          <t>Fiz uma compra de aplicativo ViewerSpy com três pagamentos, mas se tratava de [Editado pelo Reclame Aqui], quero meu dinheiro... [Editado pelo Reclame Aqui] em aplicativo ViewerSpy com cobrança indevida, solicitação de [Editado pelo Reclame Aqui].</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-de-free-fire-prometia-recuperar-conta-mas-era-editado-pelo-reclame-aqui-e-cliente-pede-reembolso_6E9DzuuICeSs7-BW/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-viewerspy-com-cobranca-indevida-solicitacao-de-editado-pelo-reclame-aqui_4jVYpRQh7FZ9NsuM/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>spygram</t>
+          <t>servi</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Spygram</t>
+          <t>servi</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2751,28 +2771,32 @@
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra me garantindo acesso a fotos e conversas de um WhatsApp meu mesmo que perdi acesso, mas fui enganado paguei tu... Compra de serviço para recuperação de WhatsApp que direciona para página de curso.</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-reembolso-de-pagamentos-via-pix-para-o-programa-spygram-identificado-como-editado-pelo-reclame-aqui_tx5DRYfAycgJL_5j/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-para-recuperacao-de-whatsapp-que-direciona-para-pagina-de-curso_9jbLXBtTk54j7-aK/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>um curso de arais amador paguei e n</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>um curso de arais amador paguei e n</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2787,7 +2811,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2801,32 +2825,28 @@
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra de um curso de arais amador paguei e não recebi segue comprovante de pagamento Fui vítima de [Editado pelo Reclame Aqui]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/fui-vitima-de-editado-pelo-reclame-aqui_eaEOE7rI3vDh1NKM/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-editado-pelo-reclame-aqui-e-solicitacao-de-editado-pelo-reclame-aqui-com-base-no-direito-de-arrependimento_SenuNicKKSMOvgEa/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>tudo dentro do prazo tudo certinho e ate</t>
+          <t>uma ferramenta de automa</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>tudo dentro do prazo tudo certinho e ate</t>
+          <t>uma ferramenta de automa</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2855,28 +2875,28 @@
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso_3QFTCw6-Ygo025v1/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-ferramenta-de-automacao-nao-recebida_3ia2l_X9I98IiU5Q/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>dois aplicativo e n</t>
+          <t>simplesmente n</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>dois aplicativo e n</t>
+          <t>simplesmente n</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2891,7 +2911,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2902,39 +2922,35 @@
       <c r="G46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>R$ 27,90</t>
-        </is>
-      </c>
+      <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Bom dia ! Fiz uma compra de dois aplicativo e não recebi o aplicativo, no valor de R$ 27,90 e outro de R$ 19,00 às 16:35 h no... Compra de aplicativos não recebidos, solicitação de reembolso.</t>
+          <t>Fiz a compra de um sistema multijogos da Retrogame Ramos, porém o produto simplesmente não funcionou. Solicitei o reembolso e... Reclamação sobre sistema multijogos não funcional e falta de reembolso pela Retrogame Ramos</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-nao-recebidos-solicitacao-de-reembolso_IVdC0jac41EFjNhF/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-sistema-multijogos-nao-funcional-e-falta-de-reembolso-pela-retrogame-ramos_yXzSmLa6zWMj18Hq/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>espia f</t>
+          <t>no valor de 97 reais que nao gostei pedi</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>espia f</t>
+          <t>no valor de 97 reais que nao gostei pedi</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2949,7 +2965,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2963,32 +2979,32 @@
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Comprei o app espia fácil pro e não me deram o acesso. Quero reembolso Cair em um [Editado pelo Reclame Aqui]</t>
+          <t>[Editado pelo Reclame Aqui]. comprei um produto no valor de 97 reais que nao gostei pedi o reembolso e ninguem resolve nada m... Reclamação sobre propaganda enganosa e dificuldade em obter reembolso de produto.</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cair-em-um-editado-pelo-reclame-aqui_3GiaHX5kQ4C877x9/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-propaganda-enganosa-e-dificuldade-em-obter-reembolso-de-produto_NexaAcyAJfkO5zUN/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>um aplicativo de monitoramento pelo an</t>
+          <t>quemetia trazer minha conta do free f</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>um aplicativo de monitoramento pelo an</t>
+          <t>que prometia trazer minha conta do free f</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3003,7 +3019,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3017,37 +3033,37 @@
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um aplicativo de monitoramento pelo anúncio no YouTube paguei 46.90 e levei um [Editado pelo Reclame Aqui] ... [Editado pelo Reclame Aqui] em aplicativo de monitoramento cliente solicita estorno de valor pago por produto não funcional.</t>
+          <t>Quero reembolso do meu dinheiro, comprei um produto que prometia trazer minha conta do free fire de volta, mais era tudo [Edi... Produto de Free Fire prometia recuperar conta, mas era [Editado pelo Reclame Aqui] e cliente pede reembolso.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-de-monitoramento-cliente-solicita-estorno-de-valor-pago-por-produto-nao-funcional_nGia5bRqbVr80nh-/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-de-free-fire-prometia-recuperar-conta-mas-era-editado-pelo-reclame-aqui-e-cliente-pede-reembolso_6E9DzuuICeSs7-BW/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>um vendedor que usa os servi</t>
+          <t>spygram</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>um vendedor que usa os servi</t>
+          <t>Spygram</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3057,7 +3073,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3071,32 +3087,28 @@
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Efetuei uma compra de um vendedor que usa os serviços da perfect pay para pagamentos. O vendedor não enviou acesso ao produto... Reclamação sobre produto não entregue e solicitação de estorno de valor pago através da Perfect Pay.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-nao-entregue-e-solicitacao-de-estorno-de-valor-pago-atraves-da-perfect-pay_87chbXy48Qb7cTPa/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-reembolso-de-pagamentos-via-pix-para-o-programa-spygram-identificado-como-editado-pelo-reclame-aqui_tx5DRYfAycgJL_5j/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>no ... reembolso dentro do prazo</t>
+          <t>um curso de arais amador paguei e n</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>no ... reembolso dentro do prazo</t>
+          <t>um curso de arais amador paguei e n</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3111,7 +3123,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3125,32 +3137,32 @@
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Solicitei reembolso dentro do prazo, mas não consigo contato com o vendedorAdquiri através da Perfect Pay um produto no ... reembolso dentro do prazo, mas não consigo contato com o vendedor após compra de produto com conteúdo enganoso.</t>
+          <t>Fiz uma compra de um curso de arais amador paguei e não recebi segue comprovante de pagamento Fui vítima de [Editado pelo Reclame Aqui]</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-dentro-do-prazo-mas-nao-consigo-contato-com-o-vendedor-apos-compra-de-produto-com-conteudo-enganoso_msDSOKrJ-W3coXfK/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/fui-vitima-de-editado-pelo-reclame-aqui_eaEOE7rI3vDh1NKM/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>grupo vip</t>
+          <t>tudo dentro do prazo tudo certinho e ate</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>grupo VIP</t>
+          <t>tudo dentro do prazo tudo certinho e ate</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3179,32 +3191,28 @@
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>Bem, eu fiz uma compra na segunda-feira de um grupo vip do js e não estou satisfeito, quero o meu reembolso, ja vou deixar es... Reembolso negado e falta de contato do suporte após compra de grupo VIP</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-negado-e-falta-de-contato-do-suporte-apos-compra-de-grupo-vip_l-3zMo_MYaiaFQbn/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso_3QFTCw6-Ygo025v1/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>e n</t>
+          <t>dois aplicativo e n</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>e n</t>
+          <t>dois aplicativo e n</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3219,7 +3227,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Serviços financeiros / Pix</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3230,35 +3238,39 @@
       <c r="G52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>R$ 27,90</t>
+        </is>
+      </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um produto e não recebi, alegam que não foi pago, já reclamei várias vezes com o vendedor e até agora ele n... Produto não recebido e vendedor alega falta de pagamento, sem resolução.</t>
+          <t>Bom dia ! Fiz uma compra de dois aplicativo e não recebi o aplicativo, no valor de R$ 27,90 e outro de R$ 19,00 às 16:35 h no... Compra de aplicativos não recebidos, solicitação de reembolso.</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-nao-recebido-e-vendedor-alega-falta-de-pagamento-sem-resolucao_4ypAxIw4TPAzgFfj/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-nao-recebidos-solicitacao-de-reembolso_IVdC0jac41EFjNhF/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>de baixa qualidade</t>
+          <t>espia f</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>de baixa qualidade</t>
+          <t>espia f</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3287,32 +3299,32 @@
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra aonde prometia uma reza sagrada que faz prosperar e abrir caminhos, mas a reza não foi feita e me cobraram 3 v... Cobrança indevida e produto de baixa qualidade (PDF de IA) em vez de reza prometida.</t>
+          <t>Comprei o app espia fácil pro e não me deram o acesso. Quero reembolso Cair em um [Editado pelo Reclame Aqui]</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-produto-de-baixa-qualidade-pdf-de-ia-em-vez-de-reza-prometida_S22Bk6Gf4HfO6zVF/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cair-em-um-editado-pelo-reclame-aqui_3GiaHX5kQ4C877x9/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>um painel e n</t>
+          <t>um aplicativo de monitoramento pelo an</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>um painel e n</t>
+          <t>um aplicativo de monitoramento pelo an</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3327,7 +3339,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3341,32 +3353,32 @@
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um painel e não funcionou [Editado pelo Reclame Aqui] Solicito reembolso 19.99 [Editado pelo Reclame Aqui]</t>
+          <t>Fiz uma compra de um aplicativo de monitoramento pelo anúncio no YouTube paguei 46.90 e levei um [Editado pelo Reclame Aqui] ... [Editado pelo Reclame Aqui] em aplicativo de monitoramento cliente solicita estorno de valor pago por produto não funcional.</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui_5xPVEL37uCq2Nl_s/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-de-monitoramento-cliente-solicita-estorno-de-valor-pago-por-produto-nao-funcional_nGia5bRqbVr80nh-/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>um curso chamado geniun shop</t>
+          <t>um vendedor que usa os servi</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>um curso chamado Geniun Shop</t>
+          <t>um vendedor que usa os servi</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3381,7 +3393,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3395,32 +3407,32 @@
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Adquiri um curso chamado Geniun Shop , em 2 de abril de 2026 , fiZ apenas as primeiras aulas, e agora quando resolvi voltar p... Perda de acesso ao curso Geniun Shop após pagamento, sem retorno do suporte.</t>
+          <t>Efetuei uma compra de um vendedor que usa os serviços da perfect pay para pagamentos. O vendedor não enviou acesso ao produto... Reclamação sobre produto não entregue e solicitação de estorno de valor pago através da Perfect Pay.</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perda-de-acesso-ao-curso-geniun-shop-apos-pagamento-sem-retorno-do-suporte_a6tTJhax8GBOg4xh/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-nao-entregue-e-solicitacao-de-estorno-de-valor-pago-atraves-da-perfect-pay_87chbXy48Qb7cTPa/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>onde dizia que tinha v</t>
+          <t>no ... reembolso dentro do prazo</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>onde dizia que tinha v</t>
+          <t>no ... reembolso dentro do prazo</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3435,7 +3447,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3449,32 +3461,32 @@
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Comprei um produto onde dizia que tinha vários fornecedores de roupas no Brasil..mas não tinha o que eu eu queria .por isso q... Reclamação sobre produto com fornecedores de roupas limitados e solicitação de reembolso.</t>
+          <t>Solicitei reembolso dentro do prazo, mas não consigo contato com o vendedorAdquiri através da Perfect Pay um produto no ... reembolso dentro do prazo, mas não consigo contato com o vendedor após compra de produto com conteúdo enganoso.</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-com-fornecedores-de-roupas-limitados-e-solicitacao-de-reembolso_H7FXu4ussEtUSJQC/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-dentro-do-prazo-mas-nao-consigo-contato-com-o-vendedor-apos-compra-de-produto-com-conteudo-enganoso_msDSOKrJ-W3coXfK/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>com defeito e solicita</t>
+          <t>grupo vip</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>com defeito e solicita</t>
+          <t>grupo VIP</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3503,32 +3515,32 @@
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra no Blackxitoficial (meu Gmail é *****). Meu CPF: *****, no valor de 31 reais. O Painel chegou, mas não funcion... Produto com defeito e solicitação de reembolso</t>
+          <t>Bem, eu fiz uma compra na segunda-feira de um grupo vip do js e não estou satisfeito, quero o meu reembolso, ja vou deixar es... Reembolso negado e falta de contato do suporte após compra de grupo VIP</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-com-defeito-e-solicitacao-de-reembolso_GgMl5lRE9VZtuHoJ/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-negado-e-falta-de-contato-do-suporte-apos-compra-de-grupo-vip_l-3zMo_MYaiaFQbn/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>na plataforma e n</t>
+          <t>e n</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>na plataforma e n</t>
+          <t>e n</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3543,7 +3555,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Serviços financeiros / Pix</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3557,32 +3569,32 @@
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>comprei um produto na plataforma e não gostei, quero meu reembolso, foi comprado no pix:Código da compra: ***** Cliente deseja reembolso de aquecedor comprado via Pix por não ter gostado do produto.</t>
+          <t>Fiz uma compra de um produto e não recebi, alegam que não foi pago, já reclamei várias vezes com o vendedor e até agora ele n... Produto não recebido e vendedor alega falta de pagamento, sem resolução.</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cliente-deseja-reembolso-de-aquecedor-comprado-via-pix-por-nao-ter-gostado-do-produto_2qo_Zk1Eh3qTNpQy/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-nao-recebido-e-vendedor-alega-falta-de-pagamento-sem-resolucao_4ypAxIw4TPAzgFfj/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>nessa plataforma</t>
+          <t>de baixa qualidade</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>nessa plataforma</t>
+          <t>de baixa qualidade</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3597,7 +3609,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -3611,32 +3623,32 @@
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Verifiquei a compra de um produto nessa plataforma, solicitei o reembolso junto a produtora do produto e não consegui retorno... Reembolso não resolvido pela plataforma após contato com produtora e cancelamento de cartão.</t>
+          <t>Fiz uma compra aonde prometia uma reza sagrada que faz prosperar e abrir caminhos, mas a reza não foi feita e me cobraram 3 v... Cobrança indevida e produto de baixa qualidade (PDF de IA) em vez de reza prometida.</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-nao-resolvido-pela-plataforma-apos-contato-com-produtora-e-cancelamento-de-cartao_P1PpJ-yUSNmPIVUp/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-produto-de-baixa-qualidade-pdf-de-ia-em-vez-de-reza-prometida_S22Bk6Gf4HfO6zVF/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>em um site na internet e ao abrir o email</t>
+          <t>um painel e n</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>em um site na internet e ao abrir o email</t>
+          <t>um painel e n</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3651,7 +3663,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Serviços financeiros / Pix</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3665,32 +3677,32 @@
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Realizei uma compra de um produto em um site na internet e ao abrir o email enviado me cobraram outra taxa que não estava com... Cobrança de taxa adicional não combinada e falta de acesso ao produto comprado.</t>
+          <t>Fiz uma compra de um painel e não funcionou [Editado pelo Reclame Aqui] Solicito reembolso 19.99 [Editado pelo Reclame Aqui]</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-de-taxa-adicional-nao-combinada-e-falta-de-acesso-ao-produto-comprado__chfFQTX8pupMWB5/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui_5xPVEL37uCq2Nl_s/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>tomei</t>
+          <t>um curso chamado geniun shop</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Tomei</t>
+          <t>um curso chamado Geniun Shop</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3705,7 +3717,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3719,28 +3731,32 @@
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K61" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Adquiri um curso chamado Geniun Shop , em 2 de abril de 2026 , fiZ apenas as primeiras aulas, e agora quando resolvi voltar p... Perda de acesso ao curso Geniun Shop após pagamento, sem retorno do suporte.</t>
+        </is>
+      </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tomei-editado-pelo-reclame-aqui_PCEkQCMzbA-5dwgy/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perda-de-acesso-ao-curso-geniun-shop-apos-pagamento-sem-retorno-do-suporte_a6tTJhax8GBOg4xh/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>no qual n</t>
+          <t>onde dizia que tinha v</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>no qual n</t>
+          <t>onde dizia que tinha v</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3755,7 +3771,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3769,32 +3785,32 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um produto no qual não corresponde a minha expectativa , então solicito o estorno do meu valor. Email: ****... Solicitação de estorno por produto não correspondente à expectativa</t>
+          <t>Comprei um produto onde dizia que tinha vários fornecedores de roupas no Brasil..mas não tinha o que eu eu queria .por isso q... Reclamação sobre produto com fornecedores de roupas limitados e solicitação de reembolso.</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-por-produto-nao-correspondente-a-expectativa_jZ-08RI4TwV-ynQ4/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-com-fornecedores-de-roupas-limitados-e-solicitacao-de-reembolso_H7FXu4ussEtUSJQC/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>um grupo vip no dia 20</t>
+          <t>com defeito e solicita</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>um grupo vip no dia 20</t>
+          <t>com defeito e solicita</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3809,7 +3825,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3823,47 +3839,47 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Olá, fiz uma compra de um grupo vip no dia 20/08 e dia 23/08 tentei fazer o cancelamento, mas o vendedor ***** - operações nã... Tentativa de cancelamento de grupo VIP e impossibilidade de contato com o vendedor</t>
+          <t>Fiz uma compra no Blackxitoficial (meu Gmail é *****). Meu CPF: *****, no valor de 31 reais. O Painel chegou, mas não funcion... Produto com defeito e solicitação de reembolso</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tentativa-de-cancelamento-de-grupo-vip-e-impossibilidade-de-contato-com-o-vendedor_SkOpE6e5RhZv8KIr/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-com-defeito-e-solicitacao-de-reembolso_GgMl5lRE9VZtuHoJ/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>turminha alfakids</t>
+          <t>na plataforma e n</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Turminha Alfakids</t>
+          <t>na plataforma e n</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Educação infantil / Materiais didáticos</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3877,32 +3893,32 @@
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra da turminha Alfakids de 2750 atividades e não recebi,o email que aparece como suporte não responde Compra não recebida e falta de resposta do suporte</t>
+          <t>comprei um produto na plataforma e não gostei, quero meu reembolso, foi comprado no pix:Código da compra: ***** Cliente deseja reembolso de aquecedor comprado via Pix por não ter gostado do produto.</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-nao-recebida-e-falta-de-resposta-do-suporte_yWkDvnrLPMHo7aTz/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cliente-deseja-reembolso-de-aquecedor-comprado-via-pix-por-nao-ter-gostado-do-produto_2qo_Zk1Eh3qTNpQy/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>um curso</t>
+          <t>nessa plataforma</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>um curso</t>
+          <t>nessa plataforma</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3912,12 +3928,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3931,43 +3947,47 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K65" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Verifiquei a compra de um produto nessa plataforma, solicitei o reembolso junto a produtora do produto e não consegui retorno... Reembolso não resolvido pela plataforma após contato com produtora e cancelamento de cartão.</t>
+        </is>
+      </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-de-curso-nao-realizado-apos-solicitacao-dentro-do-prazo_ktvLpzB4DAj5K-_J/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-nao-resolvido-pela-plataforma-apos-contato-com-produtora-e-cancelamento-de-cartao_P1PpJ-yUSNmPIVUp/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>directspeed</t>
+          <t>em um site na internet e ao abrir o email</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Directspeed</t>
+          <t>em um site na internet e ao abrir o email</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de produtividade / Assinatura</t>
+          <t>Serviços financeiros / Pix</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3981,28 +4001,32 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K66" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Realizei uma compra de um produto em um site na internet e ao abrir o email enviado me cobraram outra taxa que não estava com... Cobrança de taxa adicional não combinada e falta de acesso ao produto comprado.</t>
+        </is>
+      </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-da-ferramenta-directspeed-nao-respondida_G-frs9kFEKvabVpn/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-de-taxa-adicional-nao-combinada-e-falta-de-acesso-ao-produto-comprado__chfFQTX8pupMWB5/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>cortes do marques</t>
+          <t>tomei</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Cortes do Marques</t>
+          <t>Tomei</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4012,12 +4036,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -4031,32 +4055,28 @@
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Estou há quase 1 mês tentando cancelar a assinatura do produto Cortes do Marques, adquirido por meio da Cackto, mas até o mom... Cackto não realiza cancelamento de assinatura mesmo após várias solicitações</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cackto-nao-realiza-cancelamento-de-assinatura-mesmo-apos-varias-solicitacoes_WEDpJ2MDQNCpB9xD/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tomei-editado-pelo-reclame-aqui_PCEkQCMzbA-5dwgy/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>umgrama de karaoke e est</t>
+          <t>no qual n</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>um programa de karaoke e est</t>
+          <t>no qual n</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4066,12 +4086,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -4085,32 +4105,32 @@
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Fiz a compra de um programa de karaoke e está dando conteúdo não encontrado paguei via pix. Conteúdo não encontrado</t>
+          <t>Fiz uma compra de um produto no qual não corresponde a minha expectativa , então solicito o estorno do meu valor. Email: ****... Solicitação de estorno por produto não correspondente à expectativa</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/conteudo-nao-encontrado_eh2tS2q3T2WGSky_/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-por-produto-nao-correspondente-a-expectativa_jZ-08RI4TwV-ynQ4/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>uma m</t>
+          <t>um grupo vip no dia 20</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>uma m</t>
+          <t>um grupo vip no dia 20</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4120,7 +4140,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4139,37 +4159,37 @@
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de uma máscara coreana , fiz o pagamento no PIX e a empresa relatou que eu nao havia pago, eu ,logo a seguir ... Pagamento via PIX não reconhecido e falta de retorno da empresa após envio de comprovante.</t>
+          <t>Olá, fiz uma compra de um grupo vip no dia 20/08 e dia 23/08 tentei fazer o cancelamento, mas o vendedor ***** - operações nã... Tentativa de cancelamento de grupo VIP e impossibilidade de contato com o vendedor</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-reconhecido-e-falta-de-retorno-da-empresa-apos-envio-de-comprovante_C6tRKpYDqejq7Cvf/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tentativa-de-cancelamento-de-grupo-vip-e-impossibilidade-de-contato-com-o-vendedor_SkOpE6e5RhZv8KIr/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>curso online capsulas gourmet e c</t>
+          <t>turminha alfakids</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>curso online capsulas gourmet e c</t>
+          <t>Turminha Alfakids</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4179,7 +4199,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Educação infantil / Materiais didáticos</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4193,28 +4213,32 @@
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K70" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra da turminha Alfakids de 2750 atividades e não recebi,o email que aparece como suporte não responde Compra não recebida e falta de resposta do suporte</t>
+        </is>
+      </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/materiais-de-curso-online-de-capsulas-gourmet-e-capuccinos-nao-disponiveis_jlp3yz2MCVJGF1UT/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-nao-recebida-e-falta-de-resposta-do-suporte_yWkDvnrLPMHo7aTz/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>um curso no dia 01</t>
+          <t>um curso</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>um curso no dia 01</t>
+          <t>um curso</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4229,7 +4253,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -4243,33 +4267,33 @@
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue_RxHp4cyuljYU2Wtj/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-de-curso-nao-realizado-apos-solicitacao-dentro-do-prazo_ktvLpzB4DAj5K-_J/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>diferente do anunciado e a plataforma n</t>
+          <t>directspeed</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>diferente do anunciado e a plataforma n</t>
+          <t>Directspeed</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4279,7 +4303,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Ferramentas de produtividade / Assinatura</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4293,28 +4317,28 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/vendedor-entregou-produto-diferente-do-anunciado-e-a-plataforma-nao-resolve_vkGIXT8UU80pbQbc/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-da-ferramenta-directspeed-nao-respondida_G-frs9kFEKvabVpn/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>chegou faltando conte</t>
+          <t>cortes do marques</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>chegou faltando conte</t>
+          <t>Cortes do Marques</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4343,32 +4367,32 @@
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra por lá, produto chegou faltando conteúdo, entro em contato com eles e ZERO atendimento, preciso fazer o estorn... Produto com conteúdo faltante e falta de atendimento para estorno</t>
+          <t>Estou há quase 1 mês tentando cancelar a assinatura do produto Cortes do Marques, adquirido por meio da Cackto, mas até o mom... Cackto não realiza cancelamento de assinatura mesmo após várias solicitações</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-com-conteudo-faltante-e-falta-de-atendimento-para-estorno_S6A780k9_99Ofap-/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cackto-nao-realiza-cancelamento-de-assinatura-mesmo-apos-varias-solicitacoes_WEDpJ2MDQNCpB9xD/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>um curso na plataforma deles</t>
+          <t>umgrama de karaoke e est</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>um curso na plataforma deles</t>
+          <t>um programa de karaoke e est</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4397,28 +4421,32 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de um programa de karaoke e está dando conteúdo não encontrado paguei via pix. Conteúdo não encontrado</t>
+        </is>
+      </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-estorno-de-curso-online-com-ma-qualidade-e-falta-de-resposta_rDQ1eDeZL9eCjgqm/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/conteudo-nao-encontrado_eh2tS2q3T2WGSky_/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>auto live shop</t>
+          <t>uma m</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Auto Live Shop</t>
+          <t>uma m</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4433,7 +4461,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -4447,32 +4475,32 @@
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Realizei a compra do produto Auto Live Shop, porém, após utilizar o produto, constatei que ele não atendeu às minhas expectat... Solicitação de reembolso para produto Auto Live Shop não processada pela plataforma Cakto</t>
+          <t>Fiz uma compra de uma máscara coreana , fiz o pagamento no PIX e a empresa relatou que eu nao havia pago, eu ,logo a seguir ... Pagamento via PIX não reconhecido e falta de retorno da empresa após envio de comprovante.</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-para-produto-auto-live-shop-nao-processada-pela-plataforma-cakto_Zejb3D4JhCq2o48c/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-reconhecido-e-falta-de-retorno-da-empresa-apos-envio-de-comprovante_C6tRKpYDqejq7Cvf/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>pelo pouco que testei</t>
+          <t>curso online capsulas gourmet e c</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>pelo pouco que testei</t>
+          <t>curso online capsulas gourmet e c</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4487,7 +4515,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4498,39 +4526,31 @@
       <c r="G76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>R$ 197,99.</t>
-        </is>
-      </c>
+      <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>Comprei o Plano Starter mensal da Cloakby por R$ 197,99. O produto pelo pouco que testei é excelente. Porém, não atendeu as m... Reclamação Sobre Oferta da Cloakby: propaganda enganosa e péssimo atendimento ao solicitar reembolso</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-oferta-da-cloakby-propaganda-enganosa-e-pessimo-atendimento-ao-solicitar-reembolso_DS552Q4NU1VCy-bp/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/materiais-de-curso-online-de-capsulas-gourmet-e-capuccinos-nao-disponiveis_jlp3yz2MCVJGF1UT/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>uma assinatura do site copie</t>
+          <t>um curso no dia 01</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>uma assinatura do site copie.ai</t>
+          <t>um curso no dia 01</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4556,39 +4576,31 @@
       <c r="G77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>R$ 97,00,</t>
-        </is>
-      </c>
+      <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>Realizei a compra de uma assinatura do site copie.ai, no dia 30 de agosto de 2026, às 17h38min, no valor de R$97,00, no site ... Assinatura Copie.ai não liberada após compra e sem retorno do suporte.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/assinatura-nao-liberada-apos-compra-e-sem-retorno-do-suporte__RpqyPU88WZJtxd1/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue_RxHp4cyuljYU2Wtj/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>pois n</t>
+          <t>diferente do anunciado e a plataforma n</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>pois n</t>
+          <t>diferente do anunciado e a plataforma n</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4603,7 +4615,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4617,32 +4629,28 @@
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra mas não gostei do produto pois não atingiu minhas espectativas solicito o reembolso pois está no prazo de gara... Solicitação de reembolso por produto que não atendeu às expectativas dentro do prazo de garantia.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-que-nao-atendeu-as-expectativas-dentro-do-prazo-de-garantia_4ccUExOzKRUFA4MT/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/vendedor-entregou-produto-diferente-do-anunciado-e-a-plataforma-nao-resolve_vkGIXT8UU80pbQbc/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>dois cursos de idiomas</t>
+          <t>chegou faltando conte</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>dois cursos de idiomas</t>
+          <t>chegou faltando conte</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4657,7 +4665,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4671,32 +4679,32 @@
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de dois cursos de idiomas, no caso Espanhol. Paguei pelos dois cursos via pi, porém só tive acesso a um curso,... Acesso negado a curso de espanhol pago e dificuldade de contato com o suporte para reembolso.</t>
+          <t>Fiz uma compra por lá, produto chegou faltando conteúdo, entro em contato com eles e ZERO atendimento, preciso fazer o estorn... Produto com conteúdo faltante e falta de atendimento para estorno</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/acesso-negado-a-curso-de-espanhol-pago-e-dificuldade-de-contato-com-o-suporte-para-reembolso_9d9eJH4OMC_ApZLR/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-com-conteudo-faltante-e-falta-de-atendimento-para-estorno_S6A780k9_99Ofap-/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
+          <t>um curso na plataforma deles</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
+          <t>um curso na plataforma deles</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4711,7 +4719,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4725,32 +4733,28 @@
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>fiz uma compra de um site hoje e quero solicitar o cancelamento e direito a arrependimento dentro de 7 dias, fiz um pedido ma... Solicitação de cancelamento e estorno de 3 pedidos devido a arrependimento e insatisfação com o produto/site.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-3-pedidos-devido-a-arrependimento-e-insatisfacao-com-o-produtosite_KUDEd8s3eGajQ3-L/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-estorno-de-curso-online-com-ma-qualidade-e-falta-de-resposta_rDQ1eDeZL9eCjgqm/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>auto live shop</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
+          <t>Auto Live Shop</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4765,7 +4769,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4779,32 +4783,32 @@
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por... Reclamação sobre reembolso de mentoria não processado e falta de suporte</t>
+          <t>Realizei a compra do produto Auto Live Shop, porém, após utilizar o produto, constatei que ele não atendeu às minhas expectat... Solicitação de reembolso para produto Auto Live Shop não processada pela plataforma Cakto</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-para-produto-auto-live-shop-nao-processada-pela-plataforma-cakto_Zejb3D4JhCq2o48c/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>estrutura para gera</t>
+          <t>pelo pouco que testei</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>estrutura para gera</t>
+          <t>pelo pouco que testei</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4819,7 +4823,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4830,31 +4834,39 @@
       <c r="G82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 197,99.</t>
+        </is>
+      </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o Plano Starter mensal da Cloakby por R$ 197,99. O produto pelo pouco que testei é excelente. Porém, não atendeu as m... Reclamação Sobre Oferta da Cloakby: propaganda enganosa e péssimo atendimento ao solicitar reembolso</t>
+        </is>
+      </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-oferta-da-cloakby-propaganda-enganosa-e-pessimo-atendimento-ao-solicitar-reembolso_DS552Q4NU1VCy-bp/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>youclone no dia 28</t>
+          <t>uma assinatura do site copie</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Youclone no dia 28</t>
+          <t>uma assinatura do site copie.ai</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4880,35 +4892,39 @@
       <c r="G83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 97,00,</t>
+        </is>
+      </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Comprei o produto Youclone no dia 28/08, no pix.Quando fui entrar no curso, não abre a área de membros e não consig... Cliente não consegue acessar área de membros do curso Youclone e relata falta de suporte.</t>
+          <t>Realizei a compra de uma assinatura do site copie.ai, no dia 30 de agosto de 2026, às 17h38min, no valor de R$97,00, no site ... Assinatura Copie.ai não liberada após compra e sem retorno do suporte.</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/assinatura-nao-liberada-apos-compra-e-sem-retorno-do-suporte__RpqyPU88WZJtxd1/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>oduto</t>
+          <t>pois n</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>o produto</t>
+          <t>pois n</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4937,32 +4953,32 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Adquiri o produto &amp;quot;Combo Black&amp;quot; do Gustavo de Castro e recebi um e-mail de aprovação de compra sem acesso ao produt... Cliente não tem acesso ao produto &amp;#x27;Combo Black&amp;#x27; após aprovação de compra e não obtém resposta do suporte.</t>
+          <t>Fiz uma compra mas não gostei do produto pois não atingiu minhas espectativas solicito o reembolso pois está no prazo de gara... Solicitação de reembolso por produto que não atendeu às expectativas dentro do prazo de garantia.</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-tem-acesso-ao-produto-combo-black-apos-aprovacao-de-compra-e-nao-obtem-resposta-do-suporte_na5373f4sUAHpMsE/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-que-nao-atendeu-as-expectativas-dentro-do-prazo-de-garantia_4ccUExOzKRUFA4MT/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>um curso de ia nao gostei do curso e dent</t>
+          <t>dois cursos de idiomas</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>um curso de IA nao gostei do curso e dent</t>
+          <t>dois cursos de idiomas</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4991,32 +5007,32 @@
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>fiz uma compra de um curso de IA nao gostei do curso e dentro do prazo de 7 dias solicitei o reembolso pelo email que disponi... Estorno</t>
+          <t>Fiz uma compra de dois cursos de idiomas, no caso Espanhol. Paguei pelos dois cursos via pi, porém só tive acesso a um curso,... Acesso negado a curso de espanhol pago e dificuldade de contato com o suporte para reembolso.</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/estorno_hMRVrko0Dz8fVqsF/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/acesso-negado-a-curso-de-espanhol-pago-e-dificuldade-de-contato-com-o-suporte-para-reembolso_9d9eJH4OMC_ApZLR/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>cuja cobran</t>
+          <t>um site hoje e quero solicitar o cancelam</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>cuja cobran</t>
+          <t>um site hoje e quero solicitar o cancelam</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5045,28 +5061,32 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K86" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>fiz uma compra de um site hoje e quero solicitar o cancelamento e direito a arrependimento dentro de 7 dias, fiz um pedido ma... Solicitação de cancelamento e estorno de 3 pedidos devido a arrependimento e insatisfação com o produto/site.</t>
+        </is>
+      </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-mensal-nao-efetivada-pela-plataforma-cakto_rOS_H0sA8Ne2Yb4r/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-3-pedidos-devido-a-arrependimento-e-insatisfacao-com-o-produtosite_KUDEd8s3eGajQ3-L/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>apostila de psicologia 2025</t>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Apostila de Psicologia 2025</t>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5081,7 +5101,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Educação / Concursos e certificações</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -5095,32 +5115,32 @@
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico.Já entrei em contato por e-mail,... Apostila de Psicologia 2025 não abre e cliente não obtém retorno sobre compra online.</t>
+          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por... Reclamação sobre reembolso de mentoria não processado e falta de suporte</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>estrutura para gera</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Fábrica de Low Ticket</t>
+          <t>estrutura para gera</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5135,7 +5155,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Educação / Marketing digital e low ticket</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5149,32 +5169,28 @@
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>Olá,Solicito o reembolso da compra da Fábrica de Low Ticket.Adquiri o curso com base na promessa apresent... Reembolso solicitado por propaganda enganosa sobre suporte individual no curso Fábrica de Low Ticket</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>incompleto dentro da garantia</t>
+          <t>youclone no dia 28</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>incompleto dentro da garantia</t>
+          <t>Youclone no dia 28</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5203,32 +5219,32 @@
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Gostaria do reembolso dos seguintes produtos que comprei, está dentro do prazo de garantia de 7 dias.Email de Compra: **... Solicitação de reembolso por produto incompleto dentro da garantia</t>
+          <t>Comprei o produto Youclone no dia 28/08, no pix.Quando fui entrar no curso, não abre a área de membros e não consig... Cliente não consegue acessar área de membros do curso Youclone e relata falta de suporte.</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-incompleto-dentro-da-garantia_DBUjl2QuaruN_QYD/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>mas n</t>
+          <t>oduto</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>mas n</t>
+          <t>o produto</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5243,7 +5259,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -5257,28 +5273,32 @@
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K90" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Adquiri o produto &amp;quot;Combo Black&amp;quot; do Gustavo de Castro e recebi um e-mail de aprovação de compra sem acesso ao produt... Cliente não tem acesso ao produto &amp;#x27;Combo Black&amp;#x27; após aprovação de compra e não obtém resposta do suporte.</t>
+        </is>
+      </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-me-respondem_ddIIs2OseJhlXI2v/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-tem-acesso-ao-produto-combo-black-apos-aprovacao-de-compra-e-nao-obtem-resposta-do-suporte_na5373f4sUAHpMsE/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>de streaming n</t>
+          <t>um curso de ia nao gostei do curso e dent</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>de streaming n</t>
+          <t>um curso de IA nao gostei do curso e dent</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5293,7 +5313,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Streaming e entretenimento</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -5307,28 +5327,32 @@
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K91" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>fiz uma compra de um curso de IA nao gostei do curso e dentro do prazo de 7 dias solicitei o reembolso pelo email que disponi... Estorno</t>
+        </is>
+      </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-desacordo-comercial-por-servico-de-streaming-nao-recebido-e-falta-de-contato-do-vendedor_xHL_Rnpj7hKZ3vjT/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/estorno_hMRVrko0Dz8fVqsF/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>que eu comprei na plataforma cakto ..o pr</t>
+          <t>cuja cobran</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>que eu comprei na plataforma Cakto ..o pr</t>
+          <t>cuja cobran</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5343,7 +5367,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -5357,32 +5381,28 @@
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>Estou tentando cancelar um produto que eu comprei na plataforma Cakto ..o produto que eu comprei foi calcula chef app não es... Não consigo cancelar o produto Calcula Chef App e não recebo retorno da Cakto.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-cancelar-o-produto-calcula-chef-app-e-nao-recebo-retorno-da-cakto_mwF3xbe9PnLeIpH4/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-mensal-nao-efetivada-pela-plataforma-cakto_rOS_H0sA8Ne2Yb4r/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>um curso na sexta feira e n</t>
+          <t>apostila de psicologia 2025</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>um curso na sexta feira e n</t>
+          <t>Apostila de Psicologia 2025</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5397,7 +5417,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Educação / Concursos e certificações</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -5411,32 +5431,32 @@
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>fiz uma compra de um curso na sexta feira e não recebi, também pelo chat de suporte não tenho retorno. Quero o reembolso, poi... Curso não recebido e falta de retorno do suporte, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
+          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico.Já entrei em contato por e-mail,... Apostila de Psicologia 2025 não abre e cliente não obtém retorno sobre compra online.</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-nao-recebido-e-falta-de-retorno-do-suporte-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_KD9yrBbG0QhwORjs/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>uma planilha e n</t>
+          <t>fábrica de low ticket</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>uma planilha e n</t>
+          <t>Fábrica de Low Ticket</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5451,7 +5471,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Educação / Marketing digital e low ticket</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5465,28 +5485,32 @@
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K94" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Olá,Solicito o reembolso da compra da Fábrica de Low Ticket.Adquiri o curso com base na promessa apresent... Reembolso solicitado por propaganda enganosa sobre suporte individual no curso Fábrica de Low Ticket</t>
+        </is>
+      </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-suporte_245GAIgR4SjdP8m1/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>um aplicativo</t>
+          <t>incompleto dentro da garantia</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>um aplicativo</t>
+          <t>incompleto dentro da garantia</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5501,7 +5525,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -5515,32 +5539,32 @@
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo ... Reclamação sobre aplicativo não funcional e falta de resposta do suporte para reembolso.</t>
+          <t>Gostaria do reembolso dos seguintes produtos que comprei, está dentro do prazo de garantia de 7 dias.Email de Compra: **... Solicitação de reembolso por produto incompleto dentro da garantia</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-incompleto-dentro-da-garantia_DBUjl2QuaruN_QYD/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>material de fonoaudiologia e n</t>
+          <t>mas n</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>material de fonoaudiologia e n</t>
+          <t>mas n</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5555,7 +5579,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -5569,32 +5593,28 @@
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>Fiz uma compra de material de fonoaudiologia e não no momento de baixar o material era mal feito, a fonoaudióloga sequer exis... Material de fonoaudiologia de má qualidade e recusa de reembolso pela Cacto.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/material-de-fonoaudiologia-de-ma-qualidade-e-recusa-de-reembolso-pela-cacto_zjP5uaGFy2s7z7ZP/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-me-respondem_ddIIs2OseJhlXI2v/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>pela cakto e logo realizei o pedido de re</t>
+          <t>de streaming n</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>pela cakto e logo realizei o pedido de re</t>
+          <t>de streaming n</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5609,7 +5629,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Streaming e entretenimento</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -5623,32 +5643,28 @@
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>Fiz a compra de um produto pela cakto e logo realizei o pedido de reembolso, porem sem sucesso, pois a plataforma dar erro: &amp;... Erro ao tentar solicitar reembolso de produto na Cakto</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/erro-ao-tentar-solicitar-reembolso-de-produto-na-cakto_ZhxbaEfvn9crLs7c/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-desacordo-comercial-por-servico-de-streaming-nao-recebido-e-falta-de-contato-do-vendedor_xHL_Rnpj7hKZ3vjT/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>programa n</t>
+          <t>que eu comprei na plataforma cakto ..o pr</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>programa n</t>
+          <t>que eu comprei na plataforma Cakto ..o pr</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5663,7 +5679,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5677,32 +5693,32 @@
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra online e o programa não funcionou durante dois dias comecei a enviar para o produtor e para empresa Catho o pe... Reembolso não efetuado e falta de resposta da Catho e do produtor após compra de programa não funcional.</t>
+          <t>Estou tentando cancelar um produto que eu comprei na plataforma Cakto ..o produto que eu comprei foi calcula chef app não es... Não consigo cancelar o produto Calcula Chef App e não recebo retorno da Cakto.</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-nao-efetuado-e-falta-de-resposta-da-catho-e-do-produtor-apos-compra-de-programa-nao-funcional_2BTWhdCr7obnyw-X/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-cancelar-o-produto-calcula-chef-app-e-nao-recebo-retorno-da-cakto_mwF3xbe9PnLeIpH4/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria</t>
+          <t>um curso na sexta feira e n</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>uma mentoria</t>
+          <t>um curso na sexta feira e n</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5717,7 +5733,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Educação e consultoria</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -5731,28 +5747,32 @@
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K99" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>fiz uma compra de um curso na sexta feira e não recebi, também pelo chat de suporte não tenho retorno. Quero o reembolso, poi... Curso não recebido e falta de retorno do suporte, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
+        </is>
+      </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-de-mentoria-nao-encontrada-e-falta-de-suporte-da-cakto-e-do-vendedor_Bt44ofl5iW09TC9d/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-nao-recebido-e-falta-de-retorno-do-suporte-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_KD9yrBbG0QhwORjs/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>com defeito</t>
+          <t>uma planilha e n</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>com defeito</t>
+          <t>uma planilha e n</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5781,37 +5801,33 @@
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>fiz a comprar de um produto , o produto não rodou no meu pc pedi o reembolso e mandaram falar com o produtor , mandei mensage... Reembolso negado e contato com o produtor indisponível após compra de produto com defeito</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-negado-e-contato-com-o-produtor-indisponivel-apos-compra-de-produto-com-defeito_JT9yPhOIhMRefinl/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-suporte_245GAIgR4SjdP8m1/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>frequência da vinci</t>
+          <t>um aplicativo</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Frequência da Vinci</t>
+          <t>um aplicativo</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -5821,7 +5837,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Saúde / Tratamentos alternativos</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -5835,32 +5851,32 @@
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra por impulso,de um programa de cura do zumbido no ouvido e gostaria de cancelar e ter o extorno do valor pago p... Solicitação de cancelamento e estorno de programa de cura de zumbido</t>
+          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo ... Reclamação sobre aplicativo não funcional e falta de resposta do suporte para reembolso.</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-programa-de-cura-de-zumbido_T3cY3B6mIP4BEv_Y/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>da vav</t>
+          <t>material de fonoaudiologia e n</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>da Vav</t>
+          <t>material de fonoaudiologia e n</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5875,7 +5891,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -5889,32 +5905,32 @@
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>**Produto não entregue e criador não responde solicito reembolso**Realizei a compra de um produto da Vavá Aca... Produto não entregue e criador não responde, solicito reembolso</t>
+          <t>Fiz uma compra de material de fonoaudiologia e não no momento de baixar o material era mal feito, a fonoaudióloga sequer exis... Material de fonoaudiologia de má qualidade e recusa de reembolso pela Cacto.</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue-e-criador-nao-responde-solicito-reembolso_605Q8ntQ-aQlegi3/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/material-de-fonoaudiologia-de-ma-qualidade-e-recusa-de-reembolso-pela-cacto_zjP5uaGFy2s7z7ZP/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>digitalcessada pela cakto</t>
+          <t>pela cakto e logo realizei o pedido de re</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>digital processada pela Cakto</t>
+          <t>pela cakto e logo realizei o pedido de re</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5943,33 +5959,37 @@
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K103" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de um produto pela cakto e logo realizei o pedido de reembolso, porem sem sucesso, pois a plataforma dar erro: &amp;... Erro ao tentar solicitar reembolso de produto na Cakto</t>
+        </is>
+      </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-em-compra-de-produto-digital-processada-pela-cakto-com-editado-pelo-reclame-aqui-e-nao-entrega_HJtQooCkVBEfTtMB/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/erro-ao-tentar-solicitar-reembolso-de-produto-na-cakto_ZhxbaEfvn9crLs7c/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>converza.io</t>
+          <t>programa n</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Converza.io</t>
+          <t>programa n</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -5979,7 +5999,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Chatbots / Automação de mensagens</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5993,28 +6013,32 @@
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K104" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra online e o programa não funcionou durante dois dias comecei a enviar para o produtor e para empresa Catho o pe... Reembolso não efetuado e falta de resposta da Catho e do produtor após compra de programa não funcional.</t>
+        </is>
+      </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/exijo-reembolso-servico-nao-funciona-e-suporte-nao-responde_OPi-rimJXtkjo2yB/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-nao-efetuado-e-falta-de-resposta-da-catho-e-do-produtor-apos-compra-de-programa-nao-funcional_2BTWhdCr7obnyw-X/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>comprad... pagamento via pix n</t>
+          <t>uma mentoria</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>comprad... Pagamento via PIX n</t>
+          <t>uma mentoria</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6043,32 +6067,28 @@
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>Fiz o pgto via PIX para a empresa seguro-vidasaudavel.site através da Cakto Pay, porém não me foi fornecido o produto comprad... Pagamento via PIX não resultou na entrega do produto, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-resultou-na-entrega-do-produto-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_cbUdm8Fq5-5oanwH/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-de-mentoria-nao-encontrada-e-falta-de-suporte-da-cakto-e-do-vendedor_Bt44ofl5iW09TC9d/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>curso online</t>
+          <t>com defeito</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>curso online</t>
+          <t>com defeito</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6083,7 +6103,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Crescimento em redes sociais</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -6097,37 +6117,37 @@
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Fiz uma compra de curso online, pgn no Instagran que se chama Amigurumi Brasil, pgn com mais de 1.5 k de seguidores, e até ho... Curso online não entregue após pagamento, com falha na comunicação e solicitação de estorno.</t>
+          <t>fiz a comprar de um produto , o produto não rodou no meu pc pedi o reembolso e mandaram falar com o produtor , mandei mensage... Reembolso negado e contato com o produtor indisponível após compra de produto com defeito</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-online-nao-entregue-apos-pagamento-com-falha-na-comunicacao-e-solicitacao-de-estorno_-bekag5hY78F-1mM/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-negado-e-contato-com-o-produtor-indisponivel-apos-compra-de-produto-com-defeito_JT9yPhOIhMRefinl/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>mas at</t>
+          <t>frequência da vinci</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>mas at</t>
+          <t>Frequência da Vinci</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6137,7 +6157,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Infoprodutos - suporte e reembolso</t>
+          <t>Saúde / Tratamentos alternativos</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -6151,25 +6171,341 @@
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
+          <t>Fiz uma compra por impulso,de um programa de cura do zumbido no ouvido e gostaria de cancelar e ter o extorno do valor pago p... Solicitação de cancelamento e estorno de programa de cura de zumbido</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-programa-de-cura-de-zumbido_T3cY3B6mIP4BEv_Y/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>da vav</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>da Vav</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>**Produto não entregue e criador não responde solicito reembolso**Realizei a compra de um produto da Vavá Aca... Produto não entregue e criador não responde, solicito reembolso</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue-e-criador-nao-responde-solicito-reembolso_605Q8ntQ-aQlegi3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>digitalcessada pela cakto</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>digital processada pela Cakto</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-em-compra-de-produto-digital-processada-pela-cakto-com-editado-pelo-reclame-aqui-e-nao-entrega_HJtQooCkVBEfTtMB/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>converza.io</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Converza.io</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Chatbots / Automação de mensagens</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/exijo-reembolso-servico-nao-funciona-e-suporte-nao-responde_OPi-rimJXtkjo2yB/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>comprad... pagamento via pix n</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>comprad... Pagamento via PIX n</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Fiz o pgto via PIX para a empresa seguro-vidasaudavel.site através da Cakto Pay, porém não me foi fornecido o produto comprad... Pagamento via PIX não resultou na entrega do produto, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-resultou-na-entrega-do-produto-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_cbUdm8Fq5-5oanwH/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>curso online</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>curso online</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Crescimento em redes sociais</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de curso online, pgn no Instagran que se chama Amigurumi Brasil, pgn com mais de 1.5 k de seguidores, e até ho... Curso online não entregue após pagamento, com falha na comunicação e solicitação de estorno.</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-online-nao-entregue-apos-pagamento-com-falha-na-comunicacao-e-solicitacao-de-estorno_-bekag5hY78F-1mM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>mas at</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>mas at</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
           <t>Fiz uma compra na loja e quero reembolsar meu produto mas até agora não fui atendido Reembolso</t>
         </is>
       </c>
-      <c r="L107" s="2" t="inlineStr">
+      <c r="L113" s="2" t="inlineStr">
         <is>
           <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso_Ou6F1k9zy_0W3ATN/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L107"/>
+  <autoFilter ref="A1:L113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6236,13 +6572,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -6251,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -6286,13 +6622,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
@@ -6301,7 +6637,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -6357,7 +6693,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Crescimento em redes sociais</t>
+          <t>Streaming e entretenimento</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -6382,7 +6718,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Serviços financeiros / Pix</t>
+          <t>Crescimento em redes sociais</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -6407,17 +6743,17 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Ferramentas / Aplicativos</t>
+          <t>Serviços financeiros / Pix</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0</v>
@@ -6426,13 +6762,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria / Mentoria</t>
+          <t>Ferramentas / Aplicativos</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -6457,7 +6793,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Educação / Idiomas</t>
+          <t>Educação e consultoria / Mentoria</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -6482,17 +6818,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Comunidades / Mentoria de negócios</t>
+          <t>Educação / Idiomas</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
@@ -6507,17 +6843,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Marketing / Comunidades de negócios</t>
+          <t>Comunidades / Mentoria de negócios</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
@@ -6532,7 +6868,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Arte personalizada / IA generativa</t>
+          <t>Marketing / Comunidades de negócios</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -6557,7 +6893,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria / Cursos online</t>
+          <t>Arte personalizada / IA generativa</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -6582,17 +6918,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+          <t>Educação e consultoria / Cursos online</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
@@ -6607,7 +6943,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Ferramentas de espionagem / WhatsApp</t>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -6632,17 +6968,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Educação infantil / Materiais didáticos</t>
+          <t>Ferramentas de espionagem / WhatsApp</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
@@ -6657,7 +6993,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Ferramentas de produtividade / Assinatura</t>
+          <t>Educação infantil / Materiais didáticos</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -6682,17 +7018,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Educação / Concursos e certificações</t>
+          <t>Ferramentas de produtividade / Assinatura</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
@@ -6707,7 +7043,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Educação / Marketing digital e low ticket</t>
+          <t>Educação / Concursos e certificações</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
@@ -6732,7 +7068,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Streaming e entretenimento</t>
+          <t>Educação / Marketing digital e low ticket</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
@@ -6815,7 +7151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -6848,1886 +7184,1676 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>adquirido teria condi</t>
+          <t>aparece na perfect pay mas o mesmo n</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>aparece na perfect pay mas o mesmo n</t>
+          <t>aplicativo</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>aplicativo</t>
+          <t>aplicativo viewerspy com tr</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>aplicativo n</t>
+          <t>apostila de psicologia 2025</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>aplicativo viewerspy com tr</t>
+          <t>auks bot</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>apostila de psicologia 2025</t>
+          <t>auto live shop</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>apostila de psicologia025</t>
+          <t>chamado f</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>aristocracy negócios digitais</t>
+          <t>chamado protocolo black digital e comprei</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>auks bot</t>
+          <t>chegou faltando conte</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>auto live shop</t>
+          <t>com defeito</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>chamado f</t>
+          <t>com defeito e solicita</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>chamado protocolo black digital e comprei</t>
+          <t>comprad... pagamento via pix n</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>chegou faltando conte</t>
+          <t>comunidade knights club</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>cloakeuai</t>
+          <t>comunidade mvz no dia 27</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>com defeito</t>
+          <t>comunidade vsa</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>com defeito e solicita</t>
+          <t>converza.io</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>comprad... pagamento via pix n</t>
+          <t>cortes do marques</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>comunidade knights club</t>
+          <t>cuja cobran</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>comunidade mvz no dia 27</t>
+          <t>curso de mandarim</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>comunidade vsa</t>
+          <t>curso de yoga n</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>continua ativo</t>
+          <t>curso online</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>converza.io</t>
+          <t>curso online capsulas gourmet e c</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>cortes do marques</t>
+          <t>códigos lucrativos</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>cuja cobran</t>
+          <t>da vav</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>curso de mandarim</t>
+          <t>de baixa qualidade</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>curso de yoga n</t>
+          <t>de postagem autom</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>curso online</t>
+          <t>de streaming n</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>curso online capsulas gourmet e c</t>
+          <t>diferente do anunciado e a plataforma n</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>códigos lucrativos</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>da vav</t>
+          <t>digital ap</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>de baixa qualidade</t>
+          <t>digital apexshop vital</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>de postagem autom</t>
+          <t>digital n</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>de seguran</t>
+          <t>digitalcessada pela cakto</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>de streaming n</t>
+          <t>directspeed</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>diferente do anunciado e a plataforma n</t>
+          <t>dois aplicativo e n</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>digital</t>
+          <t>dois cursos de idiomas</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>digital n</t>
+          <t>e n</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>digitalcessada pela cakto</t>
+          <t>e solicita</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>directspeed</t>
+          <t>em um site na internet e ao abrir o email</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>dois aplicativo e n</t>
+          <t>espia f</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>dois cursos de idiomas</t>
+          <t>estrutura para gera</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>e a plataforma deveria no m</t>
+          <t>fica saindo e entrando sozinho</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>e conseguiu acess</t>
+          <t>frequência da vinci</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>e ele nao chegou quero meu dinheiro de volta ra ad</t>
+          <t>fábrica de low ticket</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>e n</t>
+          <t>grupo vip</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>e solicita</t>
+          <t>ia academy</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>em um site na internet e ao abrir o email</t>
+          <t>incompleto dentro da garantia</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>espia f</t>
+          <t>incompleto dentro do prazo de 7 dias. n</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>estrutura para gera</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>fica saindo e entrando sozinho</t>
+          <t>low ticket do zero 2.0 no dia 30</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>frequência da vinci</t>
+          <t>mas at</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>fábrica de low ticket</t>
+          <t>mas n</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>grupo vip</t>
+          <t>material de fonoaudiologia e n</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>ia academy</t>
+          <t>mentoria nova profissão</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>incompleto dentro da garantia</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>na plataforma e n</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>interactive live</t>
+          <t>na ultima quarta feira</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero</t>
+          <t>nessa plataforma</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>low ticket do zero 2.0 no dia 30</t>
+          <t>no ... reembolso dentro do prazo</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>manuscrito dos milagres</t>
+          <t>no dia</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>mas at</t>
+          <t>no qual n</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>mas n</t>
+          <t>no valor de 97 reais que nao gostei pedi</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>material de fonoaudiologia e n</t>
+          <t>oduto</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>mentoria nova profissão</t>
+          <t>onde dizia que tinha v</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>método atlas</t>
+          <t>online</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>na plataforma e n</t>
+          <t>para poder solicitar o cancelamento</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>na ultima quarta feira</t>
+          <t>pela cakto e logo realizei o pedido de re</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>nessa plataforma</t>
+          <t>pelo pouco que testei</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>no ... reembolso dentro do prazo</t>
+          <t>perfect academy</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>no qual n</t>
+          <t>plataforma home office</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>no valor de 97 reais que nao gostei pedi</t>
+          <t>plataforma tikspy pelo valor de r</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>não conseguiu confirmar a distribuidora</t>
+          <t>pois n</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>oduto</t>
+          <t>produto malu</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>on line rj comercio varejista de acessorios ltda</t>
+          <t>programa n</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>onde dizia que tinha v</t>
+          <t>que era pelo gmail mandei a mensagem expl</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>que eu comprei na plataforma cakto ..o pr</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>pack canva</t>
+          <t>quemetia trazer minha conta do free f</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>pela cakto e logo realizei o pedido de re</t>
+          <t>receb... propaganda enganosa</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>pelo pouco que testei</t>
+          <t>retrato da sua alma gêmea</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>pelo qual paguei n</t>
+          <t>servi</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>perfect academy</t>
+          <t>simplesmente n</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>plataforma home office</t>
+          <t>spygram</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>plataforma tikspy pelo valor de r</t>
+          <t>stalkeia</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>pois n</t>
+          <t>tikedit pela perfectpay</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>produto malu</t>
+          <t>tomei</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>programa n</t>
+          <t>tudo dentro do prazo tudo certinho e ate</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>que era pelo gmail mandei a mensagem expl</t>
+          <t>turminha alfakids</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>que eu comprei na plataforma cakto ..o pr</t>
+          <t>um aplicativo</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>quemetia trazer minha conta do free f</t>
+          <t>um aplicativo de monitoramento pelo an</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>ra ads previous slide next slide compartilhe resp</t>
+          <t>um curso</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>receb... propaganda enganosa</t>
+          <t>um curso chamado geniun shop</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>retrato da sua alma gêmea</t>
+          <t>um curso de arais amador paguei e n</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>servi</t>
+          <t>um curso de ia nao gostei do curso e dent</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>simplesmente n</t>
+          <t>um curso na plataforma deles</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>spygram</t>
+          <t>um curso na sexta feira e n</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>stalkeia</t>
+          <t>um curso no dia 01</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>tikedit pela perfectpay</t>
+          <t>um grupo vip no dia 20</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>tomei</t>
+          <t>um painel e n</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>tudo dentro do prazo tudo certinho e ate</t>
+          <t>um site hoje e quero solicitar o cancelam</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>turminha alfakids</t>
+          <t>um usu</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>um aplicativo</t>
+          <t>um vendedor que usa os servi</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>um aplicativo de monitoramento pelo an</t>
+          <t>uma assinatura do site copie</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>um curso</t>
+          <t>uma ferramenta de automa</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>um curso chamado geniun shop</t>
+          <t>uma m</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>um curso de arais amador paguei e n</t>
+          <t>uma mentoria</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>um curso de ia nao gostei do curso e dent</t>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>uma planilha e n</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>um curso na plataforma deles</t>
+          <t>umgrama de karaoke e est</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>um curso na sexta feira e n</t>
+          <t>vendido pela appluna.net</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>um curso no dia 01</t>
+          <t>youclone no dia 28</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>um grupo vip no dia 20</t>
+          <t>zap radar</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>um painel e n</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>um site hoje e quero solicitar o cancelam</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>um vendedor que usa os servi</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>uma assinatura do site copie</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>uma ferramenta de automa</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>uma m</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>uma mentoria</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>uma mentoria no dia 26 onde o reembolso e</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>uma planilha e n</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>umgrama de karaoke e est</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>validação cadastral: em análise</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>vendido pela appluna.net</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>youclone no dia 28</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>zap radar</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -7308,7 +7308,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -7323,7 +7323,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -7443,7 +7443,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -7623,7 +7623,7 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -8298,7 +8298,7 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -8343,7 +8343,7 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -8598,7 +8598,7 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -8658,7 +8658,7 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -8823,7 +8823,7 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -7308,7 +7308,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -7323,7 +7323,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -7443,7 +7443,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -7623,7 +7623,7 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -8298,7 +8298,7 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -8343,7 +8343,7 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -8598,7 +8598,7 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -8658,7 +8658,7 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -8823,7 +8823,7 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Radar/radar-low-ticket.xlsx
+++ b/Radar/radar-low-ticket.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Achados'!$A$1:$L$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -548,15 +548,15 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>fria</t>
+          <t>morna</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>R$ 47</t>
+          <t>R$ 87,00</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -565,33 +565,33 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas propaganda enganosa do Stalkeia.app e solicitação de reembolso do valor pago.  Resolvido  PerfectPay  Goiânia - GO  31/08/2026 às 04:47  ID: 257782105  realizei o pagamento direto no aplicativo, que prometia te entregar</t>
+          <t>Realizei a compra do produto &amp;#39;Stalkea AI&amp;#39; intermediado pela plataforma Perfect Pay. O produto trata-se de uma [Editad... Exijo estorno de compra de produto [Editado pelo Reclame Aqui] intermediado pela Perfect Pay</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-enganosa-do-e-solicitacao-de-reembolso-do-valor-pago_yID1cmkfVopy5OrZ/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/exijo-estorno-de-compra-de-produto-editado-pelo-reclame-aqui-intermediado-pela-perfect-pay_dDCHm8bcfbJi5cGU/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>método atlas</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>um curso e</t>
+          <t>Método Atlas</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -610,37 +610,37 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas [Editado pelo Reclame Aqui]  Resolvido  PerfectPay  Osasco - SP  31/08/2026 às 00:24  ID: 257779321  Fiz compra de um curso e é [Editado pelo Reclame Aqui]. Quero [Editado pelo Reclame Aqui] código *****  Aguardo.  RA Ad</t>
+          <t>Fiz uma compra desse tal método atlas, não cumpriu com prometido ,tento falar com suporte wattsap, e-mail e simplesmente desa... Clonado cartão</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/editado-pelo-reclame-aqui_UeZdzzFsRKKhakiR/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/clonado-cartao_bkNp4YTe6nDKqL90/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ra ads previous slide next slide compartilhe resp</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Previous slide Next slide Compartilhe Resp</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -664,42 +664,42 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas [Editado pelo Reclame Aqui]  Resolvido  PerfectPay  Mogi das Cruzes - SP  30/08/2026 às 23:05  ID: 257777077  Sofia um [Editado pelo Reclame Aqui], paguei e não recebi o produto  RA Ads Previous slide Next slide  Compart</t>
+          <t>Quero solicitar um reembolso, pois eu comprei um produto digital, já solicitei o suporte do Produtor, mas não me deram respos... Solicitação de reembolso por produto digital não respondido pelo produtor e suspeita de [Editado pelo Reclame Aqui].</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/editado-pelo-reclame-aqui_SUXSgNqlxlTtM8rF/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-reembolso-por-produto-digital-nao-respondido-pelo-produtor-e-suspeita-de-editado-pelo-reclame-aqui_4rad2Noh-3EVPiq-/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>e ele nao chegou quero meu dinheiro de volta ra ad</t>
+          <t>produto malu</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>e ele nao chegou quero meu dinheiro de volta RA Ad</t>
+          <t>Produto Malu</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>angulo</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Ferramentas / Aplicativos</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -718,52 +718,52 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Propaganda inganosa  Respondida  PerfectPay  Caxias do Sul - RS  30/08/2026 às 15:07  ID: 257755023     Fiz a compra de um produto e ele nao chegou quero meu dinheiro de volta  RA Ads Previous slide Next slide  Compartil</t>
+          <t>Título: Produto Malu não correspondeu às minhas expectativas e exige novo pagamento para ativaçãoRealizei a compra ... Produto Malu exige novo pagamento para ativação, solicito cancelamento e reembolso.</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/perfectpay/propaganda-inganosa_WXGZ3QLZ1OhfoBjb/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-malu-exige-novo-pagamento-para-ativacao-solicito-cancelamento-e-reembolso_EGQhjKMbfuFFizV7/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>converza.io</t>
+          <t>plataforma tikspy pelo valor de r</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Converza.io</t>
+          <t>plataforma TikSpy pelo valor de R</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Espionagem e rastreamento</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -774,7 +774,11 @@
       <c r="G6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>R$ 360,24</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2026-09-04</t>
@@ -785,24 +789,24 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Exijo reembolso serviço não funciona e suporte não responde  Respondida  CAKTO PAY  São Paulo - SP  31/08/2026 às 03:25  ID: 257781633  Assinei um plano da Converza.io, porém não consigo sequer criar um dispositivo para</t>
+          <t>No dia 24/08/2026 adquiri a plataforma TikSpy pelo valor de R$ 360,24Após acessar a plataforma, concluí que ela não... Dificuldade em cancelar compra e solicitar reembolso de plataforma digital</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/exijo-reembolso-servico-nao-funciona-e-suporte-nao-responde_OPi-rimJXtkjo2yB/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/dificuldade-em-cancelar-compra-e-solicitar-reembolso-de-plataforma-digital_MNsF1CWfu9nJFQaI/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>comunidade vsa</t>
+          <t>mentoria nova profissão</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>COMUNIDADE VSA</t>
+          <t>Mentoria Nova Profissão</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -817,7 +821,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Espionagem e rastreamento</t>
+          <t>Educação e consultoria / Mentoria</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -826,13 +830,9 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>R$ 248,89.</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2026-09-04</t>
@@ -841,41 +841,37 @@
       <c r="J7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Solicitação de reembolso de compra com erro de saldo na conta do vendedor  Respondida  CAKTO PAY  Junqueiro - AL  31/08/2026 às 02:34  ID: 257781211  Olá,  Solicito o reembolso da compra da COMUNIDADE VSA, realizada em 2</t>
-        </is>
-      </c>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-reembolso-de-compra-com-erro-de-saldo-na-conta-do-vendedor_e5d-tH3gUGahNktM/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-mentoria-nova-profissao-propaganda-enganosa-e-falha-na-intermediacao-de-reembolso-pela-cakto-pay_WVFYGdZmjsyF9dv0/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>retrato da sua alma gêmea</t>
+          <t>auks bot</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Retrato da Sua Alma Gêmea</t>
+          <t>Auks Bot</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>angulo</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Cakto</t>
+          <t>PerfectPay</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -888,7 +884,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>R$ 48,89</t>
+          <t>R$ 277,00,</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -901,24 +897,24 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas [Editado pelo Reclame Aqui] e solicitação de estorno para produto "Retrato da Sua Alma Gêmea"  Respondida  CAKTO PAY  Campinas - SP  31/08/2026 às 02:06  ID: 257780917  Olá, equipe da Cakto Pay,No dia 28/08/2026, realize</t>
+          <t>Comprei o produto Auks Bot, pelo valor de R$ 277,00, com pagamento processado pela Perfect Pay.Em 27/08/2026, ainda... Reclamação sobre reembolso negado pela Perfect Pay para o produto Auks Bot</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/editado-pelo-reclame-aqui-e-solicitacao-de-estorno-para-produto-retrato-da-sua-alma-gemea_H8ihRLGIEQMZ9WSb/</t>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-reembolso-negado-pela-perfect-pay-para-o-produto-auks-bot_KqYsYdFXN1z0_dI5/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>pack canva</t>
+          <t>curso de mandarim</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Pack Canva</t>
+          <t>Curso de Mandarim</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -933,7 +929,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Educação / Idiomas</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -944,39 +940,31 @@
       <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>R$ 15,15</t>
-        </is>
-      </c>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>RA Ads Veja também todas as reclamações não respondidas respondidas finalizadas Solicitação de cancelamento e reembolso de cursos online após arrependimento de compra.  Respondida  CAKTO PAY  Suzano - SP  30/08/2026 às 19:54  ID: 257768163  Me chamo *****, solicito o cancelamento e reembolso do valo</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-reembolso-de-cursos-online-apos-arrependimento-de-compra_-CZPnDHntp_r19_O/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-no-face-book-compra-de-curso-de-mandarim-2099-02092026-190111_uKMKomnheob91qjy/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>em análise</t>
+          <t>e solicita</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>em análise</t>
+          <t>e solicita</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -991,7 +979,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1005,25 +993,5519 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Veja também todas as reclamações não respondidas respondidas finalizadas Cadastro em análise há 10 dias e saldo preso na plataforma  Não respondida  CAKTO PAY  Olinda - PE  06/09/2026 às 03:52  ID: 258329517  Me afiliei à Cacto e já realizei minhas primeiras vendas, mas não consigo sacar meu dinheir</t>
+          <t>Fiz uma compra pela cakto Detalhes do PedidoPedido: *****Data: 02/09/2026Produto: 100 Remédios Naturais ... Reclamação sobre não recebimento de produto e solicitação de estorno do valor pago via PIX.</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.reclameaqui.com.br/cakto-pay/cadastro-em-analise-ha-10-dias-e-saldo-preso-na-plataforma_33Z4I-4H81OMuZA6/</t>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-nao-recebimento-de-produto-e-solicitacao-de-estorno-do-valor-pago-via-pix_19VMI-vOfIlR0IIm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>comunidade mvz no dia 27</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Comunidade MVZ no dia 27</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>R$ 248,89,</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra do produto Comunidade MVZ no dia 27/08/2026, no valor de R$ 248,89, através da plataforma Cakto. Dentro do ... Cliente solicita cancelamento e reembolso de curso online após ser direcionado entre plataforma e produtor.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-solicita-cancelamento-e-reembolso-de-curso-online-apos-ser-direcionado-entre-plataforma-e-produtor_7fIx89P-1ZpAApHx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>na ultima quarta feira</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>na ultima quarta feira</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Boa noite. Fiz a compra de um produto na ultima quarta feira (26/08/20226) e até essa data eu não recebi o produto.Receb... Produto não recebido e dificuldade de acesso ao material digital, com falha no reembolso e suporte ineficaz.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-recebido-e-dificuldade-de-acesso-ao-material-digital-com-falha-no-reembolso-e-suporte-ineficaz_iOzRmbylQ4neQezT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ia academy</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>IA Academy</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>R$ 197,99,</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Realizei no dia 01/09/2026 uma compra através da plataforma Cakto, referente ao produto IA Academy, no valor de R$ 197,99, pa... Solicitação de cancelamento e reembolso de curso online não respondido pelo produtor.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-reembolso-de-curso-online-nao-respondido-pelo-produtor_ddqfFY8ufw0eiA3F/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>comunidade knights club</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>COMUNIDADE KNIGHTS CLUB</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Comunidades / Mentoria de negócios</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO DE REEMBOLSO NÃO CUMPRIDA PAGAMENTO VIA PIXNo dia 21/08/2026, realizei a compra da COMUNIDADE KNIGHTS ... Reembolso de compra via Pix não realizado após solicitação dentro do prazo legal.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-de-compra-via-pix-nao-realizado-apos-solicitacao-dentro-do-prazo-legal_w1bmesmQpVhI5h0M/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>low ticket do zero 2.0 no dia 30</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Low Ticket do Zero 2.0 no dia 30</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra do produto Low Ticket do Zero 2.0 no dia 30/08/2026. Após acessar o produto, constatei que ele não atendeu ... Solicitação de cancelamento e reembolso negada por falta de saldo na conta do produtor.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-reembolso-negada-por-falta-de-saldo-na-conta-do-produtor_g_uRVUXcpBO7YtT5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>chamado f</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>chamado F</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Dia 27/08/2026 comprei um produto chamado Fábrica Viral, não recebi o material no e-mail e o produtor não respondeu a minha t... Comprei um produto, não recebi e não consigo pedir reembolso</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/comprei-um-produto-nao-recebi-e-nao-consigo-pedir-reembolso_kESf7mBZQ-lYpUvb/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>comunidade vsa</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>COMUNIDADE VSA</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Marketing / Comunidades de negócios</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>R$ 248,89.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-de-compra-com-erro-de-saldo-na-conta-do-vendedor_e5d-tH3gUGahNktM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>retrato da sua alma gêmea</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Retrato da Sua Alma Gêmea</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Arte personalizada / IA generativa</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Olá, equipe da Cakto Pay,No dia 28/08/2026, realizei a compra do produto &amp;quot;Retrato da Sua Alma Gêmea&amp;quot; (Código do Ped... [Editado pelo Reclame Aqui] e solicitação de estorno para produto &amp;quot;Retrato da Sua Alma Gêmea&amp;quot;</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-e-solicitacao-de-estorno-para-produto-retrato-da-sua-alma-gemea_H8ihRLGIEQMZ9WSb/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>digital n</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>digital n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Comprei dois produtos digitais que não foram entregues. RA Ads</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/produto-digital-nao-entregue_BJSp7nt8u2UDuoYS/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>curso de yoga n</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>curso de yoga n</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Prezados, esta manha fiz uma compra (+108 Posturas de Yoga Ilustradas, plano premium). Nao recebi o produto, recebi outra coisa e nao consta na area da Cakto Members. Paguei com Pix. O link do reembolso nao funciona, sempre a mesma mensagem: "Não foi possível confirmar o código. Tente novamente". Entrei em contato com o vendedor, sem resposta. Mandei email para a Cakto, sem resposta.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/compra-de-curso-de-yoga-nao-recebida-link-de-reembolso-inoperante-e-falta-de-contato-do-vendedorsuporte_zv5I8nnWtCj3LtbF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>que era pelo gmail mandei a mensagem expl</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>que era pelo Gmail mandei a mensagem expl</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de ferramenta inteligência artificial o acesso pelo cakto mas algumas das principais funções da ferramenta, como o motion control usei 121 de crédito a plataforma não gerou o vídeo e não voltou os créditos até então não gostei da ferramenta eu quis meu reembolso quando fui tentar fazer o reembolso a plataforma do cakto falou que era só com o suporte do produto que era pelo Gmail mandei a mensagem explicando que queria o reembolso não tive resposta aí entrei em contato pelo zap ele</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-negado-e-falta-de-suporte-para-ferramenta-de-ia-nao-funcional_k4Zr32LLud7_uMfl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>digital apexshop vital</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>digital ApexShop Vital</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Streaming e entretenimento</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>R$ 179,90,</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Realizei em 24/08/2026 a compra do produto digital ApexShop Vitalício, no valor de R$ 179,90, por meio da plataforma Perfect Pay. Logo após a contratação, solicitei formalmente o cancelamento da compra e a restituição integral do valor pago, dentro do prazo informado e previsto para o direito de arrependimento. Ao entrar em contato com a Perfect Pay, fui orientada a procurar diretamente o suporte do produto e, caso não recebesse resposta em até 2 dias úteis, deveria encaminhar os comprovantes da</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/perfect-pay-nao-resolve-cancelamento-e-reembolso-repetindo-orientacoes_zJl8k8FgpoKAMXba/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>um usu</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>um usu</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um usuário da aplicação e não recebi o que estava sendo anunciado e pedir reembolso e enviei vários e-mails e sempre dando uma desculpa e não fez o reembolso mandando entrar em contato com o vendedor e ao entrar em contato o e-mail do vendedor não funciona e não tem telefone pra contato sendo assim a perfectpay fica enrolando pra fazer o [Editado pelo Reclame Aqui] RA Ads</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/perfectpay/reclamacao-sobre-produto-nao-recebido-e-dificuldade-de-reembolso-na-perfect-pay_zlFPokdZpRPcKoYM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>digital ap</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>digital ap</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>R$ 88,19,</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra do produto +600 Horas de Roteiros Prontos para Live Shop, no dia 19/08/2026, pelo valor de R$ 88,19, pago via PIX. Após a compra, decidi não continuar com o produto e solicitei o cancelamento da compra e o reembolso do valor pago. No dia 24/08/2026, enviei uma solicitação por escrito pedindo formalmente o cancelamento e o reembolso, informando os dados da compra e o número do pedido. Até o momento, porém, não obtive uma solução para o meu pedido. Também tive dificuldades para e</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/cliente-solicita-cancelamento-e-reembolso-de-produto-digital-apos-dificuldades-de-contato-e-falta-de-solucao_iqfFFkNKnKahBQk5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>no dia</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>no dia</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>R$ 86,80</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Comprei um produto no dia **26/08** e, no mesmo dia, solicitei o reembolso, pois o produto recebido não correspondia ao que era prometido na oferta. Ao entrar em contato com a **Cakto**, fui informado de que o reembolso deveria ser solicitado diretamente ao produtor. Tentei contato com o produtor durante **3 dias**, mas não obtive nenhum retorno. No dia **29/08**, entrei novamente em contato com um atendente da Cakto pelo WhatsApp, porém também não tive retorno. Fiz uma nova tentativa de contato</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-de-produto-nao-correspondente-a-oferta-apos-8-dias-de-tentativas-de-contato-sem-sucesso_vgLnIAw9NhALvEvt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>incompleto dentro do prazo de 7 dias. n</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>incompleto dentro do prazo de 7 dias. N</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra na caktos mais o produto veio incompleto pedi o reembolso dentro do 7 dias ..eles nao fizeram o reembolso. RA Ads</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/reembolso-nao-realizado-apos-devolucao-de-produto-incompleto-dentro-do-prazo-de-7-dias_ESBgjxHcHH6maS_a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>para poder solicitar o cancelamento</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>para poder solicitar o cancelamento</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de uma assinatura online, porém o serviço não me atendeu, eu solicitei o cancelamento dentro do prazo de 7 dias por e-mail no suporte da empresa, porém até hoje não tive o retorno sobre o cancelamento do pedido. Solicito o cancelamento e estorno eu valor. A empresa não tem nenhum campo no site deles ou do produto para poder solicitar o cancelamento, somente por e-mail, quando enviamos um e-mail só vem resposta automática, aguardo previdências. RA Ads</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-assinatura-online-nao-respondida-pelo-suporte_t696AVuN0Vj7PGWm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>perfect academy</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Perfect Academy</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria / Cursos online</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Comprei um curso na perfect academy, mais o curso veio incompleto, fui tentar pedir meu reembolso, onde me deparei sem suport... Curso incompleto e falta de suporte para reembolso na Perfect Academy</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/curso-incompleto-e-falta-de-suporte-para-reembolso-na-perfect-academy_xfFtbFJD4cncefLz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>aplicativo</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>aplicativo</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Eu adquiri uma compra pela [Editado pelo Reclame Aqui] prometendo acesso a um app pago e após pagar o aplicativo simplesmente... Cobrança indevida e solicitação de estorno após compra de aplicativo</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-solicitacao-de-estorno-apos-compra-de-aplicativo_k54KbhcZ8MWgLTn0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>tikedit pela perfectpay</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>TikEdit pela PerfectPay</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/recusa-de-reembolso-em-renovacao-automatica-de-produto-tikedit-pela-perfectpay_7DczqrMSjVJHqp26/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>vendido pela appluna.net</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>vendido pela Appluna.net</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>A referida empresa, alega ser uma plataforma de gerenciamento de pagamentos online que informa não ter responsabilidade sobre... Perfectpay cobra por serviço, mas não resolve problemas de acesso ao produto vendido pela Appluna.net</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perfectpay-cobra-por-servico-mas-nao-resolve-problemas-de-acesso-ao-produto-vendido-pela_a5_1eWXf4MZ6sZZ7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>aparece na perfect pay mas o mesmo n</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>APARECE NA PERFECT PAY MAS O MESMO N</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Fiz A COMPRA DE UM SERVIÇO NO QUAL É [Editado pelo Reclame Aqui] E O PRODUTO APARECE NA PERFECT PAY MAS O MESMO NÃO SE RESPO... Compra de serviço com promessa de [Editado pelo Reclame Aqui] e Perfect Pay se isenta de responsabilidade</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-com-promessa-de-editado-pelo-reclame-aqui-e-perfect-pay-se-isenta-de-responsabilidade_0DOgqsLTHMXBEQUg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>receb... propaganda enganosa</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>receb... Propaganda enganosa</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/propaganda-enganosa_zOGr7sPQQhH7ROqM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>plataforma home office</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma Home Office</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Solicito o cancelamento e o reembolso do valor pago pelo produto Plataforma Home Office, vinculado ao e-mail ***** . O produt... Solicitação de cancelamento e reembolso de Plataforma Home Office por propaganda enganosa.</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-plataforma-home-office-por-propaganda-enganosa_Z3FnnwZ03NBXKWFQ/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>de postagem autom</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>de postagem autom</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Comprei um produto ( inteligência artificial com + 10.700 vídeos) com a proposta de postagens automáticas na shopee vídeo, In... Reclamação sobre produto de postagem automática com cobranças adicionais, sem retorno do suporte , sem liberação do prometido e com acesso restrito ao conteúdo,e falta de reembolso.</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-de-postagem-automatica-com-cobrancas-adicionais-sem-retorno-do-suporte-sem-liberacao-do-prometido-e-com-acesso-restrito-ao-conteudoe-falta-de-reembolso_6xa6Ai85fTyG0Yce/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>acesso a conversas do instagram n</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>acesso a conversas do Instagram n</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Crescimento em redes sociais</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-acesso-a-conversas-do-instagram-nao-realizada-e-solicitacao-de-reembolso_bEr04z5n0qvNdmJf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>códigos lucrativos</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Códigos Lucrativos</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-editado-pelo-reclame-aqui-e-editado-pelo-reclame-aqui-solicitacao-de-reembolso_xx2YJjct0gsb0fGa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>zap radar</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ZAP Radar</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de espionagem / WhatsApp</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra no valor de 137,00 site ZAP radar e fui [Editado pelo Reclame Aqui] porque não abre um relatório. Peço o ... Solicitação de estorno de compra no site ZAP Radar por não recebimento de relatório.</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-de-compra-no-site-zap-radar-por-nao-recebimento-de-relatorio_lZ9TTmWZxIG43bv7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>fica saindo e entrando sozinho</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>fica saindo e entrando sozinho</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/nao-gostei-do-app-fica-saindo-e-entrando-sozinho_UkdzKQ86egq0egAP/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-e-nao-recebi_IgLy-Z3TgKa5WfbK/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>chamado protocolo black digital e comprei</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>chamado Protocolo Black Digital e comprei</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Eu comprei um produto chamado Protocolo Black Digital e comprei dois order bumps, e o produto é horrível, na hora de eu pedir... Impossibilidade de solicitar reembolso para o produto Protocolo Black Digital e order bumps.</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/impossibilidade-de-solicitar-reembolso-para-o-produto-protocolo-black-digital-e-order-bumps_KUmvlWU2BBaqoLGc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>aplicativo viewerspy com tr</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>aplicativo ViewerSpy com tr</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de aplicativo ViewerSpy com três pagamentos, mas se tratava de [Editado pelo Reclame Aqui], quero meu dinheiro... [Editado pelo Reclame Aqui] em aplicativo ViewerSpy com cobrança indevida, solicitação de [Editado pelo Reclame Aqui].</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-viewerspy-com-cobranca-indevida-solicitacao-de-editado-pelo-reclame-aqui_4jVYpRQh7FZ9NsuM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>servi</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>servi</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra me garantindo acesso a fotos e conversas de um WhatsApp meu mesmo que perdi acesso, mas fui enganado paguei tu... Compra de serviço para recuperação de WhatsApp que direciona para página de curso.</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-servico-para-recuperacao-de-whatsapp-que-direciona-para-pagina-de-curso_9jbLXBtTk54j7-aK/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>inexistente</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>inexistente</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-editado-pelo-reclame-aqui-e-solicitacao-de-editado-pelo-reclame-aqui-com-base-no-direito-de-arrependimento_SenuNicKKSMOvgEa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>uma ferramenta de automa</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>uma ferramenta de automa</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-cancelamento-e-reembolso-de-ferramenta-de-automacao-nao-recebida_3ia2l_X9I98IiU5Q/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>simplesmente n</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>simplesmente n</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de um sistema multijogos da Retrogame Ramos, porém o produto simplesmente não funcionou. Solicitei o reembolso e... Reclamação sobre sistema multijogos não funcional e falta de reembolso pela Retrogame Ramos</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-sistema-multijogos-nao-funcional-e-falta-de-reembolso-pela-retrogame-ramos_yXzSmLa6zWMj18Hq/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>no valor de 97 reais que nao gostei pedi</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>no valor de 97 reais que nao gostei pedi</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>[Editado pelo Reclame Aqui]. comprei um produto no valor de 97 reais que nao gostei pedi o reembolso e ninguem resolve nada m... Reclamação sobre propaganda enganosa e dificuldade em obter reembolso de produto.</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-propaganda-enganosa-e-dificuldade-em-obter-reembolso-de-produto_NexaAcyAJfkO5zUN/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>quemetia trazer minha conta do free f</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>que prometia trazer minha conta do free f</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Quero reembolso do meu dinheiro, comprei um produto que prometia trazer minha conta do free fire de volta, mais era tudo [Edi... Produto de Free Fire prometia recuperar conta, mas era [Editado pelo Reclame Aqui] e cliente pede reembolso.</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-de-free-fire-prometia-recuperar-conta-mas-era-editado-pelo-reclame-aqui-e-cliente-pede-reembolso_6E9DzuuICeSs7-BW/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>spygram</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Spygram</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-reembolso-de-pagamentos-via-pix-para-o-programa-spygram-identificado-como-editado-pelo-reclame-aqui_tx5DRYfAycgJL_5j/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>um curso de arais amador paguei e n</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>um curso de arais amador paguei e n</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um curso de arais amador paguei e não recebi segue comprovante de pagamento Fui vítima de [Editado pelo Reclame Aqui]</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/fui-vitima-de-editado-pelo-reclame-aqui_eaEOE7rI3vDh1NKM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>tudo dentro do prazo tudo certinho e ate</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>tudo dentro do prazo tudo certinho e ate</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso_3QFTCw6-Ygo025v1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>dois aplicativo e n</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>dois aplicativo e n</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>R$ 27,90</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Bom dia ! Fiz uma compra de dois aplicativo e não recebi o aplicativo, no valor de R$ 27,90 e outro de R$ 19,00 às 16:35 h no... Compra de aplicativos não recebidos, solicitação de reembolso.</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/compra-de-aplicativos-nao-recebidos-solicitacao-de-reembolso_IVdC0jac41EFjNhF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>espia f</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>espia f</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o app espia fácil pro e não me deram o acesso. Quero reembolso Cair em um [Editado pelo Reclame Aqui]</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cair-em-um-editado-pelo-reclame-aqui_3GiaHX5kQ4C877x9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>um aplicativo de monitoramento pelo an</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>um aplicativo de monitoramento pelo an</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um aplicativo de monitoramento pelo anúncio no YouTube paguei 46.90 e levei um [Editado pelo Reclame Aqui] ... [Editado pelo Reclame Aqui] em aplicativo de monitoramento cliente solicita estorno de valor pago por produto não funcional.</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui-em-aplicativo-de-monitoramento-cliente-solicita-estorno-de-valor-pago-por-produto-nao-funcional_nGia5bRqbVr80nh-/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>um vendedor que usa os servi</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>um vendedor que usa os servi</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Efetuei uma compra de um vendedor que usa os serviços da perfect pay para pagamentos. O vendedor não enviou acesso ao produto... Reclamação sobre produto não entregue e solicitação de estorno de valor pago através da Perfect Pay.</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-nao-entregue-e-solicitacao-de-estorno-de-valor-pago-atraves-da-perfect-pay_87chbXy48Qb7cTPa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>no ... reembolso dentro do prazo</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>no ... reembolso dentro do prazo</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Solicitei reembolso dentro do prazo, mas não consigo contato com o vendedorAdquiri através da Perfect Pay um produto no ... reembolso dentro do prazo, mas não consigo contato com o vendedor após compra de produto com conteúdo enganoso.</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-dentro-do-prazo-mas-nao-consigo-contato-com-o-vendedor-apos-compra-de-produto-com-conteudo-enganoso_msDSOKrJ-W3coXfK/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>grupo vip</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>grupo VIP</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Bem, eu fiz uma compra na segunda-feira de um grupo vip do js e não estou satisfeito, quero o meu reembolso, ja vou deixar es... Reembolso negado e falta de contato do suporte após compra de grupo VIP</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-negado-e-falta-de-contato-do-suporte-apos-compra-de-grupo-vip_l-3zMo_MYaiaFQbn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>e n</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>e n</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Serviços financeiros / Pix</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um produto e não recebi, alegam que não foi pago, já reclamei várias vezes com o vendedor e até agora ele n... Produto não recebido e vendedor alega falta de pagamento, sem resolução.</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-nao-recebido-e-vendedor-alega-falta-de-pagamento-sem-resolucao_4ypAxIw4TPAzgFfj/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>de baixa qualidade</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>de baixa qualidade</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra aonde prometia uma reza sagrada que faz prosperar e abrir caminhos, mas a reza não foi feita e me cobraram 3 v... Cobrança indevida e produto de baixa qualidade (PDF de IA) em vez de reza prometida.</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-indevida-e-produto-de-baixa-qualidade-pdf-de-ia-em-vez-de-reza-prometida_S22Bk6Gf4HfO6zVF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>um painel e n</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>um painel e n</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um painel e não funcionou [Editado pelo Reclame Aqui] Solicito reembolso 19.99 [Editado pelo Reclame Aqui]</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/editado-pelo-reclame-aqui_5xPVEL37uCq2Nl_s/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>um curso chamado geniun shop</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>um curso chamado Geniun Shop</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Adquiri um curso chamado Geniun Shop , em 2 de abril de 2026 , fiZ apenas as primeiras aulas, e agora quando resolvi voltar p... Perda de acesso ao curso Geniun Shop após pagamento, sem retorno do suporte.</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/perda-de-acesso-ao-curso-geniun-shop-apos-pagamento-sem-retorno-do-suporte_a6tTJhax8GBOg4xh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>onde dizia que tinha v</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>onde dizia que tinha v</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Comprei um produto onde dizia que tinha vários fornecedores de roupas no Brasil..mas não tinha o que eu eu queria .por isso q... Reclamação sobre produto com fornecedores de roupas limitados e solicitação de reembolso.</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reclamacao-sobre-produto-com-fornecedores-de-roupas-limitados-e-solicitacao-de-reembolso_H7FXu4ussEtUSJQC/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>com defeito e solicita</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>com defeito e solicita</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra no Blackxitoficial (meu Gmail é *****). Meu CPF: *****, no valor de 31 reais. O Painel chegou, mas não funcion... Produto com defeito e solicitação de reembolso</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/produto-com-defeito-e-solicitacao-de-reembolso_GgMl5lRE9VZtuHoJ/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>na plataforma e n</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>na plataforma e n</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>comprei um produto na plataforma e não gostei, quero meu reembolso, foi comprado no pix:Código da compra: ***** Cliente deseja reembolso de aquecedor comprado via Pix por não ter gostado do produto.</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cliente-deseja-reembolso-de-aquecedor-comprado-via-pix-por-nao-ter-gostado-do-produto_2qo_Zk1Eh3qTNpQy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>nessa plataforma</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>nessa plataforma</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Verifiquei a compra de um produto nessa plataforma, solicitei o reembolso junto a produtora do produto e não consegui retorno... Reembolso não resolvido pela plataforma após contato com produtora e cancelamento de cartão.</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/reembolso-nao-resolvido-pela-plataforma-apos-contato-com-produtora-e-cancelamento-de-cartao_P1PpJ-yUSNmPIVUp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>em um site na internet e ao abrir o email</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>em um site na internet e ao abrir o email</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Serviços financeiros / Pix</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Realizei uma compra de um produto em um site na internet e ao abrir o email enviado me cobraram outra taxa que não estava com... Cobrança de taxa adicional não combinada e falta de acesso ao produto comprado.</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/cobranca-de-taxa-adicional-nao-combinada-e-falta-de-acesso-ao-produto-comprado__chfFQTX8pupMWB5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>tomei</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Tomei</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tomei-editado-pelo-reclame-aqui_PCEkQCMzbA-5dwgy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>no qual n</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>no qual n</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um produto no qual não corresponde a minha expectativa , então solicito o estorno do meu valor. Email: ****... Solicitação de estorno por produto não correspondente à expectativa</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/solicitacao-de-estorno-por-produto-nao-correspondente-a-expectativa_jZ-08RI4TwV-ynQ4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>um grupo vip no dia 20</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>um grupo vip no dia 20</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>PerfectPay</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Olá, fiz uma compra de um grupo vip no dia 20/08 e dia 23/08 tentei fazer o cancelamento, mas o vendedor ***** - operações nã... Tentativa de cancelamento de grupo VIP e impossibilidade de contato com o vendedor</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/perfectpay/tentativa-de-cancelamento-de-grupo-vip-e-impossibilidade-de-contato-com-o-vendedor_SkOpE6e5RhZv8KIr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>turminha alfakids</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Turminha Alfakids</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Educação infantil / Materiais didáticos</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra da turminha Alfakids de 2750 atividades e não recebi,o email que aparece como suporte não responde Compra não recebida e falta de resposta do suporte</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-nao-recebida-e-falta-de-resposta-do-suporte_yWkDvnrLPMHo7aTz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>um curso</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>um curso</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-de-curso-nao-realizado-apos-solicitacao-dentro-do-prazo_ktvLpzB4DAj5K-_J/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>directspeed</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Directspeed</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de produtividade / Assinatura</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-da-ferramenta-directspeed-nao-respondida_G-frs9kFEKvabVpn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>cortes do marques</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Cortes do Marques</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Estou há quase 1 mês tentando cancelar a assinatura do produto Cortes do Marques, adquirido por meio da Cackto, mas até o mom... Cackto não realiza cancelamento de assinatura mesmo após várias solicitações</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cackto-nao-realiza-cancelamento-de-assinatura-mesmo-apos-varias-solicitacoes_WEDpJ2MDQNCpB9xD/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>umgrama de karaoke e est</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>um programa de karaoke e est</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de um programa de karaoke e está dando conteúdo não encontrado paguei via pix. Conteúdo não encontrado</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/conteudo-nao-encontrado_eh2tS2q3T2WGSky_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>uma m</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>uma m</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de uma máscara coreana , fiz o pagamento no PIX e a empresa relatou que eu nao havia pago, eu ,logo a seguir ... Pagamento via PIX não reconhecido e falta de retorno da empresa após envio de comprovante.</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-reconhecido-e-falta-de-retorno-da-empresa-apos-envio-de-comprovante_C6tRKpYDqejq7Cvf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>curso online capsulas gourmet e c</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>curso online capsulas gourmet e c</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/materiais-de-curso-online-de-capsulas-gourmet-e-capuccinos-nao-disponiveis_jlp3yz2MCVJGF1UT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>um curso no dia 01</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>um curso no dia 01</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue_RxHp4cyuljYU2Wtj/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>diferente do anunciado e a plataforma n</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>diferente do anunciado e a plataforma n</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/vendedor-entregou-produto-diferente-do-anunciado-e-a-plataforma-nao-resolve_vkGIXT8UU80pbQbc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>chegou faltando conte</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>chegou faltando conte</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra por lá, produto chegou faltando conteúdo, entro em contato com eles e ZERO atendimento, preciso fazer o estorn... Produto com conteúdo faltante e falta de atendimento para estorno</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-com-conteudo-faltante-e-falta-de-atendimento-para-estorno_S6A780k9_99Ofap-/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>um curso na plataforma deles</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>um curso na plataforma deles</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-estorno-de-curso-online-com-ma-qualidade-e-falta-de-resposta_rDQ1eDeZL9eCjgqm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>auto live shop</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Auto Live Shop</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra do produto Auto Live Shop, porém, após utilizar o produto, constatei que ele não atendeu às minhas expectat... Solicitação de reembolso para produto Auto Live Shop não processada pela plataforma Cakto</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-para-produto-auto-live-shop-nao-processada-pela-plataforma-cakto_Zejb3D4JhCq2o48c/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>pelo pouco que testei</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>pelo pouco que testei</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 197,99.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o Plano Starter mensal da Cloakby por R$ 197,99. O produto pelo pouco que testei é excelente. Porém, não atendeu as m... Reclamação Sobre Oferta da Cloakby: propaganda enganosa e péssimo atendimento ao solicitar reembolso</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-oferta-da-cloakby-propaganda-enganosa-e-pessimo-atendimento-ao-solicitar-reembolso_DS552Q4NU1VCy-bp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>uma assinatura do site copie</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>uma assinatura do site copie.ai</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 97,00,</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Realizei a compra de uma assinatura do site copie.ai, no dia 30 de agosto de 2026, às 17h38min, no valor de R$97,00, no site ... Assinatura Copie.ai não liberada após compra e sem retorno do suporte.</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/assinatura-nao-liberada-apos-compra-e-sem-retorno-do-suporte__RpqyPU88WZJtxd1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>pois n</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>pois n</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra mas não gostei do produto pois não atingiu minhas espectativas solicito o reembolso pois está no prazo de gara... Solicitação de reembolso por produto que não atendeu às expectativas dentro do prazo de garantia.</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-que-nao-atendeu-as-expectativas-dentro-do-prazo-de-garantia_4ccUExOzKRUFA4MT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>dois cursos de idiomas</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>dois cursos de idiomas</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de dois cursos de idiomas, no caso Espanhol. Paguei pelos dois cursos via pi, porém só tive acesso a um curso,... Acesso negado a curso de espanhol pago e dificuldade de contato com o suporte para reembolso.</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/acesso-negado-a-curso-de-espanhol-pago-e-dificuldade-de-contato-com-o-suporte-para-reembolso_9d9eJH4OMC_ApZLR/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>um site hoje e quero solicitar o cancelam</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>um site hoje e quero solicitar o cancelam</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>fiz uma compra de um site hoje e quero solicitar o cancelamento e direito a arrependimento dentro de 7 dias, fiz um pedido ma... Solicitação de cancelamento e estorno de 3 pedidos devido a arrependimento e insatisfação com o produto/site.</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-3-pedidos-devido-a-arrependimento-e-insatisfacao-com-o-produtosite_KUDEd8s3eGajQ3-L/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria no dia 26 onde o reembolso e</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de uma mentoria no dia 26 onde o reembolso era de responsabilidade do produtor, produtor esse que me ignorou por... Reclamação sobre reembolso de mentoria não processado e falta de suporte</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-reembolso-de-mentoria-nao-processado-e-falta-de-suporte_nV8WPHM4qJbjnUSu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>estrutura para gera</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>estrutura para gera</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/contestacao-de-compra-de-estrutura-para-geracao-de-retorno-financeiro-nao-concretizado-e-falta-de-informacao-sobre-investimentos-adicionais_CUW1-e-tTFELAg9M/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Youclone no dia 28</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Comprei o produto Youclone no dia 28/08, no pix.Quando fui entrar no curso, não abre a área de membros e não consig... Cliente não consegue acessar área de membros do curso Youclone e relata falta de suporte.</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-consegue-acessar-area-de-membros-do-curso-youclone-e-relata-falta-de-suporte_2aC8MLyewmAd3CCU/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>oduto</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>o produto</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Adquiri o produto &amp;quot;Combo Black&amp;quot; do Gustavo de Castro e recebi um e-mail de aprovação de compra sem acesso ao produt... Cliente não tem acesso ao produto &amp;#x27;Combo Black&amp;#x27; após aprovação de compra e não obtém resposta do suporte.</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/cliente-nao-tem-acesso-ao-produto-combo-black-apos-aprovacao-de-compra-e-nao-obtem-resposta-do-suporte_na5373f4sUAHpMsE/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>um curso de ia nao gostei do curso e dent</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>um curso de IA nao gostei do curso e dent</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>fiz uma compra de um curso de IA nao gostei do curso e dentro do prazo de 7 dias solicitei o reembolso pelo email que disponi... Estorno</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/estorno_hMRVrko0Dz8fVqsF/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>cuja cobran</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>cuja cobran</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-de-assinatura-mensal-nao-efetivada-pela-plataforma-cakto_rOS_H0sA8Ne2Yb4r/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>apostila de psicologia 2025</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Apostila de Psicologia 2025</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Educação / Concursos e certificações</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra on-line de uma Apostila de Psicologia 2025 e um combo de Aprovação Psico.Já entrei em contato por e-mail,... Apostila de Psicologia 2025 não abre e cliente não obtém retorno sobre compra online.</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/apostila-de-psicologia-2025-nao-abre-e-cliente-nao-obtem-retorno-sobre-compra-online_30j5btxdpP7LLsjJ/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>fábrica de low ticket</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Fábrica de Low Ticket</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Educação / Marketing digital e low ticket</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Olá,Solicito o reembolso da compra da Fábrica de Low Ticket.Adquiri o curso com base na promessa apresent... Reembolso solicitado por propaganda enganosa sobre suporte individual no curso Fábrica de Low Ticket</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-solicitado-por-propaganda-enganosa-sobre-suporte-individual-no-curso-fabrica-de-low-ticket_BQx79JwlEi7-NBzU/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>incompleto dentro da garantia</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>incompleto dentro da garantia</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Gostaria do reembolso dos seguintes produtos que comprei, está dentro do prazo de garantia de 7 dias.Email de Compra: **... Solicitação de reembolso por produto incompleto dentro da garantia</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-reembolso-por-produto-incompleto-dentro-da-garantia_DBUjl2QuaruN_QYD/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>mas n</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>mas n</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Espionagem e rastreamento</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-me-respondem_ddIIs2OseJhlXI2v/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>de streaming n</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>de streaming n</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Streaming e entretenimento</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-desacordo-comercial-por-servico-de-streaming-nao-recebido-e-falta-de-contato-do-vendedor_xHL_Rnpj7hKZ3vjT/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>que eu comprei na plataforma cakto ..o pr</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>que eu comprei na plataforma Cakto ..o pr</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Estou tentando cancelar um produto que eu comprei na plataforma Cakto ..o produto que eu comprei foi calcula chef app não es... Não consigo cancelar o produto Calcula Chef App e não recebo retorno da Cakto.</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-cancelar-o-produto-calcula-chef-app-e-nao-recebo-retorno-da-cakto_mwF3xbe9PnLeIpH4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>um curso na sexta feira e n</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>um curso na sexta feira e n</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>fiz uma compra de um curso na sexta feira e não recebi, também pelo chat de suporte não tenho retorno. Quero o reembolso, poi... Curso não recebido e falta de retorno do suporte, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-nao-recebido-e-falta-de-retorno-do-suporte-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_KD9yrBbG0QhwORjs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>uma planilha e n</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>uma planilha e n</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/nao-consigo-suporte_245GAIgR4SjdP8m1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>um aplicativo</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>um aplicativo</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de um aplicativo, porém o mesmo não funciona, entrei em contato com a cakto por email, entrei em contato pelo ... Reclamação sobre aplicativo não funcional e falta de resposta do suporte para reembolso.</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reclamacao-sobre-aplicativo-nao-funcional-e-falta-de-resposta-do-suporte-para-reembolso_vE-W5K4jwJY0jtXa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>material de fonoaudiologia e n</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>material de fonoaudiologia e n</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de material de fonoaudiologia e não no momento de baixar o material era mal feito, a fonoaudióloga sequer exis... Material de fonoaudiologia de má qualidade e recusa de reembolso pela Cacto.</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/material-de-fonoaudiologia-de-ma-qualidade-e-recusa-de-reembolso-pela-cacto_zjP5uaGFy2s7z7ZP/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>pela cakto e logo realizei o pedido de re</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>pela cakto e logo realizei o pedido de re</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Fiz a compra de um produto pela cakto e logo realizei o pedido de reembolso, porem sem sucesso, pois a plataforma dar erro: &amp;... Erro ao tentar solicitar reembolso de produto na Cakto</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/erro-ao-tentar-solicitar-reembolso-de-produto-na-cakto_ZhxbaEfvn9crLs7c/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>programa n</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>programa n</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra online e o programa não funcionou durante dois dias comecei a enviar para o produtor e para empresa Catho o pe... Reembolso não efetuado e falta de resposta da Catho e do produtor após compra de programa não funcional.</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-nao-efetuado-e-falta-de-resposta-da-catho-e-do-produtor-apos-compra-de-programa-nao-funcional_2BTWhdCr7obnyw-X/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>uma mentoria</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/compra-de-mentoria-nao-encontrada-e-falta-de-suporte-da-cakto-e-do-vendedor_Bt44ofl5iW09TC9d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>com defeito</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>com defeito</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>fiz a comprar de um produto , o produto não rodou no meu pc pedi o reembolso e mandaram falar com o produtor , mandei mensage... Reembolso negado e contato com o produtor indisponível após compra de produto com defeito</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso-negado-e-contato-com-o-produtor-indisponivel-apos-compra-de-produto-com-defeito_JT9yPhOIhMRefinl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>frequência da vinci</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Frequência da Vinci</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Saúde / Tratamentos alternativos</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra por impulso,de um programa de cura do zumbido no ouvido e gostaria de cancelar e ter o extorno do valor pago p... Solicitação de cancelamento e estorno de programa de cura de zumbido</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/solicitacao-de-cancelamento-e-estorno-de-programa-de-cura-de-zumbido_T3cY3B6mIP4BEv_Y/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>da vav</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>da Vav</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>**Produto não entregue e criador não responde solicito reembolso**Realizei a compra de um produto da Vavá Aca... Produto não entregue e criador não responde, solicito reembolso</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/produto-nao-entregue-e-criador-nao-responde-solicito-reembolso_605Q8ntQ-aQlegi3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>digitalcessada pela cakto</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>digital processada pela Cakto</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/editado-pelo-reclame-aqui-em-compra-de-produto-digital-processada-pela-cakto-com-editado-pelo-reclame-aqui-e-nao-entrega_HJtQooCkVBEfTtMB/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>converza.io</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Converza.io</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Chatbots / Automação de mensagens</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/exijo-reembolso-servico-nao-funciona-e-suporte-nao-responde_OPi-rimJXtkjo2yB/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>comprad... pagamento via pix n</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>comprad... Pagamento via PIX n</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Ferramentas de IA / Produtividade</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Fiz o pgto via PIX para a empresa seguro-vidasaudavel.site através da Cakto Pay, porém não me foi fornecido o produto comprad... Pagamento via PIX não resultou na entrega do produto, solicitação de reembolso por possível [Editado pelo Reclame Aqui].</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/pagamento-via-pix-nao-resultou-na-entrega-do-produto-solicitacao-de-reembolso-por-possivel-editado-pelo-reclame-aqui_cbUdm8Fq5-5oanwH/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>curso online</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>curso online</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Crescimento em redes sociais</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra de curso online, pgn no Instagran que se chama Amigurumi Brasil, pgn com mais de 1.5 k de seguidores, e até ho... Curso online não entregue após pagamento, com falha na comunicação e solicitação de estorno.</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/curso-online-nao-entregue-apos-pagamento-com-falha-na-comunicacao-e-solicitacao-de-estorno_-bekag5hY78F-1mM/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>mas at</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>mas at</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>angulo</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Cakto</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Infoprodutos - suporte e reembolso</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>fria</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Fiz uma compra na loja e quero reembolsar meu produto mas até agora não fui atendido Reembolso</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reclameaqui.com.br/empresa/cakto-pay/reembolso_Ou6F1k9zy_0W3ATN/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L10"/>
+  <autoFilter ref="A1:L113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1034,7 +6516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1086,17 +6568,17 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Ferramentas de IA / Produtividade</t>
+          <t>Infoprodutos - suporte e reembolso</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -1105,23 +6587,23 @@
         <v>0</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Educação e consultoria</t>
+          <t>Ferramentas de IA / Produtividade</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
@@ -1130,7 +6612,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -1140,22 +6622,522 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Educação e consultoria</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Streaming e entretenimento</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Crescimento em redes sociais</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Serviços financeiros / Pix</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Ferramentas / Aplicativos</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Educação e consultoria / Mentoria</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Educação / Idiomas</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Comunidades / Mentoria de negócios</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Marketing / Comunidades de negócios</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Arte personalizada / IA generativa</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Educação e consultoria / Cursos online</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Ganhar dinheiro online / Ferramentas de afiliado</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Ferramentas de espionagem / WhatsApp</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Educação infantil / Materiais didáticos</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Ferramentas de produtividade / Assinatura</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Educação / Concursos e certificações</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Educação / Marketing digital e low ticket</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Saúde / Tratamentos alternativos</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Chatbots / Automação de mensagens</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1431,7 +7413,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,7 +7428,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1761,7 +7743,7 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1806,7 +7788,7 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2226,7 +8208,7 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2421,7 +8403,7 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2451,7 +8433,7 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -2511,7 +8493,7 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
@@ -2676,7 +8658,7 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
